--- a/outputs/QLD_historical_prices.xlsx
+++ b/outputs/QLD_historical_prices.xlsx
@@ -528,16 +528,16 @@
         </is>
       </c>
       <c r="B5" s="5" t="n">
-        <v>79.2</v>
+        <v>75.58</v>
       </c>
       <c r="C5" s="5" t="n">
-        <v>83.27</v>
+        <v>78.97</v>
       </c>
       <c r="D5" s="5" t="n">
-        <v>80.06</v>
+        <v>76.25</v>
       </c>
       <c r="E5" s="5" t="n">
-        <v>84.28</v>
+        <v>79.78</v>
       </c>
     </row>
     <row r="6">
@@ -547,16 +547,16 @@
         </is>
       </c>
       <c r="B6" s="5" t="n">
-        <v>91.75</v>
+        <v>90.51000000000001</v>
       </c>
       <c r="C6" s="5" t="n">
-        <v>99.70999999999999</v>
+        <v>98.5</v>
       </c>
       <c r="D6" s="5" t="n">
-        <v>94.15000000000001</v>
+        <v>92.73999999999999</v>
       </c>
       <c r="E6" s="5" t="n">
-        <v>102.39</v>
+        <v>101.03</v>
       </c>
     </row>
     <row r="7">
@@ -566,16 +566,16 @@
         </is>
       </c>
       <c r="B7" s="5" t="n">
-        <v>92.56999999999999</v>
+        <v>91.05</v>
       </c>
       <c r="C7" s="5" t="n">
-        <v>101.11</v>
+        <v>99.36</v>
       </c>
       <c r="D7" s="5" t="n">
-        <v>96.34</v>
+        <v>94.55</v>
       </c>
       <c r="E7" s="5" t="n">
-        <v>105.28</v>
+        <v>103.26</v>
       </c>
     </row>
     <row r="8">
@@ -585,16 +585,16 @@
         </is>
       </c>
       <c r="B8" s="5" t="n">
-        <v>116.97</v>
+        <v>117</v>
       </c>
       <c r="C8" s="5" t="n">
-        <v>137.06</v>
+        <v>136.84</v>
       </c>
       <c r="D8" s="5" t="n">
-        <v>128.84</v>
+        <v>128.67</v>
       </c>
       <c r="E8" s="5" t="n">
-        <v>151.82</v>
+        <v>151.38</v>
       </c>
     </row>
     <row r="9">
@@ -604,22 +604,22 @@
         </is>
       </c>
       <c r="B9" s="5" t="n">
-        <v>93.40000000000001</v>
+        <v>93.31</v>
       </c>
       <c r="C9" s="5" t="n">
-        <v>108.7</v>
+        <v>108.44</v>
       </c>
       <c r="D9" s="5" t="n">
-        <v>109.17</v>
+        <v>108.89</v>
       </c>
       <c r="E9" s="5" t="n">
-        <v>127.43</v>
+        <v>126.95</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="6" t="inlineStr">
         <is>
-          <t>Data through: Mar 2026</t>
+          <t>Data through: Apr 2026</t>
         </is>
       </c>
     </row>
@@ -634,7 +634,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F274"/>
+  <dimension ref="A1:F275"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -6220,18 +6220,38 @@
         </is>
       </c>
       <c r="B274" s="5" t="n">
-        <v>65.23</v>
+        <v>62.64</v>
       </c>
       <c r="C274" s="5" t="n">
-        <v>65.02</v>
+        <v>61.19</v>
       </c>
       <c r="D274" s="5" t="n">
-        <v>65.23</v>
+        <v>62.64</v>
       </c>
       <c r="E274" s="5" t="n">
-        <v>65.02</v>
+        <v>61.19</v>
       </c>
       <c r="F274" s="7" t="inlineStr"/>
+    </row>
+    <row r="275">
+      <c r="A275" s="4" t="inlineStr">
+        <is>
+          <t>Apr 2026</t>
+        </is>
+      </c>
+      <c r="B275" s="5" t="n">
+        <v>57.69</v>
+      </c>
+      <c r="C275" s="5" t="n">
+        <v>51.98</v>
+      </c>
+      <c r="D275" s="5" t="n">
+        <v>57.69</v>
+      </c>
+      <c r="E275" s="5" t="n">
+        <v>51.98</v>
+      </c>
+      <c r="F275" s="7" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -6244,7 +6264,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E274"/>
+  <dimension ref="A1:E275"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -11456,20 +11476,39 @@
         </is>
       </c>
       <c r="B274" s="5" t="n">
-        <v>65.23</v>
+        <v>62.64</v>
       </c>
       <c r="C274" s="5" t="n">
-        <v>65.02</v>
+        <v>61.19</v>
       </c>
       <c r="D274" s="5" t="n">
-        <v>65.23</v>
+        <v>62.64</v>
       </c>
       <c r="E274" s="5" t="n">
-        <v>65.02</v>
+        <v>61.19</v>
+      </c>
+    </row>
+    <row r="275">
+      <c r="A275" s="4" t="inlineStr">
+        <is>
+          <t>Apr 2026</t>
+        </is>
+      </c>
+      <c r="B275" s="5" t="n">
+        <v>57.69</v>
+      </c>
+      <c r="C275" s="5" t="n">
+        <v>51.98</v>
+      </c>
+      <c r="D275" s="5" t="n">
+        <v>57.69</v>
+      </c>
+      <c r="E275" s="5" t="n">
+        <v>51.98</v>
       </c>
     </row>
   </sheetData>
-  <conditionalFormatting sqref="B2:B274">
+  <conditionalFormatting sqref="B2:B275">
     <cfRule type="colorScale" priority="1">
       <colorScale>
         <cfvo type="min"/>
@@ -11481,7 +11520,7 @@
       </colorScale>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="C2:C274">
+  <conditionalFormatting sqref="C2:C275">
     <cfRule type="colorScale" priority="2">
       <colorScale>
         <cfvo type="min"/>
@@ -11493,7 +11532,7 @@
       </colorScale>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="D2:D274">
+  <conditionalFormatting sqref="D2:D275">
     <cfRule type="colorScale" priority="3">
       <colorScale>
         <cfvo type="min"/>
@@ -11505,7 +11544,7 @@
       </colorScale>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="E2:E274">
+  <conditionalFormatting sqref="E2:E275">
     <cfRule type="colorScale" priority="4">
       <colorScale>
         <cfvo type="min"/>

--- a/outputs/QLD_historical_prices.xlsx
+++ b/outputs/QLD_historical_prices.xlsx
@@ -528,16 +528,16 @@
         </is>
       </c>
       <c r="B5" s="5" t="n">
-        <v>75.58</v>
+        <v>75.22</v>
       </c>
       <c r="C5" s="5" t="n">
-        <v>78.97</v>
+        <v>78.44</v>
       </c>
       <c r="D5" s="5" t="n">
-        <v>76.25</v>
+        <v>76.72</v>
       </c>
       <c r="E5" s="5" t="n">
-        <v>79.78</v>
+        <v>80.13</v>
       </c>
     </row>
     <row r="6">
@@ -547,16 +547,16 @@
         </is>
       </c>
       <c r="B6" s="5" t="n">
-        <v>90.51000000000001</v>
+        <v>90.33</v>
       </c>
       <c r="C6" s="5" t="n">
-        <v>98.5</v>
+        <v>98.23999999999999</v>
       </c>
       <c r="D6" s="5" t="n">
-        <v>92.73999999999999</v>
+        <v>93.73</v>
       </c>
       <c r="E6" s="5" t="n">
-        <v>101.03</v>
+        <v>102.05</v>
       </c>
     </row>
     <row r="7">
@@ -566,16 +566,16 @@
         </is>
       </c>
       <c r="B7" s="5" t="n">
-        <v>91.05</v>
+        <v>90.92</v>
       </c>
       <c r="C7" s="5" t="n">
-        <v>99.36</v>
+        <v>99.18000000000001</v>
       </c>
       <c r="D7" s="5" t="n">
-        <v>94.55</v>
+        <v>95.66</v>
       </c>
       <c r="E7" s="5" t="n">
-        <v>103.26</v>
+        <v>104.43</v>
       </c>
     </row>
     <row r="8">
@@ -585,16 +585,16 @@
         </is>
       </c>
       <c r="B8" s="5" t="n">
-        <v>117</v>
+        <v>116.93</v>
       </c>
       <c r="C8" s="5" t="n">
-        <v>136.84</v>
+        <v>136.73</v>
       </c>
       <c r="D8" s="5" t="n">
-        <v>128.67</v>
+        <v>130.32</v>
       </c>
       <c r="E8" s="5" t="n">
-        <v>151.38</v>
+        <v>153.31</v>
       </c>
     </row>
     <row r="9">
@@ -604,16 +604,16 @@
         </is>
       </c>
       <c r="B9" s="5" t="n">
-        <v>93.31</v>
+        <v>93.27</v>
       </c>
       <c r="C9" s="5" t="n">
-        <v>108.44</v>
+        <v>108.38</v>
       </c>
       <c r="D9" s="5" t="n">
-        <v>108.89</v>
+        <v>110.33</v>
       </c>
       <c r="E9" s="5" t="n">
-        <v>126.95</v>
+        <v>128.62</v>
       </c>
     </row>
     <row r="11">
@@ -690,10 +690,10 @@
         <v>72.18000000000001</v>
       </c>
       <c r="D2" s="5" t="n">
-        <v>80.26000000000001</v>
+        <v>81.36</v>
       </c>
       <c r="E2" s="5" t="n">
-        <v>132.32</v>
+        <v>134.14</v>
       </c>
       <c r="F2" s="7" t="inlineStr"/>
     </row>
@@ -710,10 +710,10 @@
         <v>18.84</v>
       </c>
       <c r="D3" s="5" t="n">
-        <v>30.94</v>
+        <v>31.37</v>
       </c>
       <c r="E3" s="5" t="n">
-        <v>34.47</v>
+        <v>34.95</v>
       </c>
       <c r="F3" s="7" t="inlineStr"/>
     </row>
@@ -730,10 +730,10 @@
         <v>18.7</v>
       </c>
       <c r="D4" s="5" t="n">
-        <v>29.31</v>
+        <v>29.72</v>
       </c>
       <c r="E4" s="5" t="n">
-        <v>34.15</v>
+        <v>34.62</v>
       </c>
       <c r="F4" s="7" t="inlineStr"/>
     </row>
@@ -750,10 +750,10 @@
         <v>16.84</v>
       </c>
       <c r="D5" s="5" t="n">
-        <v>27.15</v>
+        <v>27.52</v>
       </c>
       <c r="E5" s="5" t="n">
-        <v>30.7</v>
+        <v>31.12</v>
       </c>
       <c r="F5" s="7" t="inlineStr"/>
     </row>
@@ -770,10 +770,10 @@
         <v>19.15</v>
       </c>
       <c r="D6" s="5" t="n">
-        <v>37.75</v>
+        <v>38.26</v>
       </c>
       <c r="E6" s="5" t="n">
-        <v>34.85</v>
+        <v>35.33</v>
       </c>
       <c r="F6" s="7" t="inlineStr"/>
     </row>
@@ -790,10 +790,10 @@
         <v>28.76</v>
       </c>
       <c r="D7" s="5" t="n">
-        <v>41.17</v>
+        <v>41.73</v>
       </c>
       <c r="E7" s="5" t="n">
-        <v>52.25</v>
+        <v>52.97</v>
       </c>
       <c r="F7" s="7" t="inlineStr"/>
     </row>
@@ -810,10 +810,10 @@
         <v>26.73</v>
       </c>
       <c r="D8" s="5" t="n">
-        <v>41.79</v>
+        <v>42.36</v>
       </c>
       <c r="E8" s="5" t="n">
-        <v>48.42</v>
+        <v>49.08</v>
       </c>
       <c r="F8" s="7" t="inlineStr"/>
     </row>
@@ -830,10 +830,10 @@
         <v>47.14</v>
       </c>
       <c r="D9" s="5" t="n">
-        <v>73.47</v>
+        <v>74.48</v>
       </c>
       <c r="E9" s="5" t="n">
-        <v>85.14</v>
+        <v>86.31</v>
       </c>
       <c r="F9" s="7" t="inlineStr"/>
     </row>
@@ -850,10 +850,10 @@
         <v>101.08</v>
       </c>
       <c r="D10" s="5" t="n">
-        <v>100.59</v>
+        <v>101.97</v>
       </c>
       <c r="E10" s="5" t="n">
-        <v>182.02</v>
+        <v>184.52</v>
       </c>
       <c r="F10" s="7" t="inlineStr"/>
     </row>
@@ -870,10 +870,10 @@
         <v>34.66</v>
       </c>
       <c r="D11" s="5" t="n">
-        <v>50.79</v>
+        <v>51.49</v>
       </c>
       <c r="E11" s="5" t="n">
-        <v>62.32</v>
+        <v>63.17</v>
       </c>
       <c r="F11" s="7" t="inlineStr"/>
     </row>
@@ -890,10 +890,10 @@
         <v>33.41</v>
       </c>
       <c r="D12" s="5" t="n">
-        <v>51.88</v>
+        <v>52.59</v>
       </c>
       <c r="E12" s="5" t="n">
-        <v>59.98</v>
+        <v>60.8</v>
       </c>
       <c r="F12" s="7" t="inlineStr"/>
     </row>
@@ -910,10 +910,10 @@
         <v>27.84</v>
       </c>
       <c r="D13" s="5" t="n">
-        <v>47.52</v>
+        <v>48.17</v>
       </c>
       <c r="E13" s="5" t="n">
-        <v>49.9</v>
+        <v>50.59</v>
       </c>
       <c r="F13" s="7" t="inlineStr"/>
     </row>
@@ -930,10 +930,10 @@
         <v>25.42</v>
       </c>
       <c r="D14" s="5" t="n">
-        <v>45.05</v>
+        <v>45.67</v>
       </c>
       <c r="E14" s="5" t="n">
-        <v>45.5</v>
+        <v>46.13</v>
       </c>
       <c r="F14" s="7" t="inlineStr"/>
     </row>
@@ -950,10 +950,10 @@
         <v>29.72</v>
       </c>
       <c r="D15" s="5" t="n">
-        <v>43.85</v>
+        <v>44.45</v>
       </c>
       <c r="E15" s="5" t="n">
-        <v>53.12</v>
+        <v>53.86</v>
       </c>
       <c r="F15" s="7" t="inlineStr"/>
     </row>
@@ -970,10 +970,10 @@
         <v>32.97</v>
       </c>
       <c r="D16" s="5" t="n">
-        <v>49.36</v>
+        <v>50.04</v>
       </c>
       <c r="E16" s="5" t="n">
-        <v>58.85</v>
+        <v>59.66</v>
       </c>
       <c r="F16" s="7" t="inlineStr"/>
     </row>
@@ -990,10 +990,10 @@
         <v>82.45</v>
       </c>
       <c r="D17" s="5" t="n">
-        <v>91.13</v>
+        <v>92.38</v>
       </c>
       <c r="E17" s="5" t="n">
-        <v>146.8</v>
+        <v>148.82</v>
       </c>
       <c r="F17" s="7" t="inlineStr"/>
     </row>
@@ -1010,10 +1010,10 @@
         <v>77.28</v>
       </c>
       <c r="D18" s="5" t="n">
-        <v>90.43000000000001</v>
+        <v>91.68000000000001</v>
       </c>
       <c r="E18" s="5" t="n">
-        <v>137.25</v>
+        <v>139.14</v>
       </c>
       <c r="F18" s="7" t="inlineStr"/>
     </row>
@@ -1030,10 +1030,10 @@
         <v>41.3</v>
       </c>
       <c r="D19" s="5" t="n">
-        <v>56.07</v>
+        <v>56.84</v>
       </c>
       <c r="E19" s="5" t="n">
-        <v>73.16</v>
+        <v>74.17</v>
       </c>
       <c r="F19" s="7" t="inlineStr"/>
     </row>
@@ -1050,10 +1050,10 @@
         <v>27.18</v>
       </c>
       <c r="D20" s="5" t="n">
-        <v>40.44</v>
+        <v>41</v>
       </c>
       <c r="E20" s="5" t="n">
-        <v>48.04</v>
+        <v>48.7</v>
       </c>
       <c r="F20" s="7" t="inlineStr"/>
     </row>
@@ -1070,10 +1070,10 @@
         <v>48.21</v>
       </c>
       <c r="D21" s="5" t="n">
-        <v>54.72</v>
+        <v>55.48</v>
       </c>
       <c r="E21" s="5" t="n">
-        <v>85.02</v>
+        <v>86.19</v>
       </c>
       <c r="F21" s="7" t="inlineStr"/>
     </row>
@@ -1090,10 +1090,10 @@
         <v>18.12</v>
       </c>
       <c r="D22" s="5" t="n">
-        <v>29.18</v>
+        <v>29.58</v>
       </c>
       <c r="E22" s="5" t="n">
-        <v>31.89</v>
+        <v>32.32</v>
       </c>
       <c r="F22" s="7" t="inlineStr"/>
     </row>
@@ -1110,10 +1110,10 @@
         <v>29.03</v>
       </c>
       <c r="D23" s="5" t="n">
-        <v>41.74</v>
+        <v>42.32</v>
       </c>
       <c r="E23" s="5" t="n">
-        <v>50.98</v>
+        <v>51.68</v>
       </c>
       <c r="F23" s="7" t="inlineStr"/>
     </row>
@@ -1130,10 +1130,10 @@
         <v>23.51</v>
       </c>
       <c r="D24" s="5" t="n">
-        <v>36.6</v>
+        <v>37.1</v>
       </c>
       <c r="E24" s="5" t="n">
-        <v>41.21</v>
+        <v>41.77</v>
       </c>
       <c r="F24" s="7" t="inlineStr"/>
     </row>
@@ -1150,10 +1150,10 @@
         <v>25.47</v>
       </c>
       <c r="D25" s="5" t="n">
-        <v>37.96</v>
+        <v>38.48</v>
       </c>
       <c r="E25" s="5" t="n">
-        <v>44.55</v>
+        <v>45.17</v>
       </c>
       <c r="F25" s="7" t="inlineStr"/>
     </row>
@@ -1170,10 +1170,10 @@
         <v>20.87</v>
       </c>
       <c r="D26" s="5" t="n">
-        <v>32.34</v>
+        <v>32.79</v>
       </c>
       <c r="E26" s="5" t="n">
-        <v>36.39</v>
+        <v>36.89</v>
       </c>
       <c r="F26" s="7" t="inlineStr"/>
     </row>
@@ -1190,10 +1190,10 @@
         <v>24.32</v>
       </c>
       <c r="D27" s="5" t="n">
-        <v>35.33</v>
+        <v>35.81</v>
       </c>
       <c r="E27" s="5" t="n">
-        <v>42.26</v>
+        <v>42.84</v>
       </c>
       <c r="F27" s="7" t="inlineStr"/>
     </row>
@@ -1210,10 +1210,10 @@
         <v>30.66</v>
       </c>
       <c r="D28" s="5" t="n">
-        <v>41.55</v>
+        <v>42.12</v>
       </c>
       <c r="E28" s="5" t="n">
-        <v>53.1</v>
+        <v>53.83</v>
       </c>
       <c r="F28" s="7" t="inlineStr"/>
     </row>
@@ -1230,10 +1230,10 @@
         <v>36.89</v>
       </c>
       <c r="D29" s="5" t="n">
-        <v>43.85</v>
+        <v>44.45</v>
       </c>
       <c r="E29" s="5" t="n">
-        <v>63.78</v>
+        <v>64.66</v>
       </c>
       <c r="F29" s="7" t="inlineStr"/>
     </row>
@@ -1250,10 +1250,10 @@
         <v>24.68</v>
       </c>
       <c r="D30" s="5" t="n">
-        <v>34.25</v>
+        <v>34.72</v>
       </c>
       <c r="E30" s="5" t="n">
-        <v>42.6</v>
+        <v>43.19</v>
       </c>
       <c r="F30" s="7" t="inlineStr"/>
     </row>
@@ -1270,10 +1270,10 @@
         <v>103.94</v>
       </c>
       <c r="D31" s="5" t="n">
-        <v>98.73</v>
+        <v>100.09</v>
       </c>
       <c r="E31" s="5" t="n">
-        <v>179.1</v>
+        <v>181.56</v>
       </c>
       <c r="F31" s="7" t="inlineStr"/>
     </row>
@@ -1290,10 +1290,10 @@
         <v>45.52</v>
       </c>
       <c r="D32" s="5" t="n">
-        <v>51.27</v>
+        <v>51.98</v>
       </c>
       <c r="E32" s="5" t="n">
-        <v>78.20999999999999</v>
+        <v>79.29000000000001</v>
       </c>
       <c r="F32" s="7" t="inlineStr"/>
     </row>
@@ -1310,10 +1310,10 @@
         <v>97.20999999999999</v>
       </c>
       <c r="D33" s="5" t="n">
-        <v>93.09999999999999</v>
+        <v>94.38</v>
       </c>
       <c r="E33" s="5" t="n">
-        <v>166.55</v>
+        <v>168.84</v>
       </c>
       <c r="F33" s="7" t="inlineStr"/>
     </row>
@@ -1330,10 +1330,10 @@
         <v>24.22</v>
       </c>
       <c r="D34" s="5" t="n">
-        <v>33.61</v>
+        <v>34.07</v>
       </c>
       <c r="E34" s="5" t="n">
-        <v>41.38</v>
+        <v>41.95</v>
       </c>
       <c r="F34" s="7" t="inlineStr"/>
     </row>
@@ -1350,10 +1350,10 @@
         <v>30.02</v>
       </c>
       <c r="D35" s="5" t="n">
-        <v>36.76</v>
+        <v>37.27</v>
       </c>
       <c r="E35" s="5" t="n">
-        <v>51.02</v>
+        <v>51.72</v>
       </c>
       <c r="F35" s="7" t="inlineStr"/>
     </row>
@@ -1370,10 +1370,10 @@
         <v>29.88</v>
       </c>
       <c r="D36" s="5" t="n">
-        <v>39.17</v>
+        <v>39.71</v>
       </c>
       <c r="E36" s="5" t="n">
-        <v>50.52</v>
+        <v>51.21</v>
       </c>
       <c r="F36" s="7" t="inlineStr"/>
     </row>
@@ -1390,10 +1390,10 @@
         <v>30.41</v>
       </c>
       <c r="D37" s="5" t="n">
-        <v>42.47</v>
+        <v>43.05</v>
       </c>
       <c r="E37" s="5" t="n">
-        <v>51.14</v>
+        <v>51.85</v>
       </c>
       <c r="F37" s="7" t="inlineStr"/>
     </row>
@@ -1410,10 +1410,10 @@
         <v>42.03</v>
       </c>
       <c r="D38" s="5" t="n">
-        <v>49.5</v>
+        <v>50.18</v>
       </c>
       <c r="E38" s="5" t="n">
-        <v>70.48</v>
+        <v>71.45</v>
       </c>
       <c r="F38" s="7" t="inlineStr"/>
     </row>
@@ -1430,10 +1430,10 @@
         <v>29.73</v>
       </c>
       <c r="D39" s="5" t="n">
-        <v>41.11</v>
+        <v>41.68</v>
       </c>
       <c r="E39" s="5" t="n">
-        <v>49.71</v>
+        <v>50.39</v>
       </c>
       <c r="F39" s="7" t="inlineStr"/>
     </row>
@@ -1450,10 +1450,10 @@
         <v>22.14</v>
       </c>
       <c r="D40" s="5" t="n">
-        <v>32.64</v>
+        <v>33.09</v>
       </c>
       <c r="E40" s="5" t="n">
-        <v>36.91</v>
+        <v>37.42</v>
       </c>
       <c r="F40" s="7" t="inlineStr"/>
     </row>
@@ -1470,10 +1470,10 @@
         <v>23.84</v>
       </c>
       <c r="D41" s="5" t="n">
-        <v>33.97</v>
+        <v>34.44</v>
       </c>
       <c r="E41" s="5" t="n">
-        <v>39.76</v>
+        <v>40.3</v>
       </c>
       <c r="F41" s="7" t="inlineStr"/>
     </row>
@@ -1490,10 +1490,10 @@
         <v>33.69</v>
       </c>
       <c r="D42" s="5" t="n">
-        <v>43.59</v>
+        <v>44.19</v>
       </c>
       <c r="E42" s="5" t="n">
-        <v>56.2</v>
+        <v>56.98</v>
       </c>
       <c r="F42" s="7" t="inlineStr"/>
     </row>
@@ -1510,10 +1510,10 @@
         <v>25.24</v>
       </c>
       <c r="D43" s="5" t="n">
-        <v>33.36</v>
+        <v>33.82</v>
       </c>
       <c r="E43" s="5" t="n">
-        <v>42.12</v>
+        <v>42.7</v>
       </c>
       <c r="F43" s="7" t="inlineStr"/>
     </row>
@@ -1530,10 +1530,10 @@
         <v>129.47</v>
       </c>
       <c r="D44" s="5" t="n">
-        <v>122.93</v>
+        <v>124.62</v>
       </c>
       <c r="E44" s="5" t="n">
-        <v>216.02</v>
+        <v>218.99</v>
       </c>
       <c r="F44" s="7" t="inlineStr"/>
     </row>
@@ -1550,10 +1550,10 @@
         <v>53.02</v>
       </c>
       <c r="D45" s="5" t="n">
-        <v>62.68</v>
+        <v>63.55</v>
       </c>
       <c r="E45" s="5" t="n">
-        <v>88.44</v>
+        <v>89.65000000000001</v>
       </c>
       <c r="F45" s="7" t="inlineStr"/>
     </row>
@@ -1570,10 +1570,10 @@
         <v>62.97</v>
       </c>
       <c r="D46" s="5" t="n">
-        <v>79.33</v>
+        <v>80.42</v>
       </c>
       <c r="E46" s="5" t="n">
-        <v>105.01</v>
+        <v>106.45</v>
       </c>
       <c r="F46" s="7" t="inlineStr"/>
     </row>
@@ -1590,10 +1590,10 @@
         <v>98.91</v>
       </c>
       <c r="D47" s="5" t="n">
-        <v>124.74</v>
+        <v>126.45</v>
       </c>
       <c r="E47" s="5" t="n">
-        <v>164.26</v>
+        <v>166.52</v>
       </c>
       <c r="F47" s="7" t="inlineStr"/>
     </row>
@@ -1610,10 +1610,10 @@
         <v>72.97</v>
       </c>
       <c r="D48" s="5" t="n">
-        <v>101.03</v>
+        <v>102.42</v>
       </c>
       <c r="E48" s="5" t="n">
-        <v>120.69</v>
+        <v>122.35</v>
       </c>
       <c r="F48" s="7" t="inlineStr"/>
     </row>
@@ -1630,10 +1630,10 @@
         <v>321.63</v>
       </c>
       <c r="D49" s="5" t="n">
-        <v>317.02</v>
+        <v>321.38</v>
       </c>
       <c r="E49" s="5" t="n">
-        <v>529.8200000000001</v>
+        <v>537.11</v>
       </c>
       <c r="F49" s="7" t="inlineStr"/>
     </row>
@@ -1650,10 +1650,10 @@
         <v>94.81</v>
       </c>
       <c r="D50" s="5" t="n">
-        <v>116.48</v>
+        <v>118.08</v>
       </c>
       <c r="E50" s="5" t="n">
-        <v>155.82</v>
+        <v>157.96</v>
       </c>
       <c r="F50" s="7" t="inlineStr"/>
     </row>
@@ -1670,10 +1670,10 @@
         <v>44.82</v>
       </c>
       <c r="D51" s="5" t="n">
-        <v>62.29</v>
+        <v>63.15</v>
       </c>
       <c r="E51" s="5" t="n">
-        <v>73.48999999999999</v>
+        <v>74.5</v>
       </c>
       <c r="F51" s="7" t="inlineStr"/>
     </row>
@@ -1690,10 +1690,10 @@
         <v>68.55</v>
       </c>
       <c r="D52" s="5" t="n">
-        <v>83.67</v>
+        <v>84.81999999999999</v>
       </c>
       <c r="E52" s="5" t="n">
-        <v>112.15</v>
+        <v>113.69</v>
       </c>
       <c r="F52" s="7" t="inlineStr"/>
     </row>
@@ -1710,10 +1710,10 @@
         <v>97.91</v>
       </c>
       <c r="D53" s="5" t="n">
-        <v>102.36</v>
+        <v>103.77</v>
       </c>
       <c r="E53" s="5" t="n">
-        <v>159.69</v>
+        <v>161.88</v>
       </c>
       <c r="F53" s="7" t="inlineStr"/>
     </row>
@@ -1730,10 +1730,10 @@
         <v>50.94</v>
       </c>
       <c r="D54" s="5" t="n">
-        <v>89</v>
+        <v>90.23</v>
       </c>
       <c r="E54" s="5" t="n">
-        <v>82.81999999999999</v>
+        <v>83.95999999999999</v>
       </c>
       <c r="F54" s="7" t="inlineStr"/>
     </row>
@@ -1750,10 +1750,10 @@
         <v>57.6</v>
       </c>
       <c r="D55" s="5" t="n">
-        <v>61.11</v>
+        <v>61.95</v>
       </c>
       <c r="E55" s="5" t="n">
-        <v>93.37</v>
+        <v>94.65000000000001</v>
       </c>
       <c r="F55" s="7" t="inlineStr"/>
     </row>
@@ -1770,10 +1770,10 @@
         <v>75.11</v>
       </c>
       <c r="D56" s="5" t="n">
-        <v>76.59999999999999</v>
+        <v>77.66</v>
       </c>
       <c r="E56" s="5" t="n">
-        <v>121.21</v>
+        <v>122.87</v>
       </c>
       <c r="F56" s="7" t="inlineStr"/>
     </row>
@@ -1790,10 +1790,10 @@
         <v>163.94</v>
       </c>
       <c r="D57" s="5" t="n">
-        <v>210.64</v>
+        <v>213.54</v>
       </c>
       <c r="E57" s="5" t="n">
-        <v>263.38</v>
+        <v>267.01</v>
       </c>
       <c r="F57" s="7" t="inlineStr"/>
     </row>
@@ -1810,10 +1810,10 @@
         <v>40.15</v>
       </c>
       <c r="D58" s="5" t="n">
-        <v>46.87</v>
+        <v>47.51</v>
       </c>
       <c r="E58" s="5" t="n">
-        <v>64.22</v>
+        <v>65.09999999999999</v>
       </c>
       <c r="F58" s="7" t="inlineStr"/>
     </row>
@@ -1830,10 +1830,10 @@
         <v>34.99</v>
       </c>
       <c r="D59" s="5" t="n">
-        <v>45.33</v>
+        <v>45.96</v>
       </c>
       <c r="E59" s="5" t="n">
-        <v>55.7</v>
+        <v>56.46</v>
       </c>
       <c r="F59" s="7" t="inlineStr"/>
     </row>
@@ -1850,10 +1850,10 @@
         <v>46.42</v>
       </c>
       <c r="D60" s="5" t="n">
-        <v>62.38</v>
+        <v>63.24</v>
       </c>
       <c r="E60" s="5" t="n">
-        <v>73.54000000000001</v>
+        <v>74.55</v>
       </c>
       <c r="F60" s="7" t="inlineStr"/>
     </row>
@@ -1870,10 +1870,10 @@
         <v>51.37</v>
       </c>
       <c r="D61" s="5" t="n">
-        <v>64.84999999999999</v>
+        <v>65.73999999999999</v>
       </c>
       <c r="E61" s="5" t="n">
-        <v>80.98999999999999</v>
+        <v>82.09999999999999</v>
       </c>
       <c r="F61" s="7" t="inlineStr"/>
     </row>
@@ -1890,10 +1890,10 @@
         <v>50.74</v>
       </c>
       <c r="D62" s="5" t="n">
-        <v>57.1</v>
+        <v>57.89</v>
       </c>
       <c r="E62" s="5" t="n">
-        <v>79.69</v>
+        <v>80.78</v>
       </c>
       <c r="F62" s="7" t="inlineStr"/>
     </row>
@@ -1910,10 +1910,10 @@
         <v>43.69</v>
       </c>
       <c r="D63" s="5" t="n">
-        <v>56.02</v>
+        <v>56.79</v>
       </c>
       <c r="E63" s="5" t="n">
-        <v>68.34999999999999</v>
+        <v>69.29000000000001</v>
       </c>
       <c r="F63" s="7" t="inlineStr"/>
     </row>
@@ -1930,10 +1930,10 @@
         <v>37.24</v>
       </c>
       <c r="D64" s="5" t="n">
-        <v>48.14</v>
+        <v>48.8</v>
       </c>
       <c r="E64" s="5" t="n">
-        <v>58.04</v>
+        <v>58.84</v>
       </c>
       <c r="F64" s="7" t="inlineStr"/>
     </row>
@@ -1950,10 +1950,10 @@
         <v>57.1</v>
       </c>
       <c r="D65" s="5" t="n">
-        <v>62.58</v>
+        <v>63.44</v>
       </c>
       <c r="E65" s="5" t="n">
-        <v>89.09</v>
+        <v>90.31</v>
       </c>
       <c r="F65" s="7" t="inlineStr"/>
     </row>
@@ -1970,10 +1970,10 @@
         <v>53.97</v>
       </c>
       <c r="D66" s="5" t="n">
-        <v>58.4</v>
+        <v>59.2</v>
       </c>
       <c r="E66" s="5" t="n">
-        <v>84.3</v>
+        <v>85.45</v>
       </c>
       <c r="F66" s="7" t="inlineStr"/>
     </row>
@@ -1990,10 +1990,10 @@
         <v>46.2</v>
       </c>
       <c r="D67" s="5" t="n">
-        <v>52.3</v>
+        <v>53.02</v>
       </c>
       <c r="E67" s="5" t="n">
-        <v>72.23999999999999</v>
+        <v>73.23</v>
       </c>
       <c r="F67" s="7" t="inlineStr"/>
     </row>
@@ -2010,10 +2010,10 @@
         <v>58.59</v>
       </c>
       <c r="D68" s="5" t="n">
-        <v>62.96</v>
+        <v>63.82</v>
       </c>
       <c r="E68" s="5" t="n">
-        <v>91.58</v>
+        <v>92.84</v>
       </c>
       <c r="F68" s="7" t="inlineStr"/>
     </row>
@@ -2030,10 +2030,10 @@
         <v>52.64</v>
       </c>
       <c r="D69" s="5" t="n">
-        <v>59.61</v>
+        <v>60.43</v>
       </c>
       <c r="E69" s="5" t="n">
-        <v>82.25</v>
+        <v>83.38</v>
       </c>
       <c r="F69" s="7" t="inlineStr"/>
     </row>
@@ -2050,10 +2050,10 @@
         <v>32.61</v>
       </c>
       <c r="D70" s="5" t="n">
-        <v>40.16</v>
+        <v>40.71</v>
       </c>
       <c r="E70" s="5" t="n">
-        <v>50.93</v>
+        <v>51.63</v>
       </c>
       <c r="F70" s="7" t="inlineStr"/>
     </row>
@@ -2070,10 +2070,10 @@
         <v>40.78</v>
       </c>
       <c r="D71" s="5" t="n">
-        <v>50.07</v>
+        <v>50.76</v>
       </c>
       <c r="E71" s="5" t="n">
-        <v>63.59</v>
+        <v>64.45999999999999</v>
       </c>
       <c r="F71" s="7" t="inlineStr"/>
     </row>
@@ -2090,10 +2090,10 @@
         <v>32.17</v>
       </c>
       <c r="D72" s="5" t="n">
-        <v>42.39</v>
+        <v>42.97</v>
       </c>
       <c r="E72" s="5" t="n">
-        <v>50.08</v>
+        <v>50.77</v>
       </c>
       <c r="F72" s="7" t="inlineStr"/>
     </row>
@@ -2110,10 +2110,10 @@
         <v>41.23</v>
       </c>
       <c r="D73" s="5" t="n">
-        <v>47.81</v>
+        <v>48.46</v>
       </c>
       <c r="E73" s="5" t="n">
-        <v>64.08</v>
+        <v>64.95999999999999</v>
       </c>
       <c r="F73" s="7" t="inlineStr"/>
     </row>
@@ -2130,10 +2130,10 @@
         <v>33.09</v>
       </c>
       <c r="D74" s="5" t="n">
-        <v>42.43</v>
+        <v>43.02</v>
       </c>
       <c r="E74" s="5" t="n">
-        <v>51.27</v>
+        <v>51.97</v>
       </c>
       <c r="F74" s="7" t="inlineStr"/>
     </row>
@@ -2150,10 +2150,10 @@
         <v>26.93</v>
       </c>
       <c r="D75" s="5" t="n">
-        <v>35.81</v>
+        <v>36.31</v>
       </c>
       <c r="E75" s="5" t="n">
-        <v>41.59</v>
+        <v>42.16</v>
       </c>
       <c r="F75" s="7" t="inlineStr"/>
     </row>
@@ -2170,10 +2170,10 @@
         <v>27.31</v>
       </c>
       <c r="D76" s="5" t="n">
-        <v>37.78</v>
+        <v>38.3</v>
       </c>
       <c r="E76" s="5" t="n">
-        <v>42.05</v>
+        <v>42.62</v>
       </c>
       <c r="F76" s="7" t="inlineStr"/>
     </row>
@@ -2190,10 +2190,10 @@
         <v>31.56</v>
       </c>
       <c r="D77" s="5" t="n">
-        <v>40.47</v>
+        <v>41.02</v>
       </c>
       <c r="E77" s="5" t="n">
-        <v>48.5</v>
+        <v>49.17</v>
       </c>
       <c r="F77" s="7" t="inlineStr"/>
     </row>
@@ -2210,10 +2210,10 @@
         <v>158.57</v>
       </c>
       <c r="D78" s="5" t="n">
-        <v>129.54</v>
+        <v>131.32</v>
       </c>
       <c r="E78" s="5" t="n">
-        <v>243.26</v>
+        <v>246.61</v>
       </c>
       <c r="F78" s="7" t="inlineStr"/>
     </row>
@@ -2230,10 +2230,10 @@
         <v>44.59</v>
       </c>
       <c r="D79" s="5" t="n">
-        <v>47.32</v>
+        <v>47.97</v>
       </c>
       <c r="E79" s="5" t="n">
-        <v>68.28</v>
+        <v>69.22</v>
       </c>
       <c r="F79" s="7" t="inlineStr"/>
     </row>
@@ -2250,10 +2250,10 @@
         <v>101.15</v>
       </c>
       <c r="D80" s="5" t="n">
-        <v>84.97</v>
+        <v>86.14</v>
       </c>
       <c r="E80" s="5" t="n">
-        <v>154.42</v>
+        <v>156.54</v>
       </c>
       <c r="F80" s="7" t="inlineStr"/>
     </row>
@@ -2270,10 +2270,10 @@
         <v>63.4</v>
       </c>
       <c r="D81" s="5" t="n">
-        <v>59.98</v>
+        <v>60.8</v>
       </c>
       <c r="E81" s="5" t="n">
-        <v>96.48999999999999</v>
+        <v>97.81999999999999</v>
       </c>
       <c r="F81" s="7" t="inlineStr"/>
     </row>
@@ -2290,10 +2290,10 @@
         <v>30.36</v>
       </c>
       <c r="D82" s="5" t="n">
-        <v>36.72</v>
+        <v>37.22</v>
       </c>
       <c r="E82" s="5" t="n">
-        <v>46.06</v>
+        <v>46.7</v>
       </c>
       <c r="F82" s="7" t="inlineStr"/>
     </row>
@@ -2310,10 +2310,10 @@
         <v>22.61</v>
       </c>
       <c r="D83" s="5" t="n">
-        <v>32.16</v>
+        <v>32.6</v>
       </c>
       <c r="E83" s="5" t="n">
-        <v>34.24</v>
+        <v>34.71</v>
       </c>
       <c r="F83" s="7" t="inlineStr"/>
     </row>
@@ -2330,10 +2330,10 @@
         <v>24.98</v>
       </c>
       <c r="D84" s="5" t="n">
-        <v>31.67</v>
+        <v>32.11</v>
       </c>
       <c r="E84" s="5" t="n">
-        <v>37.75</v>
+        <v>38.27</v>
       </c>
       <c r="F84" s="7" t="inlineStr"/>
     </row>
@@ -2350,10 +2350,10 @@
         <v>25.37</v>
       </c>
       <c r="D85" s="5" t="n">
-        <v>33.98</v>
+        <v>34.45</v>
       </c>
       <c r="E85" s="5" t="n">
-        <v>38.26</v>
+        <v>38.79</v>
       </c>
       <c r="F85" s="7" t="inlineStr"/>
     </row>
@@ -2370,10 +2370,10 @@
         <v>24.17</v>
       </c>
       <c r="D86" s="5" t="n">
-        <v>31.49</v>
+        <v>31.92</v>
       </c>
       <c r="E86" s="5" t="n">
-        <v>36.36</v>
+        <v>36.86</v>
       </c>
       <c r="F86" s="7" t="inlineStr"/>
     </row>
@@ -2390,10 +2390,10 @@
         <v>22.64</v>
       </c>
       <c r="D87" s="5" t="n">
-        <v>31.88</v>
+        <v>32.32</v>
       </c>
       <c r="E87" s="5" t="n">
-        <v>33.98</v>
+        <v>34.45</v>
       </c>
       <c r="F87" s="7" t="inlineStr"/>
     </row>
@@ -2410,10 +2410,10 @@
         <v>23.3</v>
       </c>
       <c r="D88" s="5" t="n">
-        <v>31.74</v>
+        <v>32.18</v>
       </c>
       <c r="E88" s="5" t="n">
-        <v>34.89</v>
+        <v>35.37</v>
       </c>
       <c r="F88" s="7" t="inlineStr"/>
     </row>
@@ -2430,10 +2430,10 @@
         <v>22.29</v>
       </c>
       <c r="D89" s="5" t="n">
-        <v>29.91</v>
+        <v>30.32</v>
       </c>
       <c r="E89" s="5" t="n">
-        <v>33.33</v>
+        <v>33.79</v>
       </c>
       <c r="F89" s="7" t="inlineStr"/>
     </row>
@@ -2450,10 +2450,10 @@
         <v>20.14</v>
       </c>
       <c r="D90" s="5" t="n">
-        <v>26.34</v>
+        <v>26.71</v>
       </c>
       <c r="E90" s="5" t="n">
-        <v>30.08</v>
+        <v>30.49</v>
       </c>
       <c r="F90" s="7" t="inlineStr"/>
     </row>
@@ -2470,10 +2470,10 @@
         <v>26.94</v>
       </c>
       <c r="D91" s="5" t="n">
-        <v>32.93</v>
+        <v>33.39</v>
       </c>
       <c r="E91" s="5" t="n">
-        <v>40.18</v>
+        <v>40.73</v>
       </c>
       <c r="F91" s="7" t="inlineStr"/>
     </row>
@@ -2490,10 +2490,10 @@
         <v>68.84</v>
       </c>
       <c r="D92" s="5" t="n">
-        <v>64.81999999999999</v>
+        <v>65.70999999999999</v>
       </c>
       <c r="E92" s="5" t="n">
-        <v>102.15</v>
+        <v>103.56</v>
       </c>
       <c r="F92" s="7" t="inlineStr"/>
     </row>
@@ -2510,10 +2510,10 @@
         <v>196.36</v>
       </c>
       <c r="D93" s="5" t="n">
-        <v>155.99</v>
+        <v>158.13</v>
       </c>
       <c r="E93" s="5" t="n">
-        <v>289.89</v>
+        <v>293.88</v>
       </c>
       <c r="F93" s="7" t="inlineStr"/>
     </row>
@@ -2530,10 +2530,10 @@
         <v>31.68</v>
       </c>
       <c r="D94" s="5" t="n">
-        <v>40.29</v>
+        <v>40.84</v>
       </c>
       <c r="E94" s="5" t="n">
-        <v>46.53</v>
+        <v>47.17</v>
       </c>
       <c r="F94" s="7" t="inlineStr"/>
     </row>
@@ -2550,10 +2550,10 @@
         <v>26.61</v>
       </c>
       <c r="D95" s="5" t="n">
-        <v>36.65</v>
+        <v>37.16</v>
       </c>
       <c r="E95" s="5" t="n">
-        <v>38.97</v>
+        <v>39.5</v>
       </c>
       <c r="F95" s="7" t="inlineStr"/>
     </row>
@@ -2570,10 +2570,10 @@
         <v>29.09</v>
       </c>
       <c r="D96" s="5" t="n">
-        <v>40.13</v>
+        <v>40.68</v>
       </c>
       <c r="E96" s="5" t="n">
-        <v>42.47</v>
+        <v>43.05</v>
       </c>
       <c r="F96" s="7" t="inlineStr"/>
     </row>
@@ -2590,10 +2590,10 @@
         <v>28.39</v>
       </c>
       <c r="D97" s="5" t="n">
-        <v>36.85</v>
+        <v>37.36</v>
       </c>
       <c r="E97" s="5" t="n">
-        <v>41.32</v>
+        <v>41.89</v>
       </c>
       <c r="F97" s="7" t="inlineStr"/>
     </row>
@@ -2610,10 +2610,10 @@
         <v>30.87</v>
       </c>
       <c r="D98" s="5" t="n">
-        <v>38.43</v>
+        <v>38.96</v>
       </c>
       <c r="E98" s="5" t="n">
-        <v>44.84</v>
+        <v>45.46</v>
       </c>
       <c r="F98" s="7" t="inlineStr"/>
     </row>
@@ -2630,10 +2630,10 @@
         <v>32.03</v>
       </c>
       <c r="D99" s="5" t="n">
-        <v>41.88</v>
+        <v>42.46</v>
       </c>
       <c r="E99" s="5" t="n">
-        <v>46.43</v>
+        <v>47.07</v>
       </c>
       <c r="F99" s="7" t="inlineStr"/>
     </row>
@@ -2650,10 +2650,10 @@
         <v>33.77</v>
       </c>
       <c r="D100" s="5" t="n">
-        <v>41.75</v>
+        <v>42.33</v>
       </c>
       <c r="E100" s="5" t="n">
-        <v>48.86</v>
+        <v>49.53</v>
       </c>
       <c r="F100" s="7" t="inlineStr"/>
     </row>
@@ -2670,10 +2670,10 @@
         <v>30.07</v>
       </c>
       <c r="D101" s="5" t="n">
-        <v>39.5</v>
+        <v>40.04</v>
       </c>
       <c r="E101" s="5" t="n">
-        <v>43.5</v>
+        <v>44.1</v>
       </c>
       <c r="F101" s="7" t="inlineStr"/>
     </row>
@@ -2690,10 +2690,10 @@
         <v>42.54</v>
       </c>
       <c r="D102" s="5" t="n">
-        <v>48.54</v>
+        <v>49.21</v>
       </c>
       <c r="E102" s="5" t="n">
-        <v>61.55</v>
+        <v>62.39</v>
       </c>
       <c r="F102" s="7" t="inlineStr"/>
     </row>
@@ -2710,10 +2710,10 @@
         <v>28.15</v>
       </c>
       <c r="D103" s="5" t="n">
-        <v>36.99</v>
+        <v>37.5</v>
       </c>
       <c r="E103" s="5" t="n">
-        <v>40.73</v>
+        <v>41.29</v>
       </c>
       <c r="F103" s="7" t="inlineStr"/>
     </row>
@@ -2730,10 +2730,10 @@
         <v>41.84</v>
       </c>
       <c r="D104" s="5" t="n">
-        <v>46.61</v>
+        <v>47.25</v>
       </c>
       <c r="E104" s="5" t="n">
-        <v>60.52</v>
+        <v>61.35</v>
       </c>
       <c r="F104" s="7" t="inlineStr"/>
     </row>
@@ -2750,10 +2750,10 @@
         <v>37.94</v>
       </c>
       <c r="D105" s="5" t="n">
-        <v>43.46</v>
+        <v>44.06</v>
       </c>
       <c r="E105" s="5" t="n">
-        <v>54.87</v>
+        <v>55.62</v>
       </c>
       <c r="F105" s="7" t="inlineStr"/>
     </row>
@@ -2770,10 +2770,10 @@
         <v>31.14</v>
       </c>
       <c r="D106" s="5" t="n">
-        <v>39.32</v>
+        <v>39.86</v>
       </c>
       <c r="E106" s="5" t="n">
-        <v>45.03</v>
+        <v>45.65</v>
       </c>
       <c r="F106" s="7" t="inlineStr"/>
     </row>
@@ -2790,10 +2790,10 @@
         <v>32.17</v>
       </c>
       <c r="D107" s="5" t="n">
-        <v>42.15</v>
+        <v>42.73</v>
       </c>
       <c r="E107" s="5" t="n">
-        <v>46.44</v>
+        <v>47.07</v>
       </c>
       <c r="F107" s="7" t="inlineStr"/>
     </row>
@@ -2810,10 +2810,10 @@
         <v>27.95</v>
       </c>
       <c r="D108" s="5" t="n">
-        <v>36.95</v>
+        <v>37.45</v>
       </c>
       <c r="E108" s="5" t="n">
-        <v>40.27</v>
+        <v>40.83</v>
       </c>
       <c r="F108" s="7" t="inlineStr"/>
     </row>
@@ -2830,10 +2830,10 @@
         <v>39.25</v>
       </c>
       <c r="D109" s="5" t="n">
-        <v>49.34</v>
+        <v>50.02</v>
       </c>
       <c r="E109" s="5" t="n">
-        <v>56.46</v>
+        <v>57.24</v>
       </c>
       <c r="F109" s="7" t="inlineStr"/>
     </row>
@@ -2850,10 +2850,10 @@
         <v>71.37</v>
       </c>
       <c r="D110" s="9" t="n">
-        <v>91.02</v>
+        <v>92.27</v>
       </c>
       <c r="E110" s="9" t="n">
-        <v>102.2</v>
+        <v>103.61</v>
       </c>
       <c r="F110" s="10" t="inlineStr">
         <is>
@@ -2874,10 +2874,10 @@
         <v>58.94</v>
       </c>
       <c r="D111" s="9" t="n">
-        <v>76.58</v>
+        <v>77.63</v>
       </c>
       <c r="E111" s="9" t="n">
-        <v>84.02</v>
+        <v>85.18000000000001</v>
       </c>
       <c r="F111" s="10" t="inlineStr">
         <is>
@@ -2898,10 +2898,10 @@
         <v>56.11</v>
       </c>
       <c r="D112" s="9" t="n">
-        <v>74.72</v>
+        <v>75.75</v>
       </c>
       <c r="E112" s="9" t="n">
-        <v>79.63</v>
+        <v>80.72</v>
       </c>
       <c r="F112" s="10" t="inlineStr">
         <is>
@@ -2922,10 +2922,10 @@
         <v>54.75</v>
       </c>
       <c r="D113" s="9" t="n">
-        <v>74.45999999999999</v>
+        <v>75.48</v>
       </c>
       <c r="E113" s="9" t="n">
-        <v>77.63</v>
+        <v>78.7</v>
       </c>
       <c r="F113" s="10" t="inlineStr">
         <is>
@@ -2946,10 +2946,10 @@
         <v>60.67</v>
       </c>
       <c r="D114" s="9" t="n">
-        <v>76.79000000000001</v>
+        <v>77.84</v>
       </c>
       <c r="E114" s="9" t="n">
-        <v>85.95</v>
+        <v>87.14</v>
       </c>
       <c r="F114" s="10" t="inlineStr">
         <is>
@@ -2970,10 +2970,10 @@
         <v>73.14</v>
       </c>
       <c r="D115" s="9" t="n">
-        <v>83.73</v>
+        <v>84.88</v>
       </c>
       <c r="E115" s="9" t="n">
-        <v>103.53</v>
+        <v>104.96</v>
       </c>
       <c r="F115" s="10" t="inlineStr">
         <is>
@@ -2994,10 +2994,10 @@
         <v>178.66</v>
       </c>
       <c r="D116" s="9" t="n">
-        <v>220.44</v>
+        <v>223.47</v>
       </c>
       <c r="E116" s="9" t="n">
-        <v>252.62</v>
+        <v>256.09</v>
       </c>
       <c r="F116" s="10" t="inlineStr">
         <is>
@@ -3018,10 +3018,10 @@
         <v>69.16</v>
       </c>
       <c r="D117" s="9" t="n">
-        <v>83.12</v>
+        <v>84.26000000000001</v>
       </c>
       <c r="E117" s="9" t="n">
-        <v>97.68000000000001</v>
+        <v>99.02</v>
       </c>
       <c r="F117" s="10" t="inlineStr">
         <is>
@@ -3042,10 +3042,10 @@
         <v>80.01000000000001</v>
       </c>
       <c r="D118" s="9" t="n">
-        <v>104.11</v>
+        <v>105.55</v>
       </c>
       <c r="E118" s="9" t="n">
-        <v>112.88</v>
+        <v>114.43</v>
       </c>
       <c r="F118" s="10" t="inlineStr">
         <is>
@@ -3066,10 +3066,10 @@
         <v>60.49</v>
       </c>
       <c r="D119" s="9" t="n">
-        <v>78.06</v>
+        <v>79.13</v>
       </c>
       <c r="E119" s="9" t="n">
-        <v>85.23</v>
+        <v>86.40000000000001</v>
       </c>
       <c r="F119" s="10" t="inlineStr">
         <is>
@@ -3090,10 +3090,10 @@
         <v>65.18000000000001</v>
       </c>
       <c r="D120" s="9" t="n">
-        <v>81.45999999999999</v>
+        <v>82.58</v>
       </c>
       <c r="E120" s="9" t="n">
-        <v>91.72</v>
+        <v>92.98</v>
       </c>
       <c r="F120" s="10" t="inlineStr">
         <is>
@@ -3114,10 +3114,10 @@
         <v>77.73999999999999</v>
       </c>
       <c r="D121" s="9" t="n">
-        <v>90.56999999999999</v>
+        <v>91.81</v>
       </c>
       <c r="E121" s="9" t="n">
-        <v>109.26</v>
+        <v>110.76</v>
       </c>
       <c r="F121" s="10" t="inlineStr">
         <is>
@@ -3138,10 +3138,10 @@
         <v>64.43000000000001</v>
       </c>
       <c r="D122" s="9" t="n">
-        <v>85.3</v>
+        <v>86.47</v>
       </c>
       <c r="E122" s="9" t="n">
-        <v>90.19</v>
+        <v>91.43000000000001</v>
       </c>
       <c r="F122" s="10" t="inlineStr">
         <is>
@@ -3162,10 +3162,10 @@
         <v>71.94</v>
       </c>
       <c r="D123" s="9" t="n">
-        <v>85.47</v>
+        <v>86.65000000000001</v>
       </c>
       <c r="E123" s="9" t="n">
-        <v>100.29</v>
+        <v>101.67</v>
       </c>
       <c r="F123" s="10" t="inlineStr">
         <is>
@@ -3186,10 +3186,10 @@
         <v>62.27</v>
       </c>
       <c r="D124" s="9" t="n">
-        <v>77.87</v>
+        <v>78.94</v>
       </c>
       <c r="E124" s="9" t="n">
-        <v>86.45999999999999</v>
+        <v>87.65000000000001</v>
       </c>
       <c r="F124" s="10" t="inlineStr">
         <is>
@@ -3210,10 +3210,10 @@
         <v>67.76000000000001</v>
       </c>
       <c r="D125" s="9" t="n">
-        <v>85</v>
+        <v>86.16</v>
       </c>
       <c r="E125" s="9" t="n">
-        <v>93.86</v>
+        <v>95.15000000000001</v>
       </c>
       <c r="F125" s="10" t="inlineStr">
         <is>
@@ -3234,10 +3234,10 @@
         <v>59.33</v>
       </c>
       <c r="D126" s="9" t="n">
-        <v>75.22</v>
+        <v>76.25</v>
       </c>
       <c r="E126" s="9" t="n">
-        <v>81.98999999999999</v>
+        <v>83.11</v>
       </c>
       <c r="F126" s="10" t="inlineStr">
         <is>
@@ -3258,10 +3258,10 @@
         <v>61.95</v>
       </c>
       <c r="D127" s="9" t="n">
-        <v>80.29000000000001</v>
+        <v>81.39</v>
       </c>
       <c r="E127" s="9" t="n">
-        <v>85.40000000000001</v>
+        <v>86.58</v>
       </c>
       <c r="F127" s="10" t="inlineStr">
         <is>
@@ -3282,10 +3282,10 @@
         <v>84.06999999999999</v>
       </c>
       <c r="D128" s="9" t="n">
-        <v>97.83</v>
+        <v>99.17</v>
       </c>
       <c r="E128" s="9" t="n">
-        <v>115.67</v>
+        <v>117.26</v>
       </c>
       <c r="F128" s="10" t="inlineStr">
         <is>
@@ -3306,10 +3306,10 @@
         <v>108.19</v>
       </c>
       <c r="D129" s="9" t="n">
-        <v>106.87</v>
+        <v>108.34</v>
       </c>
       <c r="E129" s="9" t="n">
-        <v>148.56</v>
+        <v>150.61</v>
       </c>
       <c r="F129" s="10" t="inlineStr">
         <is>
@@ -3330,10 +3330,10 @@
         <v>55.81</v>
       </c>
       <c r="D130" s="9" t="n">
-        <v>68.09</v>
+        <v>69.02</v>
       </c>
       <c r="E130" s="9" t="n">
-        <v>76.48999999999999</v>
+        <v>77.54000000000001</v>
       </c>
       <c r="F130" s="10" t="inlineStr">
         <is>
@@ -3354,10 +3354,10 @@
         <v>52.99</v>
       </c>
       <c r="D131" s="9" t="n">
-        <v>67.38</v>
+        <v>68.31</v>
       </c>
       <c r="E131" s="9" t="n">
-        <v>72.5</v>
+        <v>73.5</v>
       </c>
       <c r="F131" s="10" t="inlineStr">
         <is>
@@ -3378,10 +3378,10 @@
         <v>56.78</v>
       </c>
       <c r="D132" s="9" t="n">
-        <v>69.73</v>
+        <v>70.69</v>
       </c>
       <c r="E132" s="9" t="n">
-        <v>77.56</v>
+        <v>78.62</v>
       </c>
       <c r="F132" s="10" t="inlineStr">
         <is>
@@ -3402,10 +3402,10 @@
         <v>58.65</v>
       </c>
       <c r="D133" s="9" t="n">
-        <v>69.43000000000001</v>
+        <v>70.39</v>
       </c>
       <c r="E133" s="9" t="n">
-        <v>79.98</v>
+        <v>81.08</v>
       </c>
       <c r="F133" s="10" t="inlineStr">
         <is>
@@ -3426,10 +3426,10 @@
         <v>37.69</v>
       </c>
       <c r="D134" s="5" t="n">
-        <v>44.66</v>
+        <v>45.28</v>
       </c>
       <c r="E134" s="5" t="n">
-        <v>51.32</v>
+        <v>52.03</v>
       </c>
       <c r="F134" s="7" t="inlineStr"/>
     </row>
@@ -3446,10 +3446,10 @@
         <v>29.9</v>
       </c>
       <c r="D135" s="5" t="n">
-        <v>35.25</v>
+        <v>35.73</v>
       </c>
       <c r="E135" s="5" t="n">
-        <v>40.66</v>
+        <v>41.22</v>
       </c>
       <c r="F135" s="7" t="inlineStr"/>
     </row>
@@ -3466,10 +3466,10 @@
         <v>42.79</v>
       </c>
       <c r="D136" s="5" t="n">
-        <v>45.86</v>
+        <v>46.49</v>
       </c>
       <c r="E136" s="5" t="n">
-        <v>58.1</v>
+        <v>58.9</v>
       </c>
       <c r="F136" s="7" t="inlineStr"/>
     </row>
@@ -3486,10 +3486,10 @@
         <v>27.94</v>
       </c>
       <c r="D137" s="5" t="n">
-        <v>31.82</v>
+        <v>32.26</v>
       </c>
       <c r="E137" s="5" t="n">
-        <v>37.92</v>
+        <v>38.44</v>
       </c>
       <c r="F137" s="7" t="inlineStr"/>
     </row>
@@ -3506,10 +3506,10 @@
         <v>57.77</v>
       </c>
       <c r="D138" s="5" t="n">
-        <v>53.5</v>
+        <v>54.24</v>
       </c>
       <c r="E138" s="5" t="n">
-        <v>78.34999999999999</v>
+        <v>79.42</v>
       </c>
       <c r="F138" s="7" t="inlineStr"/>
     </row>
@@ -3526,10 +3526,10 @@
         <v>204.51</v>
       </c>
       <c r="D139" s="5" t="n">
-        <v>145.41</v>
+        <v>147.41</v>
       </c>
       <c r="E139" s="5" t="n">
-        <v>277.17</v>
+        <v>280.99</v>
       </c>
       <c r="F139" s="7" t="inlineStr"/>
     </row>
@@ -3546,10 +3546,10 @@
         <v>185.37</v>
       </c>
       <c r="D140" s="5" t="n">
-        <v>158.93</v>
+        <v>161.12</v>
       </c>
       <c r="E140" s="5" t="n">
-        <v>251.08</v>
+        <v>254.53</v>
       </c>
       <c r="F140" s="7" t="inlineStr"/>
     </row>
@@ -3566,10 +3566,10 @@
         <v>42.71</v>
       </c>
       <c r="D141" s="5" t="n">
-        <v>45.71</v>
+        <v>46.34</v>
       </c>
       <c r="E141" s="5" t="n">
-        <v>57.81</v>
+        <v>58.61</v>
       </c>
       <c r="F141" s="7" t="inlineStr"/>
     </row>
@@ -3586,10 +3586,10 @@
         <v>218.4</v>
       </c>
       <c r="D142" s="5" t="n">
-        <v>159.11</v>
+        <v>161.3</v>
       </c>
       <c r="E142" s="5" t="n">
-        <v>295.44</v>
+        <v>299.5</v>
       </c>
       <c r="F142" s="7" t="inlineStr"/>
     </row>
@@ -3606,10 +3606,10 @@
         <v>37.91</v>
       </c>
       <c r="D143" s="5" t="n">
-        <v>43.25</v>
+        <v>43.85</v>
       </c>
       <c r="E143" s="5" t="n">
-        <v>51.16</v>
+        <v>51.86</v>
       </c>
       <c r="F143" s="7" t="inlineStr"/>
     </row>
@@ -3626,10 +3626,10 @@
         <v>34.67</v>
       </c>
       <c r="D144" s="5" t="n">
-        <v>41.92</v>
+        <v>42.5</v>
       </c>
       <c r="E144" s="5" t="n">
-        <v>46.68</v>
+        <v>47.32</v>
       </c>
       <c r="F144" s="7" t="inlineStr"/>
     </row>
@@ -3646,10 +3646,10 @@
         <v>37.13</v>
       </c>
       <c r="D145" s="5" t="n">
-        <v>42.32</v>
+        <v>42.9</v>
       </c>
       <c r="E145" s="5" t="n">
-        <v>49.87</v>
+        <v>50.56</v>
       </c>
       <c r="F145" s="7" t="inlineStr"/>
     </row>
@@ -3666,10 +3666,10 @@
         <v>58.91</v>
       </c>
       <c r="D146" s="5" t="n">
-        <v>62.59</v>
+        <v>63.45</v>
       </c>
       <c r="E146" s="5" t="n">
-        <v>79.02</v>
+        <v>80.11</v>
       </c>
       <c r="F146" s="7" t="inlineStr"/>
     </row>
@@ -3686,10 +3686,10 @@
         <v>50.96</v>
       </c>
       <c r="D147" s="5" t="n">
-        <v>53.98</v>
+        <v>54.72</v>
       </c>
       <c r="E147" s="5" t="n">
-        <v>68.27</v>
+        <v>69.20999999999999</v>
       </c>
       <c r="F147" s="7" t="inlineStr"/>
     </row>
@@ -3706,10 +3706,10 @@
         <v>48.15</v>
       </c>
       <c r="D148" s="5" t="n">
-        <v>59.93</v>
+        <v>60.75</v>
       </c>
       <c r="E148" s="5" t="n">
-        <v>64.42</v>
+        <v>65.31</v>
       </c>
       <c r="F148" s="7" t="inlineStr"/>
     </row>
@@ -3726,10 +3726,10 @@
         <v>41.6</v>
       </c>
       <c r="D149" s="5" t="n">
-        <v>48.76</v>
+        <v>49.43</v>
       </c>
       <c r="E149" s="5" t="n">
-        <v>55.59</v>
+        <v>56.35</v>
       </c>
       <c r="F149" s="7" t="inlineStr"/>
     </row>
@@ -3746,10 +3746,10 @@
         <v>61.27</v>
       </c>
       <c r="D150" s="5" t="n">
-        <v>60.45</v>
+        <v>61.29</v>
       </c>
       <c r="E150" s="5" t="n">
-        <v>81.77</v>
+        <v>82.89</v>
       </c>
       <c r="F150" s="7" t="inlineStr"/>
     </row>
@@ -3766,10 +3766,10 @@
         <v>49.59</v>
       </c>
       <c r="D151" s="5" t="n">
-        <v>57.42</v>
+        <v>58.21</v>
       </c>
       <c r="E151" s="5" t="n">
-        <v>66.09</v>
+        <v>67</v>
       </c>
       <c r="F151" s="7" t="inlineStr"/>
     </row>
@@ -3786,10 +3786,10 @@
         <v>71.04000000000001</v>
       </c>
       <c r="D152" s="5" t="n">
-        <v>68.75</v>
+        <v>69.7</v>
       </c>
       <c r="E152" s="5" t="n">
-        <v>94.75</v>
+        <v>96.05</v>
       </c>
       <c r="F152" s="7" t="inlineStr"/>
     </row>
@@ -3806,10 +3806,10 @@
         <v>210.46</v>
       </c>
       <c r="D153" s="5" t="n">
-        <v>161.9</v>
+        <v>164.12</v>
       </c>
       <c r="E153" s="5" t="n">
-        <v>280.87</v>
+        <v>284.74</v>
       </c>
       <c r="F153" s="7" t="inlineStr"/>
     </row>
@@ -3826,10 +3826,10 @@
         <v>90.26000000000001</v>
       </c>
       <c r="D154" s="5" t="n">
-        <v>94.86</v>
+        <v>96.16</v>
       </c>
       <c r="E154" s="5" t="n">
-        <v>120.54</v>
+        <v>122.2</v>
       </c>
       <c r="F154" s="7" t="inlineStr"/>
     </row>
@@ -3846,10 +3846,10 @@
         <v>79.34999999999999</v>
       </c>
       <c r="D155" s="5" t="n">
-        <v>88.67</v>
+        <v>89.88</v>
       </c>
       <c r="E155" s="5" t="n">
-        <v>105.81</v>
+        <v>107.27</v>
       </c>
       <c r="F155" s="7" t="inlineStr"/>
     </row>
@@ -3866,10 +3866,10 @@
         <v>86.59999999999999</v>
       </c>
       <c r="D156" s="5" t="n">
-        <v>92.41</v>
+        <v>93.68000000000001</v>
       </c>
       <c r="E156" s="5" t="n">
-        <v>115.31</v>
+        <v>116.9</v>
       </c>
       <c r="F156" s="7" t="inlineStr"/>
     </row>
@@ -3886,10 +3886,10 @@
         <v>107.25</v>
       </c>
       <c r="D157" s="5" t="n">
-        <v>116.38</v>
+        <v>117.98</v>
       </c>
       <c r="E157" s="5" t="n">
-        <v>142.6</v>
+        <v>144.56</v>
       </c>
       <c r="F157" s="7" t="inlineStr"/>
     </row>
@@ -3906,10 +3906,10 @@
         <v>80.31999999999999</v>
       </c>
       <c r="D158" s="5" t="n">
-        <v>80.81</v>
+        <v>81.92</v>
       </c>
       <c r="E158" s="5" t="n">
-        <v>106.55</v>
+        <v>108.01</v>
       </c>
       <c r="F158" s="7" t="inlineStr"/>
     </row>
@@ -3926,10 +3926,10 @@
         <v>59.15</v>
       </c>
       <c r="D159" s="5" t="n">
-        <v>63.47</v>
+        <v>64.34</v>
       </c>
       <c r="E159" s="5" t="n">
-        <v>78.28</v>
+        <v>79.36</v>
       </c>
       <c r="F159" s="7" t="inlineStr"/>
     </row>
@@ -3946,10 +3946,10 @@
         <v>52.96</v>
       </c>
       <c r="D160" s="5" t="n">
-        <v>60.82</v>
+        <v>61.65</v>
       </c>
       <c r="E160" s="5" t="n">
-        <v>69.93000000000001</v>
+        <v>70.89</v>
       </c>
       <c r="F160" s="7" t="inlineStr"/>
     </row>
@@ -3966,10 +3966,10 @@
         <v>60.77</v>
       </c>
       <c r="D161" s="5" t="n">
-        <v>70.81999999999999</v>
+        <v>71.79000000000001</v>
       </c>
       <c r="E161" s="5" t="n">
-        <v>80.09999999999999</v>
+        <v>81.2</v>
       </c>
       <c r="F161" s="7" t="inlineStr"/>
     </row>
@@ -3986,10 +3986,10 @@
         <v>87.69</v>
       </c>
       <c r="D162" s="5" t="n">
-        <v>91.36</v>
+        <v>92.62</v>
       </c>
       <c r="E162" s="5" t="n">
-        <v>115.38</v>
+        <v>116.96</v>
       </c>
       <c r="F162" s="7" t="inlineStr"/>
     </row>
@@ -4006,10 +4006,10 @@
         <v>79.92</v>
       </c>
       <c r="D163" s="5" t="n">
-        <v>88.39</v>
+        <v>89.61</v>
       </c>
       <c r="E163" s="5" t="n">
-        <v>104.97</v>
+        <v>106.41</v>
       </c>
       <c r="F163" s="7" t="inlineStr"/>
     </row>
@@ -4026,10 +4026,10 @@
         <v>232.26</v>
       </c>
       <c r="D164" s="5" t="n">
-        <v>259.2</v>
+        <v>262.77</v>
       </c>
       <c r="E164" s="5" t="n">
-        <v>304.59</v>
+        <v>308.78</v>
       </c>
       <c r="F164" s="7" t="inlineStr"/>
     </row>
@@ -4046,10 +4046,10 @@
         <v>308.3</v>
       </c>
       <c r="D165" s="5" t="n">
-        <v>313.73</v>
+        <v>318.04</v>
       </c>
       <c r="E165" s="5" t="n">
-        <v>403.7</v>
+        <v>409.25</v>
       </c>
       <c r="F165" s="7" t="inlineStr"/>
     </row>
@@ -4066,10 +4066,10 @@
         <v>105.94</v>
       </c>
       <c r="D166" s="5" t="n">
-        <v>116.04</v>
+        <v>117.63</v>
       </c>
       <c r="E166" s="5" t="n">
-        <v>138.51</v>
+        <v>140.42</v>
       </c>
       <c r="F166" s="7" t="inlineStr"/>
     </row>
@@ -4086,10 +4086,10 @@
         <v>103.48</v>
       </c>
       <c r="D167" s="5" t="n">
-        <v>123.81</v>
+        <v>125.52</v>
       </c>
       <c r="E167" s="5" t="n">
-        <v>135.21</v>
+        <v>137.07</v>
       </c>
       <c r="F167" s="7" t="inlineStr"/>
     </row>
@@ -4106,10 +4106,10 @@
         <v>93.61</v>
       </c>
       <c r="D168" s="5" t="n">
-        <v>112.63</v>
+        <v>114.18</v>
       </c>
       <c r="E168" s="5" t="n">
-        <v>122.23</v>
+        <v>123.91</v>
       </c>
       <c r="F168" s="7" t="inlineStr"/>
     </row>
@@ -4126,10 +4126,10 @@
         <v>83.23</v>
       </c>
       <c r="D169" s="5" t="n">
-        <v>99.77</v>
+        <v>101.14</v>
       </c>
       <c r="E169" s="5" t="n">
-        <v>108.61</v>
+        <v>110.1</v>
       </c>
       <c r="F169" s="7" t="inlineStr"/>
     </row>
@@ -4146,10 +4146,10 @@
         <v>87.06999999999999</v>
       </c>
       <c r="D170" s="5" t="n">
-        <v>101.05</v>
+        <v>102.44</v>
       </c>
       <c r="E170" s="5" t="n">
-        <v>113.39</v>
+        <v>114.95</v>
       </c>
       <c r="F170" s="7" t="inlineStr"/>
     </row>
@@ -4166,10 +4166,10 @@
         <v>92.38</v>
       </c>
       <c r="D171" s="5" t="n">
-        <v>106.15</v>
+        <v>107.61</v>
       </c>
       <c r="E171" s="5" t="n">
-        <v>120.06</v>
+        <v>121.71</v>
       </c>
       <c r="F171" s="7" t="inlineStr"/>
     </row>
@@ -4186,10 +4186,10 @@
         <v>87.77</v>
       </c>
       <c r="D172" s="5" t="n">
-        <v>104.46</v>
+        <v>105.89</v>
       </c>
       <c r="E172" s="5" t="n">
-        <v>113.83</v>
+        <v>115.4</v>
       </c>
       <c r="F172" s="7" t="inlineStr"/>
     </row>
@@ -4206,10 +4206,10 @@
         <v>89.16</v>
       </c>
       <c r="D173" s="5" t="n">
-        <v>101.22</v>
+        <v>102.61</v>
       </c>
       <c r="E173" s="5" t="n">
-        <v>115.38</v>
+        <v>116.97</v>
       </c>
       <c r="F173" s="7" t="inlineStr"/>
     </row>
@@ -4226,10 +4226,10 @@
         <v>72.36</v>
       </c>
       <c r="D174" s="5" t="n">
-        <v>84.40000000000001</v>
+        <v>85.56999999999999</v>
       </c>
       <c r="E174" s="5" t="n">
-        <v>93.43000000000001</v>
+        <v>94.70999999999999</v>
       </c>
       <c r="F174" s="7" t="inlineStr"/>
     </row>
@@ -4246,10 +4246,10 @@
         <v>81.22</v>
       </c>
       <c r="D175" s="5" t="n">
-        <v>92.15000000000001</v>
+        <v>93.42</v>
       </c>
       <c r="E175" s="5" t="n">
-        <v>104.64</v>
+        <v>106.08</v>
       </c>
       <c r="F175" s="7" t="inlineStr"/>
     </row>
@@ -4266,10 +4266,10 @@
         <v>82.28</v>
       </c>
       <c r="D176" s="5" t="n">
-        <v>97.48999999999999</v>
+        <v>98.83</v>
       </c>
       <c r="E176" s="5" t="n">
-        <v>105.85</v>
+        <v>107.3</v>
       </c>
       <c r="F176" s="7" t="inlineStr"/>
     </row>
@@ -4286,10 +4286,10 @@
         <v>83.44</v>
       </c>
       <c r="D177" s="5" t="n">
-        <v>92.28</v>
+        <v>93.55</v>
       </c>
       <c r="E177" s="5" t="n">
-        <v>107.18</v>
+        <v>108.66</v>
       </c>
       <c r="F177" s="7" t="inlineStr"/>
     </row>
@@ -4306,10 +4306,10 @@
         <v>66.75</v>
       </c>
       <c r="D178" s="5" t="n">
-        <v>80.20999999999999</v>
+        <v>81.31</v>
       </c>
       <c r="E178" s="5" t="n">
-        <v>85.62</v>
+        <v>86.8</v>
       </c>
       <c r="F178" s="7" t="inlineStr"/>
     </row>
@@ -4326,10 +4326,10 @@
         <v>69.11</v>
       </c>
       <c r="D179" s="5" t="n">
-        <v>81.64</v>
+        <v>82.76000000000001</v>
       </c>
       <c r="E179" s="5" t="n">
-        <v>88.54000000000001</v>
+        <v>89.76000000000001</v>
       </c>
       <c r="F179" s="7" t="inlineStr"/>
     </row>
@@ -4346,10 +4346,10 @@
         <v>72.86</v>
       </c>
       <c r="D180" s="5" t="n">
-        <v>83.28</v>
+        <v>84.42</v>
       </c>
       <c r="E180" s="5" t="n">
-        <v>93.23999999999999</v>
+        <v>94.52</v>
       </c>
       <c r="F180" s="7" t="inlineStr"/>
     </row>
@@ -4366,10 +4366,10 @@
         <v>96.17</v>
       </c>
       <c r="D181" s="5" t="n">
-        <v>102.79</v>
+        <v>104.2</v>
       </c>
       <c r="E181" s="5" t="n">
-        <v>122.92</v>
+        <v>124.61</v>
       </c>
       <c r="F181" s="7" t="inlineStr"/>
     </row>
@@ -4386,10 +4386,10 @@
         <v>77.84</v>
       </c>
       <c r="D182" s="5" t="n">
-        <v>88.22</v>
+        <v>89.43000000000001</v>
       </c>
       <c r="E182" s="5" t="n">
-        <v>99.34999999999999</v>
+        <v>100.71</v>
       </c>
       <c r="F182" s="7" t="inlineStr"/>
     </row>
@@ -4406,10 +4406,10 @@
         <v>94.70999999999999</v>
       </c>
       <c r="D183" s="5" t="n">
-        <v>105.13</v>
+        <v>106.58</v>
       </c>
       <c r="E183" s="5" t="n">
-        <v>120.7</v>
+        <v>122.36</v>
       </c>
       <c r="F183" s="7" t="inlineStr"/>
     </row>
@@ -4426,10 +4426,10 @@
         <v>92.73999999999999</v>
       </c>
       <c r="D184" s="5" t="n">
-        <v>102.57</v>
+        <v>103.98</v>
       </c>
       <c r="E184" s="5" t="n">
-        <v>118.02</v>
+        <v>119.65</v>
       </c>
       <c r="F184" s="7" t="inlineStr"/>
     </row>
@@ -4446,10 +4446,10 @@
         <v>89.22</v>
       </c>
       <c r="D185" s="5" t="n">
-        <v>99.52</v>
+        <v>100.89</v>
       </c>
       <c r="E185" s="5" t="n">
-        <v>113.35</v>
+        <v>114.91</v>
       </c>
       <c r="F185" s="7" t="inlineStr"/>
     </row>
@@ -4466,10 +4466,10 @@
         <v>105.34</v>
       </c>
       <c r="D186" s="5" t="n">
-        <v>112.69</v>
+        <v>114.24</v>
       </c>
       <c r="E186" s="5" t="n">
-        <v>133.59</v>
+        <v>135.43</v>
       </c>
       <c r="F186" s="7" t="inlineStr"/>
     </row>
@@ -4486,10 +4486,10 @@
         <v>92.93000000000001</v>
       </c>
       <c r="D187" s="5" t="n">
-        <v>100.24</v>
+        <v>101.62</v>
       </c>
       <c r="E187" s="5" t="n">
-        <v>117.65</v>
+        <v>119.27</v>
       </c>
       <c r="F187" s="7" t="inlineStr"/>
     </row>
@@ -4506,10 +4506,10 @@
         <v>113.36</v>
       </c>
       <c r="D188" s="5" t="n">
-        <v>118.9</v>
+        <v>120.53</v>
       </c>
       <c r="E188" s="5" t="n">
-        <v>143.52</v>
+        <v>145.5</v>
       </c>
       <c r="F188" s="7" t="inlineStr"/>
     </row>
@@ -4526,10 +4526,10 @@
         <v>95.13</v>
       </c>
       <c r="D189" s="5" t="n">
-        <v>106.48</v>
+        <v>107.95</v>
       </c>
       <c r="E189" s="5" t="n">
-        <v>120.45</v>
+        <v>122.1</v>
       </c>
       <c r="F189" s="7" t="inlineStr"/>
     </row>
@@ -4546,10 +4546,10 @@
         <v>91.70999999999999</v>
       </c>
       <c r="D190" s="5" t="n">
-        <v>102.42</v>
+        <v>103.83</v>
       </c>
       <c r="E190" s="5" t="n">
-        <v>116.12</v>
+        <v>117.72</v>
       </c>
       <c r="F190" s="7" t="inlineStr"/>
     </row>
@@ -4566,10 +4566,10 @@
         <v>76.88</v>
       </c>
       <c r="D191" s="5" t="n">
-        <v>86.73999999999999</v>
+        <v>87.93000000000001</v>
       </c>
       <c r="E191" s="5" t="n">
-        <v>97.15000000000001</v>
+        <v>98.48999999999999</v>
       </c>
       <c r="F191" s="7" t="inlineStr"/>
     </row>
@@ -4586,10 +4586,10 @@
         <v>82.59999999999999</v>
       </c>
       <c r="D192" s="5" t="n">
-        <v>91.83</v>
+        <v>93.09</v>
       </c>
       <c r="E192" s="5" t="n">
-        <v>104.18</v>
+        <v>105.61</v>
       </c>
       <c r="F192" s="7" t="inlineStr"/>
     </row>
@@ -4606,10 +4606,10 @@
         <v>99.83</v>
       </c>
       <c r="D193" s="5" t="n">
-        <v>106.99</v>
+        <v>108.46</v>
       </c>
       <c r="E193" s="5" t="n">
-        <v>125.66</v>
+        <v>127.39</v>
       </c>
       <c r="F193" s="7" t="inlineStr"/>
     </row>
@@ -4626,10 +4626,10 @@
         <v>73.22</v>
       </c>
       <c r="D194" s="5" t="n">
-        <v>83.13</v>
+        <v>84.28</v>
       </c>
       <c r="E194" s="5" t="n">
-        <v>91.98999999999999</v>
+        <v>93.26000000000001</v>
       </c>
       <c r="F194" s="7" t="inlineStr"/>
     </row>
@@ -4646,10 +4646,10 @@
         <v>66.72</v>
       </c>
       <c r="D195" s="5" t="n">
-        <v>77.41</v>
+        <v>78.47</v>
       </c>
       <c r="E195" s="5" t="n">
-        <v>83.67</v>
+        <v>84.81999999999999</v>
       </c>
       <c r="F195" s="7" t="inlineStr"/>
     </row>
@@ -4666,10 +4666,10 @@
         <v>64.55</v>
       </c>
       <c r="D196" s="5" t="n">
-        <v>73.25</v>
+        <v>74.25</v>
       </c>
       <c r="E196" s="5" t="n">
-        <v>80.79000000000001</v>
+        <v>81.91</v>
       </c>
       <c r="F196" s="7" t="inlineStr"/>
     </row>
@@ -4686,10 +4686,10 @@
         <v>77.53</v>
       </c>
       <c r="D197" s="5" t="n">
-        <v>92.61</v>
+        <v>93.88</v>
       </c>
       <c r="E197" s="5" t="n">
-        <v>96.81999999999999</v>
+        <v>98.15000000000001</v>
       </c>
       <c r="F197" s="7" t="inlineStr"/>
     </row>
@@ -4706,10 +4706,10 @@
         <v>65.44</v>
       </c>
       <c r="D198" s="5" t="n">
-        <v>76.09999999999999</v>
+        <v>77.15000000000001</v>
       </c>
       <c r="E198" s="5" t="n">
-        <v>81.54000000000001</v>
+        <v>82.66</v>
       </c>
       <c r="F198" s="7" t="inlineStr"/>
     </row>
@@ -4726,10 +4726,10 @@
         <v>58.51</v>
       </c>
       <c r="D199" s="5" t="n">
-        <v>68.16</v>
+        <v>69.09999999999999</v>
       </c>
       <c r="E199" s="5" t="n">
-        <v>72.73999999999999</v>
+        <v>73.73999999999999</v>
       </c>
       <c r="F199" s="7" t="inlineStr"/>
     </row>
@@ -4746,10 +4746,10 @@
         <v>83.67</v>
       </c>
       <c r="D200" s="5" t="n">
-        <v>82.93000000000001</v>
+        <v>84.06999999999999</v>
       </c>
       <c r="E200" s="5" t="n">
-        <v>103.88</v>
+        <v>105.31</v>
       </c>
       <c r="F200" s="7" t="inlineStr"/>
     </row>
@@ -4766,10 +4766,10 @@
         <v>58.28</v>
       </c>
       <c r="D201" s="5" t="n">
-        <v>66.73</v>
+        <v>67.64</v>
       </c>
       <c r="E201" s="5" t="n">
-        <v>72.27</v>
+        <v>73.26000000000001</v>
       </c>
       <c r="F201" s="7" t="inlineStr"/>
     </row>
@@ -4786,10 +4786,10 @@
         <v>46.18</v>
       </c>
       <c r="D202" s="5" t="n">
-        <v>51.11</v>
+        <v>51.82</v>
       </c>
       <c r="E202" s="5" t="n">
-        <v>57.19</v>
+        <v>57.98</v>
       </c>
       <c r="F202" s="7" t="inlineStr"/>
     </row>
@@ -4806,10 +4806,10 @@
         <v>40.2</v>
       </c>
       <c r="D203" s="5" t="n">
-        <v>46.11</v>
+        <v>46.74</v>
       </c>
       <c r="E203" s="5" t="n">
-        <v>50.11</v>
+        <v>50.8</v>
       </c>
       <c r="F203" s="7" t="inlineStr"/>
     </row>
@@ -4826,10 +4826,10 @@
         <v>35.09</v>
       </c>
       <c r="D204" s="5" t="n">
-        <v>39.12</v>
+        <v>39.66</v>
       </c>
       <c r="E204" s="5" t="n">
-        <v>44.02</v>
+        <v>44.63</v>
       </c>
       <c r="F204" s="7" t="inlineStr"/>
     </row>
@@ -4846,10 +4846,10 @@
         <v>35.86</v>
       </c>
       <c r="D205" s="5" t="n">
-        <v>42.57</v>
+        <v>43.16</v>
       </c>
       <c r="E205" s="5" t="n">
-        <v>45.29</v>
+        <v>45.91</v>
       </c>
       <c r="F205" s="7" t="inlineStr"/>
     </row>
@@ -4866,10 +4866,10 @@
         <v>42.74</v>
       </c>
       <c r="D206" s="5" t="n">
-        <v>48.03</v>
+        <v>48.69</v>
       </c>
       <c r="E206" s="5" t="n">
-        <v>53.7</v>
+        <v>54.44</v>
       </c>
       <c r="F206" s="7" t="inlineStr"/>
     </row>
@@ -4886,10 +4886,10 @@
         <v>30.26</v>
       </c>
       <c r="D207" s="5" t="n">
-        <v>38.06</v>
+        <v>38.58</v>
       </c>
       <c r="E207" s="5" t="n">
-        <v>37.82</v>
+        <v>38.34</v>
       </c>
       <c r="F207" s="7" t="inlineStr"/>
     </row>
@@ -4906,10 +4906,10 @@
         <v>26.55</v>
       </c>
       <c r="D208" s="5" t="n">
-        <v>34.02</v>
+        <v>34.49</v>
       </c>
       <c r="E208" s="5" t="n">
-        <v>33.02</v>
+        <v>33.47</v>
       </c>
       <c r="F208" s="7" t="inlineStr"/>
     </row>
@@ -4926,10 +4926,10 @@
         <v>37.4</v>
       </c>
       <c r="D209" s="5" t="n">
-        <v>43.67</v>
+        <v>44.27</v>
       </c>
       <c r="E209" s="5" t="n">
-        <v>46.37</v>
+        <v>47.01</v>
       </c>
       <c r="F209" s="7" t="inlineStr"/>
     </row>
@@ -4946,10 +4946,10 @@
         <v>52.86</v>
       </c>
       <c r="D210" s="5" t="n">
-        <v>56.06</v>
+        <v>56.83</v>
       </c>
       <c r="E210" s="5" t="n">
-        <v>65.34</v>
+        <v>66.23999999999999</v>
       </c>
       <c r="F210" s="7" t="inlineStr"/>
     </row>
@@ -4966,10 +4966,10 @@
         <v>65.43000000000001</v>
       </c>
       <c r="D211" s="5" t="n">
-        <v>67.12</v>
+        <v>68.04000000000001</v>
       </c>
       <c r="E211" s="5" t="n">
-        <v>80.64</v>
+        <v>81.75</v>
       </c>
       <c r="F211" s="7" t="inlineStr"/>
     </row>
@@ -4986,10 +4986,10 @@
         <v>43.8</v>
       </c>
       <c r="D212" s="5" t="n">
-        <v>49.63</v>
+        <v>50.32</v>
       </c>
       <c r="E212" s="5" t="n">
-        <v>53.88</v>
+        <v>54.62</v>
       </c>
       <c r="F212" s="7" t="inlineStr"/>
     </row>
@@ -5006,10 +5006,10 @@
         <v>47.73</v>
       </c>
       <c r="D213" s="5" t="n">
-        <v>51.18</v>
+        <v>51.89</v>
       </c>
       <c r="E213" s="5" t="n">
-        <v>58.6</v>
+        <v>59.4</v>
       </c>
       <c r="F213" s="7" t="inlineStr"/>
     </row>
@@ -5026,10 +5026,10 @@
         <v>54.37</v>
       </c>
       <c r="D214" s="5" t="n">
-        <v>56.13</v>
+        <v>56.91</v>
       </c>
       <c r="E214" s="5" t="n">
-        <v>66.62</v>
+        <v>67.54000000000001</v>
       </c>
       <c r="F214" s="7" t="inlineStr"/>
     </row>
@@ -5046,10 +5046,10 @@
         <v>61.17</v>
       </c>
       <c r="D215" s="5" t="n">
-        <v>65.34999999999999</v>
+        <v>66.25</v>
       </c>
       <c r="E215" s="5" t="n">
-        <v>74.77</v>
+        <v>75.8</v>
       </c>
       <c r="F215" s="7" t="inlineStr"/>
     </row>
@@ -5066,10 +5066,10 @@
         <v>223.28</v>
       </c>
       <c r="D216" s="5" t="n">
-        <v>157.61</v>
+        <v>159.78</v>
       </c>
       <c r="E216" s="5" t="n">
-        <v>272.27</v>
+        <v>276.01</v>
       </c>
       <c r="F216" s="7" t="inlineStr"/>
     </row>
@@ -5086,10 +5086,10 @@
         <v>334.25</v>
       </c>
       <c r="D217" s="5" t="n">
-        <v>244.16</v>
+        <v>247.52</v>
       </c>
       <c r="E217" s="5" t="n">
-        <v>406.6</v>
+        <v>412.19</v>
       </c>
       <c r="F217" s="7" t="inlineStr"/>
     </row>
@@ -5106,10 +5106,10 @@
         <v>185.43</v>
       </c>
       <c r="D218" s="5" t="n">
-        <v>163.85</v>
+        <v>166.11</v>
       </c>
       <c r="E218" s="5" t="n">
-        <v>224.93</v>
+        <v>228.02</v>
       </c>
       <c r="F218" s="7" t="inlineStr"/>
     </row>
@@ -5126,10 +5126,10 @@
         <v>55.55</v>
       </c>
       <c r="D219" s="5" t="n">
-        <v>64.77</v>
+        <v>65.66</v>
       </c>
       <c r="E219" s="5" t="n">
-        <v>67.19</v>
+        <v>68.12</v>
       </c>
       <c r="F219" s="7" t="inlineStr"/>
     </row>
@@ -5146,10 +5146,10 @@
         <v>52.32</v>
       </c>
       <c r="D220" s="5" t="n">
-        <v>61.78</v>
+        <v>62.63</v>
       </c>
       <c r="E220" s="5" t="n">
-        <v>63.11</v>
+        <v>63.98</v>
       </c>
       <c r="F220" s="7" t="inlineStr"/>
     </row>
@@ -5166,10 +5166,10 @@
         <v>80.47</v>
       </c>
       <c r="D221" s="5" t="n">
-        <v>79.84999999999999</v>
+        <v>80.95</v>
       </c>
       <c r="E221" s="5" t="n">
-        <v>96.65000000000001</v>
+        <v>97.98</v>
       </c>
       <c r="F221" s="7" t="inlineStr"/>
     </row>
@@ -5186,10 +5186,10 @@
         <v>132.44</v>
       </c>
       <c r="D222" s="5" t="n">
-        <v>115.48</v>
+        <v>117.07</v>
       </c>
       <c r="E222" s="5" t="n">
-        <v>158.4</v>
+        <v>160.58</v>
       </c>
       <c r="F222" s="7" t="inlineStr"/>
     </row>
@@ -5206,10 +5206,10 @@
         <v>182.96</v>
       </c>
       <c r="D223" s="5" t="n">
-        <v>153.18</v>
+        <v>155.28</v>
       </c>
       <c r="E223" s="5" t="n">
-        <v>217.91</v>
+        <v>220.91</v>
       </c>
       <c r="F223" s="7" t="inlineStr"/>
     </row>
@@ -5226,10 +5226,10 @@
         <v>189.96</v>
       </c>
       <c r="D224" s="5" t="n">
-        <v>165.43</v>
+        <v>167.71</v>
       </c>
       <c r="E224" s="5" t="n">
-        <v>224.63</v>
+        <v>227.72</v>
       </c>
       <c r="F224" s="7" t="inlineStr"/>
     </row>
@@ -5246,10 +5246,10 @@
         <v>257.03</v>
       </c>
       <c r="D225" s="5" t="n">
-        <v>191.05</v>
+        <v>193.68</v>
       </c>
       <c r="E225" s="5" t="n">
-        <v>301.78</v>
+        <v>305.93</v>
       </c>
       <c r="F225" s="7" t="inlineStr"/>
     </row>
@@ -5266,10 +5266,10 @@
         <v>196.7</v>
       </c>
       <c r="D226" s="5" t="n">
-        <v>171.61</v>
+        <v>173.97</v>
       </c>
       <c r="E226" s="5" t="n">
-        <v>229.32</v>
+        <v>232.47</v>
       </c>
       <c r="F226" s="7" t="inlineStr"/>
     </row>
@@ -5286,10 +5286,10 @@
         <v>265.86</v>
       </c>
       <c r="D227" s="5" t="n">
-        <v>254.68</v>
+        <v>258.19</v>
       </c>
       <c r="E227" s="5" t="n">
-        <v>308.11</v>
+        <v>312.35</v>
       </c>
       <c r="F227" s="7" t="inlineStr"/>
     </row>
@@ -5306,10 +5306,10 @@
         <v>415.45</v>
       </c>
       <c r="D228" s="5" t="n">
-        <v>400.1</v>
+        <v>405.6</v>
       </c>
       <c r="E228" s="5" t="n">
-        <v>478.64</v>
+        <v>485.22</v>
       </c>
       <c r="F228" s="7" t="inlineStr"/>
     </row>
@@ -5326,10 +5326,10 @@
         <v>439.14</v>
       </c>
       <c r="D229" s="5" t="n">
-        <v>458.4</v>
+        <v>464.7</v>
       </c>
       <c r="E229" s="5" t="n">
-        <v>502.96</v>
+        <v>509.88</v>
       </c>
       <c r="F229" s="7" t="inlineStr"/>
     </row>
@@ -5346,10 +5346,10 @@
         <v>507.37</v>
       </c>
       <c r="D230" s="5" t="n">
-        <v>445.77</v>
+        <v>451.9</v>
       </c>
       <c r="E230" s="5" t="n">
-        <v>577.5700000000001</v>
+        <v>585.52</v>
       </c>
       <c r="F230" s="7" t="inlineStr"/>
     </row>
@@ -5366,10 +5366,10 @@
         <v>129.62</v>
       </c>
       <c r="D231" s="5" t="n">
-        <v>151.06</v>
+        <v>153.14</v>
       </c>
       <c r="E231" s="5" t="n">
-        <v>146.66</v>
+        <v>148.68</v>
       </c>
       <c r="F231" s="7" t="inlineStr"/>
     </row>
@@ -5386,10 +5386,10 @@
         <v>152.44</v>
       </c>
       <c r="D232" s="5" t="n">
-        <v>176.46</v>
+        <v>178.89</v>
       </c>
       <c r="E232" s="5" t="n">
-        <v>171.44</v>
+        <v>173.8</v>
       </c>
       <c r="F232" s="7" t="inlineStr"/>
     </row>
@@ -5406,10 +5406,10 @@
         <v>161.28</v>
       </c>
       <c r="D233" s="5" t="n">
-        <v>172.19</v>
+        <v>174.56</v>
       </c>
       <c r="E233" s="5" t="n">
-        <v>180.27</v>
+        <v>182.75</v>
       </c>
       <c r="F233" s="7" t="inlineStr"/>
     </row>
@@ -5426,10 +5426,10 @@
         <v>118.14</v>
       </c>
       <c r="D234" s="5" t="n">
-        <v>134.98</v>
+        <v>136.84</v>
       </c>
       <c r="E234" s="5" t="n">
-        <v>131.25</v>
+        <v>133.05</v>
       </c>
       <c r="F234" s="7" t="inlineStr"/>
     </row>
@@ -5446,10 +5446,10 @@
         <v>76.42</v>
       </c>
       <c r="D235" s="5" t="n">
-        <v>94.37</v>
+        <v>95.67</v>
       </c>
       <c r="E235" s="5" t="n">
-        <v>84.39</v>
+        <v>85.55</v>
       </c>
       <c r="F235" s="7" t="inlineStr"/>
     </row>
@@ -5466,10 +5466,10 @@
         <v>113.54</v>
       </c>
       <c r="D236" s="5" t="n">
-        <v>108.78</v>
+        <v>110.28</v>
       </c>
       <c r="E236" s="5" t="n">
-        <v>124.81</v>
+        <v>126.53</v>
       </c>
       <c r="F236" s="7" t="inlineStr"/>
     </row>
@@ -5486,10 +5486,10 @@
         <v>95.48</v>
       </c>
       <c r="D237" s="5" t="n">
-        <v>97.17</v>
+        <v>98.5</v>
       </c>
       <c r="E237" s="5" t="n">
-        <v>104.49</v>
+        <v>105.93</v>
       </c>
       <c r="F237" s="7" t="inlineStr"/>
     </row>
@@ -5506,10 +5506,10 @@
         <v>157.17</v>
       </c>
       <c r="D238" s="5" t="n">
-        <v>134.09</v>
+        <v>135.94</v>
       </c>
       <c r="E238" s="5" t="n">
-        <v>171.23</v>
+        <v>173.59</v>
       </c>
       <c r="F238" s="7" t="inlineStr"/>
     </row>
@@ -5526,10 +5526,10 @@
         <v>111.33</v>
       </c>
       <c r="D239" s="5" t="n">
-        <v>119.44</v>
+        <v>121.08</v>
       </c>
       <c r="E239" s="5" t="n">
-        <v>120.95</v>
+        <v>122.61</v>
       </c>
       <c r="F239" s="7" t="inlineStr"/>
     </row>
@@ -5546,10 +5546,10 @@
         <v>187</v>
       </c>
       <c r="D240" s="5" t="n">
-        <v>178.63</v>
+        <v>181.09</v>
       </c>
       <c r="E240" s="5" t="n">
-        <v>202.58</v>
+        <v>205.36</v>
       </c>
       <c r="F240" s="7" t="inlineStr"/>
     </row>
@@ -5566,10 +5566,10 @@
         <v>117.86</v>
       </c>
       <c r="D241" s="5" t="n">
-        <v>110.85</v>
+        <v>112.38</v>
       </c>
       <c r="E241" s="5" t="n">
-        <v>127.31</v>
+        <v>129.07</v>
       </c>
       <c r="F241" s="7" t="inlineStr"/>
     </row>
@@ -5586,10 +5586,10 @@
         <v>83.20999999999999</v>
       </c>
       <c r="D242" s="5" t="n">
-        <v>83.15000000000001</v>
+        <v>84.29000000000001</v>
       </c>
       <c r="E242" s="5" t="n">
-        <v>89.54000000000001</v>
+        <v>90.77</v>
       </c>
       <c r="F242" s="7" t="inlineStr"/>
     </row>
@@ -5606,10 +5606,10 @@
         <v>64.40000000000001</v>
       </c>
       <c r="D243" s="5" t="n">
-        <v>72.5</v>
+        <v>73.5</v>
       </c>
       <c r="E243" s="5" t="n">
-        <v>69.04000000000001</v>
+        <v>69.98999999999999</v>
       </c>
       <c r="F243" s="7" t="inlineStr"/>
     </row>
@@ -5626,10 +5626,10 @@
         <v>48.95</v>
       </c>
       <c r="D244" s="5" t="n">
-        <v>54.22</v>
+        <v>54.96</v>
       </c>
       <c r="E244" s="5" t="n">
-        <v>52.27</v>
+        <v>52.99</v>
       </c>
       <c r="F244" s="7" t="inlineStr"/>
     </row>
@@ -5646,10 +5646,10 @@
         <v>31.89</v>
       </c>
       <c r="D245" s="5" t="n">
-        <v>39.48</v>
+        <v>40.03</v>
       </c>
       <c r="E245" s="5" t="n">
-        <v>33.98</v>
+        <v>34.45</v>
       </c>
       <c r="F245" s="7" t="inlineStr"/>
     </row>
@@ -5666,10 +5666,10 @@
         <v>73.34999999999999</v>
       </c>
       <c r="D246" s="5" t="n">
-        <v>77.59999999999999</v>
+        <v>78.67</v>
       </c>
       <c r="E246" s="5" t="n">
-        <v>78.01000000000001</v>
+        <v>79.08</v>
       </c>
       <c r="F246" s="7" t="inlineStr"/>
     </row>
@@ -5686,10 +5686,10 @@
         <v>117.11</v>
       </c>
       <c r="D247" s="5" t="n">
-        <v>98.7</v>
+        <v>100.05</v>
       </c>
       <c r="E247" s="5" t="n">
-        <v>124.28</v>
+        <v>125.99</v>
       </c>
       <c r="F247" s="7" t="inlineStr"/>
     </row>
@@ -5706,10 +5706,10 @@
         <v>172.77</v>
       </c>
       <c r="D248" s="5" t="n">
-        <v>169.73</v>
+        <v>172.06</v>
       </c>
       <c r="E248" s="5" t="n">
-        <v>182.79</v>
+        <v>185.3</v>
       </c>
       <c r="F248" s="7" t="inlineStr"/>
     </row>
@@ -5726,10 +5726,10 @@
         <v>164.47</v>
       </c>
       <c r="D249" s="5" t="n">
-        <v>126.28</v>
+        <v>128.02</v>
       </c>
       <c r="E249" s="5" t="n">
-        <v>173.47</v>
+        <v>175.85</v>
       </c>
       <c r="F249" s="7" t="inlineStr"/>
     </row>
@@ -5746,10 +5746,10 @@
         <v>74.56</v>
       </c>
       <c r="D250" s="5" t="n">
-        <v>77.90000000000001</v>
+        <v>78.97</v>
       </c>
       <c r="E250" s="5" t="n">
-        <v>78.40000000000001</v>
+        <v>79.48</v>
       </c>
       <c r="F250" s="7" t="inlineStr"/>
     </row>
@@ -5766,10 +5766,10 @@
         <v>77.23</v>
       </c>
       <c r="D251" s="5" t="n">
-        <v>88.86</v>
+        <v>90.09</v>
       </c>
       <c r="E251" s="5" t="n">
-        <v>80.92</v>
+        <v>82.03</v>
       </c>
       <c r="F251" s="7" t="inlineStr"/>
     </row>
@@ -5786,10 +5786,10 @@
         <v>87.48999999999999</v>
       </c>
       <c r="D252" s="5" t="n">
-        <v>96.78</v>
+        <v>98.12</v>
       </c>
       <c r="E252" s="5" t="n">
-        <v>91.34999999999999</v>
+        <v>92.61</v>
       </c>
       <c r="F252" s="7" t="inlineStr"/>
     </row>
@@ -5806,10 +5806,10 @@
         <v>127.4</v>
       </c>
       <c r="D253" s="5" t="n">
-        <v>129.73</v>
+        <v>131.51</v>
       </c>
       <c r="E253" s="5" t="n">
-        <v>132.57</v>
+        <v>134.39</v>
       </c>
       <c r="F253" s="7" t="inlineStr"/>
     </row>
@@ -5826,10 +5826,10 @@
         <v>135.85</v>
       </c>
       <c r="D254" s="5" t="n">
-        <v>123.8</v>
+        <v>125.5</v>
       </c>
       <c r="E254" s="5" t="n">
-        <v>141.26</v>
+        <v>143.2</v>
       </c>
       <c r="F254" s="7" t="inlineStr"/>
     </row>
@@ -5846,10 +5846,10 @@
         <v>162.05</v>
       </c>
       <c r="D255" s="5" t="n">
-        <v>135.18</v>
+        <v>137.04</v>
       </c>
       <c r="E255" s="5" t="n">
-        <v>168.38</v>
+        <v>170.69</v>
       </c>
       <c r="F255" s="7" t="inlineStr"/>
     </row>
@@ -5866,10 +5866,10 @@
         <v>31.67</v>
       </c>
       <c r="D256" s="5" t="n">
-        <v>51.56</v>
+        <v>52.27</v>
       </c>
       <c r="E256" s="5" t="n">
-        <v>32.88</v>
+        <v>33.34</v>
       </c>
       <c r="F256" s="7" t="inlineStr"/>
     </row>
@@ -5886,10 +5886,10 @@
         <v>61.54</v>
       </c>
       <c r="D257" s="5" t="n">
-        <v>73.51000000000001</v>
+        <v>74.53</v>
       </c>
       <c r="E257" s="5" t="n">
-        <v>63.85</v>
+        <v>64.73</v>
       </c>
       <c r="F257" s="7" t="inlineStr"/>
     </row>
@@ -5906,10 +5906,10 @@
         <v>259.36</v>
       </c>
       <c r="D258" s="5" t="n">
-        <v>184.04</v>
+        <v>186.57</v>
       </c>
       <c r="E258" s="5" t="n">
-        <v>268.94</v>
+        <v>272.64</v>
       </c>
       <c r="F258" s="7" t="inlineStr"/>
     </row>
@@ -5926,10 +5926,10 @@
         <v>150.79</v>
       </c>
       <c r="D259" s="5" t="n">
-        <v>139.31</v>
+        <v>141.23</v>
       </c>
       <c r="E259" s="5" t="n">
-        <v>156.26</v>
+        <v>158.41</v>
       </c>
       <c r="F259" s="7" t="inlineStr"/>
     </row>
@@ -5946,10 +5946,10 @@
         <v>147.57</v>
       </c>
       <c r="D260" s="5" t="n">
-        <v>117.78</v>
+        <v>119.4</v>
       </c>
       <c r="E260" s="5" t="n">
-        <v>152.45</v>
+        <v>154.55</v>
       </c>
       <c r="F260" s="7" t="inlineStr"/>
     </row>
@@ -5966,10 +5966,10 @@
         <v>72.06999999999999</v>
       </c>
       <c r="D261" s="5" t="n">
-        <v>77.15000000000001</v>
+        <v>78.20999999999999</v>
       </c>
       <c r="E261" s="5" t="n">
-        <v>74.23</v>
+        <v>75.25</v>
       </c>
       <c r="F261" s="7" t="inlineStr"/>
     </row>
@@ -5986,10 +5986,10 @@
         <v>80.88</v>
       </c>
       <c r="D262" s="5" t="n">
-        <v>81.13</v>
+        <v>82.23999999999999</v>
       </c>
       <c r="E262" s="5" t="n">
-        <v>83.05</v>
+        <v>84.19</v>
       </c>
       <c r="F262" s="7" t="inlineStr"/>
     </row>
@@ -6006,10 +6006,10 @@
         <v>99.73999999999999</v>
       </c>
       <c r="D263" s="5" t="n">
-        <v>100.89</v>
+        <v>102.28</v>
       </c>
       <c r="E263" s="5" t="n">
-        <v>102.16</v>
+        <v>103.57</v>
       </c>
       <c r="F263" s="7" t="inlineStr"/>
     </row>
@@ -6026,10 +6026,10 @@
         <v>108.25</v>
       </c>
       <c r="D264" s="5" t="n">
-        <v>97.70999999999999</v>
+        <v>99.05</v>
       </c>
       <c r="E264" s="5" t="n">
-        <v>110.6</v>
+        <v>112.12</v>
       </c>
       <c r="F264" s="7" t="inlineStr"/>
     </row>
@@ -6046,10 +6046,10 @@
         <v>252.36</v>
       </c>
       <c r="D265" s="5" t="n">
-        <v>172.59</v>
+        <v>174.97</v>
       </c>
       <c r="E265" s="5" t="n">
-        <v>257.21</v>
+        <v>260.74</v>
       </c>
       <c r="F265" s="7" t="inlineStr"/>
     </row>
@@ -6066,10 +6066,10 @@
         <v>82.66</v>
       </c>
       <c r="D266" s="5" t="n">
-        <v>83.34</v>
+        <v>84.48999999999999</v>
       </c>
       <c r="E266" s="5" t="n">
-        <v>83.88</v>
+        <v>85.03</v>
       </c>
       <c r="F266" s="7" t="inlineStr"/>
     </row>
@@ -6086,10 +6086,10 @@
         <v>73.3</v>
       </c>
       <c r="D267" s="5" t="n">
-        <v>79.01000000000001</v>
+        <v>80.09</v>
       </c>
       <c r="E267" s="5" t="n">
-        <v>74.06</v>
+        <v>75.06999999999999</v>
       </c>
       <c r="F267" s="7" t="inlineStr"/>
     </row>
@@ -6106,10 +6106,10 @@
         <v>40.87</v>
       </c>
       <c r="D268" s="5" t="n">
-        <v>54.67</v>
+        <v>55.42</v>
       </c>
       <c r="E268" s="5" t="n">
-        <v>41.11</v>
+        <v>41.68</v>
       </c>
       <c r="F268" s="7" t="inlineStr"/>
     </row>
@@ -6126,10 +6126,10 @@
         <v>45.11</v>
       </c>
       <c r="D269" s="5" t="n">
-        <v>55.88</v>
+        <v>56.65</v>
       </c>
       <c r="E269" s="5" t="n">
-        <v>45.29</v>
+        <v>45.91</v>
       </c>
       <c r="F269" s="7" t="inlineStr"/>
     </row>
@@ -6146,10 +6146,10 @@
         <v>48.44</v>
       </c>
       <c r="D270" s="5" t="n">
-        <v>63.17</v>
+        <v>64.04000000000001</v>
       </c>
       <c r="E270" s="5" t="n">
-        <v>48.54</v>
+        <v>49.2</v>
       </c>
       <c r="F270" s="7" t="inlineStr"/>
     </row>
@@ -6166,10 +6166,10 @@
         <v>46.52</v>
       </c>
       <c r="D271" s="5" t="n">
-        <v>54.38</v>
+        <v>55.13</v>
       </c>
       <c r="E271" s="5" t="n">
-        <v>46.52</v>
+        <v>47.16</v>
       </c>
       <c r="F271" s="7" t="inlineStr"/>
     </row>
@@ -6186,10 +6186,10 @@
         <v>64.54000000000001</v>
       </c>
       <c r="D272" s="5" t="n">
-        <v>64.03</v>
+        <v>64.61</v>
       </c>
       <c r="E272" s="5" t="n">
-        <v>64.54000000000001</v>
+        <v>65.13</v>
       </c>
       <c r="F272" s="7" t="inlineStr"/>
     </row>
@@ -6206,10 +6206,10 @@
         <v>72.40000000000001</v>
       </c>
       <c r="D273" s="5" t="n">
-        <v>69.87</v>
+        <v>70.19</v>
       </c>
       <c r="E273" s="5" t="n">
-        <v>72.40000000000001</v>
+        <v>72.73</v>
       </c>
       <c r="F273" s="7" t="inlineStr"/>
     </row>
@@ -6240,16 +6240,16 @@
         </is>
       </c>
       <c r="B275" s="5" t="n">
-        <v>57.69</v>
+        <v>53.31</v>
       </c>
       <c r="C275" s="5" t="n">
-        <v>51.98</v>
+        <v>45.62</v>
       </c>
       <c r="D275" s="5" t="n">
-        <v>57.69</v>
+        <v>53.31</v>
       </c>
       <c r="E275" s="5" t="n">
-        <v>51.98</v>
+        <v>45.62</v>
       </c>
       <c r="F275" s="7" t="inlineStr"/>
     </row>
@@ -6314,10 +6314,10 @@
         <v>72.18000000000001</v>
       </c>
       <c r="D2" s="5" t="n">
-        <v>80.26000000000001</v>
+        <v>81.36</v>
       </c>
       <c r="E2" s="5" t="n">
-        <v>132.32</v>
+        <v>134.14</v>
       </c>
     </row>
     <row r="3">
@@ -6333,10 +6333,10 @@
         <v>18.84</v>
       </c>
       <c r="D3" s="5" t="n">
-        <v>30.94</v>
+        <v>31.37</v>
       </c>
       <c r="E3" s="5" t="n">
-        <v>34.47</v>
+        <v>34.95</v>
       </c>
     </row>
     <row r="4">
@@ -6352,10 +6352,10 @@
         <v>18.7</v>
       </c>
       <c r="D4" s="5" t="n">
-        <v>29.31</v>
+        <v>29.72</v>
       </c>
       <c r="E4" s="5" t="n">
-        <v>34.15</v>
+        <v>34.62</v>
       </c>
     </row>
     <row r="5">
@@ -6371,10 +6371,10 @@
         <v>16.84</v>
       </c>
       <c r="D5" s="5" t="n">
-        <v>27.15</v>
+        <v>27.52</v>
       </c>
       <c r="E5" s="5" t="n">
-        <v>30.7</v>
+        <v>31.12</v>
       </c>
     </row>
     <row r="6">
@@ -6390,10 +6390,10 @@
         <v>19.15</v>
       </c>
       <c r="D6" s="5" t="n">
-        <v>37.75</v>
+        <v>38.26</v>
       </c>
       <c r="E6" s="5" t="n">
-        <v>34.85</v>
+        <v>35.33</v>
       </c>
     </row>
     <row r="7">
@@ -6409,10 +6409,10 @@
         <v>28.76</v>
       </c>
       <c r="D7" s="5" t="n">
-        <v>41.17</v>
+        <v>41.73</v>
       </c>
       <c r="E7" s="5" t="n">
-        <v>52.25</v>
+        <v>52.97</v>
       </c>
     </row>
     <row r="8">
@@ -6428,10 +6428,10 @@
         <v>26.73</v>
       </c>
       <c r="D8" s="5" t="n">
-        <v>41.79</v>
+        <v>42.36</v>
       </c>
       <c r="E8" s="5" t="n">
-        <v>48.42</v>
+        <v>49.08</v>
       </c>
     </row>
     <row r="9">
@@ -6447,10 +6447,10 @@
         <v>47.14</v>
       </c>
       <c r="D9" s="5" t="n">
-        <v>73.47</v>
+        <v>74.48</v>
       </c>
       <c r="E9" s="5" t="n">
-        <v>85.14</v>
+        <v>86.31</v>
       </c>
     </row>
     <row r="10">
@@ -6466,10 +6466,10 @@
         <v>101.08</v>
       </c>
       <c r="D10" s="5" t="n">
-        <v>100.59</v>
+        <v>101.97</v>
       </c>
       <c r="E10" s="5" t="n">
-        <v>182.02</v>
+        <v>184.52</v>
       </c>
     </row>
     <row r="11">
@@ -6485,10 +6485,10 @@
         <v>34.66</v>
       </c>
       <c r="D11" s="5" t="n">
-        <v>50.79</v>
+        <v>51.49</v>
       </c>
       <c r="E11" s="5" t="n">
-        <v>62.32</v>
+        <v>63.17</v>
       </c>
     </row>
     <row r="12">
@@ -6504,10 +6504,10 @@
         <v>33.41</v>
       </c>
       <c r="D12" s="5" t="n">
-        <v>51.88</v>
+        <v>52.59</v>
       </c>
       <c r="E12" s="5" t="n">
-        <v>59.98</v>
+        <v>60.8</v>
       </c>
     </row>
     <row r="13">
@@ -6523,10 +6523,10 @@
         <v>27.84</v>
       </c>
       <c r="D13" s="5" t="n">
-        <v>47.52</v>
+        <v>48.17</v>
       </c>
       <c r="E13" s="5" t="n">
-        <v>49.9</v>
+        <v>50.59</v>
       </c>
     </row>
     <row r="14">
@@ -6542,10 +6542,10 @@
         <v>25.42</v>
       </c>
       <c r="D14" s="5" t="n">
-        <v>45.05</v>
+        <v>45.67</v>
       </c>
       <c r="E14" s="5" t="n">
-        <v>45.5</v>
+        <v>46.13</v>
       </c>
     </row>
     <row r="15">
@@ -6561,10 +6561,10 @@
         <v>29.72</v>
       </c>
       <c r="D15" s="5" t="n">
-        <v>43.85</v>
+        <v>44.45</v>
       </c>
       <c r="E15" s="5" t="n">
-        <v>53.12</v>
+        <v>53.86</v>
       </c>
     </row>
     <row r="16">
@@ -6580,10 +6580,10 @@
         <v>32.97</v>
       </c>
       <c r="D16" s="5" t="n">
-        <v>49.36</v>
+        <v>50.04</v>
       </c>
       <c r="E16" s="5" t="n">
-        <v>58.85</v>
+        <v>59.66</v>
       </c>
     </row>
     <row r="17">
@@ -6599,10 +6599,10 @@
         <v>82.45</v>
       </c>
       <c r="D17" s="5" t="n">
-        <v>91.13</v>
+        <v>92.38</v>
       </c>
       <c r="E17" s="5" t="n">
-        <v>146.8</v>
+        <v>148.82</v>
       </c>
     </row>
     <row r="18">
@@ -6618,10 +6618,10 @@
         <v>77.28</v>
       </c>
       <c r="D18" s="5" t="n">
-        <v>90.43000000000001</v>
+        <v>91.68000000000001</v>
       </c>
       <c r="E18" s="5" t="n">
-        <v>137.25</v>
+        <v>139.14</v>
       </c>
     </row>
     <row r="19">
@@ -6637,10 +6637,10 @@
         <v>41.3</v>
       </c>
       <c r="D19" s="5" t="n">
-        <v>56.07</v>
+        <v>56.84</v>
       </c>
       <c r="E19" s="5" t="n">
-        <v>73.16</v>
+        <v>74.17</v>
       </c>
     </row>
     <row r="20">
@@ -6656,10 +6656,10 @@
         <v>27.18</v>
       </c>
       <c r="D20" s="5" t="n">
-        <v>40.44</v>
+        <v>41</v>
       </c>
       <c r="E20" s="5" t="n">
-        <v>48.04</v>
+        <v>48.7</v>
       </c>
     </row>
     <row r="21">
@@ -6675,10 +6675,10 @@
         <v>48.21</v>
       </c>
       <c r="D21" s="5" t="n">
-        <v>54.72</v>
+        <v>55.48</v>
       </c>
       <c r="E21" s="5" t="n">
-        <v>85.02</v>
+        <v>86.19</v>
       </c>
     </row>
     <row r="22">
@@ -6694,10 +6694,10 @@
         <v>18.12</v>
       </c>
       <c r="D22" s="5" t="n">
-        <v>29.18</v>
+        <v>29.58</v>
       </c>
       <c r="E22" s="5" t="n">
-        <v>31.89</v>
+        <v>32.32</v>
       </c>
     </row>
     <row r="23">
@@ -6713,10 +6713,10 @@
         <v>29.03</v>
       </c>
       <c r="D23" s="5" t="n">
-        <v>41.74</v>
+        <v>42.32</v>
       </c>
       <c r="E23" s="5" t="n">
-        <v>50.98</v>
+        <v>51.68</v>
       </c>
     </row>
     <row r="24">
@@ -6732,10 +6732,10 @@
         <v>23.51</v>
       </c>
       <c r="D24" s="5" t="n">
-        <v>36.6</v>
+        <v>37.1</v>
       </c>
       <c r="E24" s="5" t="n">
-        <v>41.21</v>
+        <v>41.77</v>
       </c>
     </row>
     <row r="25">
@@ -6751,10 +6751,10 @@
         <v>25.47</v>
       </c>
       <c r="D25" s="5" t="n">
-        <v>37.96</v>
+        <v>38.48</v>
       </c>
       <c r="E25" s="5" t="n">
-        <v>44.55</v>
+        <v>45.17</v>
       </c>
     </row>
     <row r="26">
@@ -6770,10 +6770,10 @@
         <v>20.87</v>
       </c>
       <c r="D26" s="5" t="n">
-        <v>32.34</v>
+        <v>32.79</v>
       </c>
       <c r="E26" s="5" t="n">
-        <v>36.39</v>
+        <v>36.89</v>
       </c>
     </row>
     <row r="27">
@@ -6789,10 +6789,10 @@
         <v>24.32</v>
       </c>
       <c r="D27" s="5" t="n">
-        <v>35.33</v>
+        <v>35.81</v>
       </c>
       <c r="E27" s="5" t="n">
-        <v>42.26</v>
+        <v>42.84</v>
       </c>
     </row>
     <row r="28">
@@ -6808,10 +6808,10 @@
         <v>30.66</v>
       </c>
       <c r="D28" s="5" t="n">
-        <v>41.55</v>
+        <v>42.12</v>
       </c>
       <c r="E28" s="5" t="n">
-        <v>53.1</v>
+        <v>53.83</v>
       </c>
     </row>
     <row r="29">
@@ -6827,10 +6827,10 @@
         <v>36.89</v>
       </c>
       <c r="D29" s="5" t="n">
-        <v>43.85</v>
+        <v>44.45</v>
       </c>
       <c r="E29" s="5" t="n">
-        <v>63.78</v>
+        <v>64.66</v>
       </c>
     </row>
     <row r="30">
@@ -6846,10 +6846,10 @@
         <v>24.68</v>
       </c>
       <c r="D30" s="5" t="n">
-        <v>34.25</v>
+        <v>34.72</v>
       </c>
       <c r="E30" s="5" t="n">
-        <v>42.6</v>
+        <v>43.19</v>
       </c>
     </row>
     <row r="31">
@@ -6865,10 +6865,10 @@
         <v>103.94</v>
       </c>
       <c r="D31" s="5" t="n">
-        <v>98.73</v>
+        <v>100.09</v>
       </c>
       <c r="E31" s="5" t="n">
-        <v>179.1</v>
+        <v>181.56</v>
       </c>
     </row>
     <row r="32">
@@ -6884,10 +6884,10 @@
         <v>45.52</v>
       </c>
       <c r="D32" s="5" t="n">
-        <v>51.27</v>
+        <v>51.98</v>
       </c>
       <c r="E32" s="5" t="n">
-        <v>78.20999999999999</v>
+        <v>79.29000000000001</v>
       </c>
     </row>
     <row r="33">
@@ -6903,10 +6903,10 @@
         <v>97.20999999999999</v>
       </c>
       <c r="D33" s="5" t="n">
-        <v>93.09999999999999</v>
+        <v>94.38</v>
       </c>
       <c r="E33" s="5" t="n">
-        <v>166.55</v>
+        <v>168.84</v>
       </c>
     </row>
     <row r="34">
@@ -6922,10 +6922,10 @@
         <v>24.22</v>
       </c>
       <c r="D34" s="5" t="n">
-        <v>33.61</v>
+        <v>34.07</v>
       </c>
       <c r="E34" s="5" t="n">
-        <v>41.38</v>
+        <v>41.95</v>
       </c>
     </row>
     <row r="35">
@@ -6941,10 +6941,10 @@
         <v>30.02</v>
       </c>
       <c r="D35" s="5" t="n">
-        <v>36.76</v>
+        <v>37.27</v>
       </c>
       <c r="E35" s="5" t="n">
-        <v>51.02</v>
+        <v>51.72</v>
       </c>
     </row>
     <row r="36">
@@ -6960,10 +6960,10 @@
         <v>29.88</v>
       </c>
       <c r="D36" s="5" t="n">
-        <v>39.17</v>
+        <v>39.71</v>
       </c>
       <c r="E36" s="5" t="n">
-        <v>50.52</v>
+        <v>51.21</v>
       </c>
     </row>
     <row r="37">
@@ -6979,10 +6979,10 @@
         <v>30.41</v>
       </c>
       <c r="D37" s="5" t="n">
-        <v>42.47</v>
+        <v>43.05</v>
       </c>
       <c r="E37" s="5" t="n">
-        <v>51.14</v>
+        <v>51.85</v>
       </c>
     </row>
     <row r="38">
@@ -6998,10 +6998,10 @@
         <v>42.03</v>
       </c>
       <c r="D38" s="5" t="n">
-        <v>49.5</v>
+        <v>50.18</v>
       </c>
       <c r="E38" s="5" t="n">
-        <v>70.48</v>
+        <v>71.45</v>
       </c>
     </row>
     <row r="39">
@@ -7017,10 +7017,10 @@
         <v>29.73</v>
       </c>
       <c r="D39" s="5" t="n">
-        <v>41.11</v>
+        <v>41.68</v>
       </c>
       <c r="E39" s="5" t="n">
-        <v>49.71</v>
+        <v>50.39</v>
       </c>
     </row>
     <row r="40">
@@ -7036,10 +7036,10 @@
         <v>22.14</v>
       </c>
       <c r="D40" s="5" t="n">
-        <v>32.64</v>
+        <v>33.09</v>
       </c>
       <c r="E40" s="5" t="n">
-        <v>36.91</v>
+        <v>37.42</v>
       </c>
     </row>
     <row r="41">
@@ -7055,10 +7055,10 @@
         <v>23.84</v>
       </c>
       <c r="D41" s="5" t="n">
-        <v>33.97</v>
+        <v>34.44</v>
       </c>
       <c r="E41" s="5" t="n">
-        <v>39.76</v>
+        <v>40.3</v>
       </c>
     </row>
     <row r="42">
@@ -7074,10 +7074,10 @@
         <v>33.69</v>
       </c>
       <c r="D42" s="5" t="n">
-        <v>43.59</v>
+        <v>44.19</v>
       </c>
       <c r="E42" s="5" t="n">
-        <v>56.2</v>
+        <v>56.98</v>
       </c>
     </row>
     <row r="43">
@@ -7093,10 +7093,10 @@
         <v>25.24</v>
       </c>
       <c r="D43" s="5" t="n">
-        <v>33.36</v>
+        <v>33.82</v>
       </c>
       <c r="E43" s="5" t="n">
-        <v>42.12</v>
+        <v>42.7</v>
       </c>
     </row>
     <row r="44">
@@ -7112,10 +7112,10 @@
         <v>129.47</v>
       </c>
       <c r="D44" s="5" t="n">
-        <v>122.93</v>
+        <v>124.62</v>
       </c>
       <c r="E44" s="5" t="n">
-        <v>216.02</v>
+        <v>218.99</v>
       </c>
     </row>
     <row r="45">
@@ -7131,10 +7131,10 @@
         <v>53.02</v>
       </c>
       <c r="D45" s="5" t="n">
-        <v>62.68</v>
+        <v>63.55</v>
       </c>
       <c r="E45" s="5" t="n">
-        <v>88.44</v>
+        <v>89.65000000000001</v>
       </c>
     </row>
     <row r="46">
@@ -7150,10 +7150,10 @@
         <v>62.97</v>
       </c>
       <c r="D46" s="5" t="n">
-        <v>79.33</v>
+        <v>80.42</v>
       </c>
       <c r="E46" s="5" t="n">
-        <v>105.01</v>
+        <v>106.45</v>
       </c>
     </row>
     <row r="47">
@@ -7169,10 +7169,10 @@
         <v>98.91</v>
       </c>
       <c r="D47" s="5" t="n">
-        <v>124.74</v>
+        <v>126.45</v>
       </c>
       <c r="E47" s="5" t="n">
-        <v>164.26</v>
+        <v>166.52</v>
       </c>
     </row>
     <row r="48">
@@ -7188,10 +7188,10 @@
         <v>72.97</v>
       </c>
       <c r="D48" s="5" t="n">
-        <v>101.03</v>
+        <v>102.42</v>
       </c>
       <c r="E48" s="5" t="n">
-        <v>120.69</v>
+        <v>122.35</v>
       </c>
     </row>
     <row r="49">
@@ -7207,10 +7207,10 @@
         <v>321.63</v>
       </c>
       <c r="D49" s="5" t="n">
-        <v>317.02</v>
+        <v>321.38</v>
       </c>
       <c r="E49" s="5" t="n">
-        <v>529.8200000000001</v>
+        <v>537.11</v>
       </c>
     </row>
     <row r="50">
@@ -7226,10 +7226,10 @@
         <v>94.81</v>
       </c>
       <c r="D50" s="5" t="n">
-        <v>116.48</v>
+        <v>118.08</v>
       </c>
       <c r="E50" s="5" t="n">
-        <v>155.82</v>
+        <v>157.96</v>
       </c>
     </row>
     <row r="51">
@@ -7245,10 +7245,10 @@
         <v>44.82</v>
       </c>
       <c r="D51" s="5" t="n">
-        <v>62.29</v>
+        <v>63.15</v>
       </c>
       <c r="E51" s="5" t="n">
-        <v>73.48999999999999</v>
+        <v>74.5</v>
       </c>
     </row>
     <row r="52">
@@ -7264,10 +7264,10 @@
         <v>68.55</v>
       </c>
       <c r="D52" s="5" t="n">
-        <v>83.67</v>
+        <v>84.81999999999999</v>
       </c>
       <c r="E52" s="5" t="n">
-        <v>112.15</v>
+        <v>113.69</v>
       </c>
     </row>
     <row r="53">
@@ -7283,10 +7283,10 @@
         <v>97.91</v>
       </c>
       <c r="D53" s="5" t="n">
-        <v>102.36</v>
+        <v>103.77</v>
       </c>
       <c r="E53" s="5" t="n">
-        <v>159.69</v>
+        <v>161.88</v>
       </c>
     </row>
     <row r="54">
@@ -7302,10 +7302,10 @@
         <v>50.94</v>
       </c>
       <c r="D54" s="5" t="n">
-        <v>89</v>
+        <v>90.23</v>
       </c>
       <c r="E54" s="5" t="n">
-        <v>82.81999999999999</v>
+        <v>83.95999999999999</v>
       </c>
     </row>
     <row r="55">
@@ -7321,10 +7321,10 @@
         <v>57.6</v>
       </c>
       <c r="D55" s="5" t="n">
-        <v>61.11</v>
+        <v>61.95</v>
       </c>
       <c r="E55" s="5" t="n">
-        <v>93.37</v>
+        <v>94.65000000000001</v>
       </c>
     </row>
     <row r="56">
@@ -7340,10 +7340,10 @@
         <v>75.11</v>
       </c>
       <c r="D56" s="5" t="n">
-        <v>76.59999999999999</v>
+        <v>77.66</v>
       </c>
       <c r="E56" s="5" t="n">
-        <v>121.21</v>
+        <v>122.87</v>
       </c>
     </row>
     <row r="57">
@@ -7359,10 +7359,10 @@
         <v>163.94</v>
       </c>
       <c r="D57" s="5" t="n">
-        <v>210.64</v>
+        <v>213.54</v>
       </c>
       <c r="E57" s="5" t="n">
-        <v>263.38</v>
+        <v>267.01</v>
       </c>
     </row>
     <row r="58">
@@ -7378,10 +7378,10 @@
         <v>40.15</v>
       </c>
       <c r="D58" s="5" t="n">
-        <v>46.87</v>
+        <v>47.51</v>
       </c>
       <c r="E58" s="5" t="n">
-        <v>64.22</v>
+        <v>65.09999999999999</v>
       </c>
     </row>
     <row r="59">
@@ -7397,10 +7397,10 @@
         <v>34.99</v>
       </c>
       <c r="D59" s="5" t="n">
-        <v>45.33</v>
+        <v>45.96</v>
       </c>
       <c r="E59" s="5" t="n">
-        <v>55.7</v>
+        <v>56.46</v>
       </c>
     </row>
     <row r="60">
@@ -7416,10 +7416,10 @@
         <v>46.42</v>
       </c>
       <c r="D60" s="5" t="n">
-        <v>62.38</v>
+        <v>63.24</v>
       </c>
       <c r="E60" s="5" t="n">
-        <v>73.54000000000001</v>
+        <v>74.55</v>
       </c>
     </row>
     <row r="61">
@@ -7435,10 +7435,10 @@
         <v>51.37</v>
       </c>
       <c r="D61" s="5" t="n">
-        <v>64.84999999999999</v>
+        <v>65.73999999999999</v>
       </c>
       <c r="E61" s="5" t="n">
-        <v>80.98999999999999</v>
+        <v>82.09999999999999</v>
       </c>
     </row>
     <row r="62">
@@ -7454,10 +7454,10 @@
         <v>50.74</v>
       </c>
       <c r="D62" s="5" t="n">
-        <v>57.1</v>
+        <v>57.89</v>
       </c>
       <c r="E62" s="5" t="n">
-        <v>79.69</v>
+        <v>80.78</v>
       </c>
     </row>
     <row r="63">
@@ -7473,10 +7473,10 @@
         <v>43.69</v>
       </c>
       <c r="D63" s="5" t="n">
-        <v>56.02</v>
+        <v>56.79</v>
       </c>
       <c r="E63" s="5" t="n">
-        <v>68.34999999999999</v>
+        <v>69.29000000000001</v>
       </c>
     </row>
     <row r="64">
@@ -7492,10 +7492,10 @@
         <v>37.24</v>
       </c>
       <c r="D64" s="5" t="n">
-        <v>48.14</v>
+        <v>48.8</v>
       </c>
       <c r="E64" s="5" t="n">
-        <v>58.04</v>
+        <v>58.84</v>
       </c>
     </row>
     <row r="65">
@@ -7511,10 +7511,10 @@
         <v>57.1</v>
       </c>
       <c r="D65" s="5" t="n">
-        <v>62.58</v>
+        <v>63.44</v>
       </c>
       <c r="E65" s="5" t="n">
-        <v>89.09</v>
+        <v>90.31</v>
       </c>
     </row>
     <row r="66">
@@ -7530,10 +7530,10 @@
         <v>53.97</v>
       </c>
       <c r="D66" s="5" t="n">
-        <v>58.4</v>
+        <v>59.2</v>
       </c>
       <c r="E66" s="5" t="n">
-        <v>84.3</v>
+        <v>85.45</v>
       </c>
     </row>
     <row r="67">
@@ -7549,10 +7549,10 @@
         <v>46.2</v>
       </c>
       <c r="D67" s="5" t="n">
-        <v>52.3</v>
+        <v>53.02</v>
       </c>
       <c r="E67" s="5" t="n">
-        <v>72.23999999999999</v>
+        <v>73.23</v>
       </c>
     </row>
     <row r="68">
@@ -7568,10 +7568,10 @@
         <v>58.59</v>
       </c>
       <c r="D68" s="5" t="n">
-        <v>62.96</v>
+        <v>63.82</v>
       </c>
       <c r="E68" s="5" t="n">
-        <v>91.58</v>
+        <v>92.84</v>
       </c>
     </row>
     <row r="69">
@@ -7587,10 +7587,10 @@
         <v>52.64</v>
       </c>
       <c r="D69" s="5" t="n">
-        <v>59.61</v>
+        <v>60.43</v>
       </c>
       <c r="E69" s="5" t="n">
-        <v>82.25</v>
+        <v>83.38</v>
       </c>
     </row>
     <row r="70">
@@ -7606,10 +7606,10 @@
         <v>32.61</v>
       </c>
       <c r="D70" s="5" t="n">
-        <v>40.16</v>
+        <v>40.71</v>
       </c>
       <c r="E70" s="5" t="n">
-        <v>50.93</v>
+        <v>51.63</v>
       </c>
     </row>
     <row r="71">
@@ -7625,10 +7625,10 @@
         <v>40.78</v>
       </c>
       <c r="D71" s="5" t="n">
-        <v>50.07</v>
+        <v>50.76</v>
       </c>
       <c r="E71" s="5" t="n">
-        <v>63.59</v>
+        <v>64.45999999999999</v>
       </c>
     </row>
     <row r="72">
@@ -7644,10 +7644,10 @@
         <v>32.17</v>
       </c>
       <c r="D72" s="5" t="n">
-        <v>42.39</v>
+        <v>42.97</v>
       </c>
       <c r="E72" s="5" t="n">
-        <v>50.08</v>
+        <v>50.77</v>
       </c>
     </row>
     <row r="73">
@@ -7663,10 +7663,10 @@
         <v>41.23</v>
       </c>
       <c r="D73" s="5" t="n">
-        <v>47.81</v>
+        <v>48.46</v>
       </c>
       <c r="E73" s="5" t="n">
-        <v>64.08</v>
+        <v>64.95999999999999</v>
       </c>
     </row>
     <row r="74">
@@ -7682,10 +7682,10 @@
         <v>33.09</v>
       </c>
       <c r="D74" s="5" t="n">
-        <v>42.43</v>
+        <v>43.02</v>
       </c>
       <c r="E74" s="5" t="n">
-        <v>51.27</v>
+        <v>51.97</v>
       </c>
     </row>
     <row r="75">
@@ -7701,10 +7701,10 @@
         <v>26.93</v>
       </c>
       <c r="D75" s="5" t="n">
-        <v>35.81</v>
+        <v>36.31</v>
       </c>
       <c r="E75" s="5" t="n">
-        <v>41.59</v>
+        <v>42.16</v>
       </c>
     </row>
     <row r="76">
@@ -7720,10 +7720,10 @@
         <v>27.31</v>
       </c>
       <c r="D76" s="5" t="n">
-        <v>37.78</v>
+        <v>38.3</v>
       </c>
       <c r="E76" s="5" t="n">
-        <v>42.05</v>
+        <v>42.62</v>
       </c>
     </row>
     <row r="77">
@@ -7739,10 +7739,10 @@
         <v>31.56</v>
       </c>
       <c r="D77" s="5" t="n">
-        <v>40.47</v>
+        <v>41.02</v>
       </c>
       <c r="E77" s="5" t="n">
-        <v>48.5</v>
+        <v>49.17</v>
       </c>
     </row>
     <row r="78">
@@ -7758,10 +7758,10 @@
         <v>158.57</v>
       </c>
       <c r="D78" s="5" t="n">
-        <v>129.54</v>
+        <v>131.32</v>
       </c>
       <c r="E78" s="5" t="n">
-        <v>243.26</v>
+        <v>246.61</v>
       </c>
     </row>
     <row r="79">
@@ -7777,10 +7777,10 @@
         <v>44.59</v>
       </c>
       <c r="D79" s="5" t="n">
-        <v>47.32</v>
+        <v>47.97</v>
       </c>
       <c r="E79" s="5" t="n">
-        <v>68.28</v>
+        <v>69.22</v>
       </c>
     </row>
     <row r="80">
@@ -7796,10 +7796,10 @@
         <v>101.15</v>
       </c>
       <c r="D80" s="5" t="n">
-        <v>84.97</v>
+        <v>86.14</v>
       </c>
       <c r="E80" s="5" t="n">
-        <v>154.42</v>
+        <v>156.54</v>
       </c>
     </row>
     <row r="81">
@@ -7815,10 +7815,10 @@
         <v>63.4</v>
       </c>
       <c r="D81" s="5" t="n">
-        <v>59.98</v>
+        <v>60.8</v>
       </c>
       <c r="E81" s="5" t="n">
-        <v>96.48999999999999</v>
+        <v>97.81999999999999</v>
       </c>
     </row>
     <row r="82">
@@ -7834,10 +7834,10 @@
         <v>30.36</v>
       </c>
       <c r="D82" s="5" t="n">
-        <v>36.72</v>
+        <v>37.22</v>
       </c>
       <c r="E82" s="5" t="n">
-        <v>46.06</v>
+        <v>46.7</v>
       </c>
     </row>
     <row r="83">
@@ -7853,10 +7853,10 @@
         <v>22.61</v>
       </c>
       <c r="D83" s="5" t="n">
-        <v>32.16</v>
+        <v>32.6</v>
       </c>
       <c r="E83" s="5" t="n">
-        <v>34.24</v>
+        <v>34.71</v>
       </c>
     </row>
     <row r="84">
@@ -7872,10 +7872,10 @@
         <v>24.98</v>
       </c>
       <c r="D84" s="5" t="n">
-        <v>31.67</v>
+        <v>32.11</v>
       </c>
       <c r="E84" s="5" t="n">
-        <v>37.75</v>
+        <v>38.27</v>
       </c>
     </row>
     <row r="85">
@@ -7891,10 +7891,10 @@
         <v>25.37</v>
       </c>
       <c r="D85" s="5" t="n">
-        <v>33.98</v>
+        <v>34.45</v>
       </c>
       <c r="E85" s="5" t="n">
-        <v>38.26</v>
+        <v>38.79</v>
       </c>
     </row>
     <row r="86">
@@ -7910,10 +7910,10 @@
         <v>24.17</v>
       </c>
       <c r="D86" s="5" t="n">
-        <v>31.49</v>
+        <v>31.92</v>
       </c>
       <c r="E86" s="5" t="n">
-        <v>36.36</v>
+        <v>36.86</v>
       </c>
     </row>
     <row r="87">
@@ -7929,10 +7929,10 @@
         <v>22.64</v>
       </c>
       <c r="D87" s="5" t="n">
-        <v>31.88</v>
+        <v>32.32</v>
       </c>
       <c r="E87" s="5" t="n">
-        <v>33.98</v>
+        <v>34.45</v>
       </c>
     </row>
     <row r="88">
@@ -7948,10 +7948,10 @@
         <v>23.3</v>
       </c>
       <c r="D88" s="5" t="n">
-        <v>31.74</v>
+        <v>32.18</v>
       </c>
       <c r="E88" s="5" t="n">
-        <v>34.89</v>
+        <v>35.37</v>
       </c>
     </row>
     <row r="89">
@@ -7967,10 +7967,10 @@
         <v>22.29</v>
       </c>
       <c r="D89" s="5" t="n">
-        <v>29.91</v>
+        <v>30.32</v>
       </c>
       <c r="E89" s="5" t="n">
-        <v>33.33</v>
+        <v>33.79</v>
       </c>
     </row>
     <row r="90">
@@ -7986,10 +7986,10 @@
         <v>20.14</v>
       </c>
       <c r="D90" s="5" t="n">
-        <v>26.34</v>
+        <v>26.71</v>
       </c>
       <c r="E90" s="5" t="n">
-        <v>30.08</v>
+        <v>30.49</v>
       </c>
     </row>
     <row r="91">
@@ -8005,10 +8005,10 @@
         <v>26.94</v>
       </c>
       <c r="D91" s="5" t="n">
-        <v>32.93</v>
+        <v>33.39</v>
       </c>
       <c r="E91" s="5" t="n">
-        <v>40.18</v>
+        <v>40.73</v>
       </c>
     </row>
     <row r="92">
@@ -8024,10 +8024,10 @@
         <v>68.84</v>
       </c>
       <c r="D92" s="5" t="n">
-        <v>64.81999999999999</v>
+        <v>65.70999999999999</v>
       </c>
       <c r="E92" s="5" t="n">
-        <v>102.15</v>
+        <v>103.56</v>
       </c>
     </row>
     <row r="93">
@@ -8043,10 +8043,10 @@
         <v>196.36</v>
       </c>
       <c r="D93" s="5" t="n">
-        <v>155.99</v>
+        <v>158.13</v>
       </c>
       <c r="E93" s="5" t="n">
-        <v>289.89</v>
+        <v>293.88</v>
       </c>
     </row>
     <row r="94">
@@ -8062,10 +8062,10 @@
         <v>31.68</v>
       </c>
       <c r="D94" s="5" t="n">
-        <v>40.29</v>
+        <v>40.84</v>
       </c>
       <c r="E94" s="5" t="n">
-        <v>46.53</v>
+        <v>47.17</v>
       </c>
     </row>
     <row r="95">
@@ -8081,10 +8081,10 @@
         <v>26.61</v>
       </c>
       <c r="D95" s="5" t="n">
-        <v>36.65</v>
+        <v>37.16</v>
       </c>
       <c r="E95" s="5" t="n">
-        <v>38.97</v>
+        <v>39.5</v>
       </c>
     </row>
     <row r="96">
@@ -8100,10 +8100,10 @@
         <v>29.09</v>
       </c>
       <c r="D96" s="5" t="n">
-        <v>40.13</v>
+        <v>40.68</v>
       </c>
       <c r="E96" s="5" t="n">
-        <v>42.47</v>
+        <v>43.05</v>
       </c>
     </row>
     <row r="97">
@@ -8119,10 +8119,10 @@
         <v>28.39</v>
       </c>
       <c r="D97" s="5" t="n">
-        <v>36.85</v>
+        <v>37.36</v>
       </c>
       <c r="E97" s="5" t="n">
-        <v>41.32</v>
+        <v>41.89</v>
       </c>
     </row>
     <row r="98">
@@ -8138,10 +8138,10 @@
         <v>30.87</v>
       </c>
       <c r="D98" s="5" t="n">
-        <v>38.43</v>
+        <v>38.96</v>
       </c>
       <c r="E98" s="5" t="n">
-        <v>44.84</v>
+        <v>45.46</v>
       </c>
     </row>
     <row r="99">
@@ -8157,10 +8157,10 @@
         <v>32.03</v>
       </c>
       <c r="D99" s="5" t="n">
-        <v>41.88</v>
+        <v>42.46</v>
       </c>
       <c r="E99" s="5" t="n">
-        <v>46.43</v>
+        <v>47.07</v>
       </c>
     </row>
     <row r="100">
@@ -8176,10 +8176,10 @@
         <v>33.77</v>
       </c>
       <c r="D100" s="5" t="n">
-        <v>41.75</v>
+        <v>42.33</v>
       </c>
       <c r="E100" s="5" t="n">
-        <v>48.86</v>
+        <v>49.53</v>
       </c>
     </row>
     <row r="101">
@@ -8195,10 +8195,10 @@
         <v>30.07</v>
       </c>
       <c r="D101" s="5" t="n">
-        <v>39.5</v>
+        <v>40.04</v>
       </c>
       <c r="E101" s="5" t="n">
-        <v>43.5</v>
+        <v>44.1</v>
       </c>
     </row>
     <row r="102">
@@ -8214,10 +8214,10 @@
         <v>42.54</v>
       </c>
       <c r="D102" s="5" t="n">
-        <v>48.54</v>
+        <v>49.21</v>
       </c>
       <c r="E102" s="5" t="n">
-        <v>61.55</v>
+        <v>62.39</v>
       </c>
     </row>
     <row r="103">
@@ -8233,10 +8233,10 @@
         <v>28.15</v>
       </c>
       <c r="D103" s="5" t="n">
-        <v>36.99</v>
+        <v>37.5</v>
       </c>
       <c r="E103" s="5" t="n">
-        <v>40.73</v>
+        <v>41.29</v>
       </c>
     </row>
     <row r="104">
@@ -8252,10 +8252,10 @@
         <v>41.84</v>
       </c>
       <c r="D104" s="5" t="n">
-        <v>46.61</v>
+        <v>47.25</v>
       </c>
       <c r="E104" s="5" t="n">
-        <v>60.52</v>
+        <v>61.35</v>
       </c>
     </row>
     <row r="105">
@@ -8271,10 +8271,10 @@
         <v>37.94</v>
       </c>
       <c r="D105" s="5" t="n">
-        <v>43.46</v>
+        <v>44.06</v>
       </c>
       <c r="E105" s="5" t="n">
-        <v>54.87</v>
+        <v>55.62</v>
       </c>
     </row>
     <row r="106">
@@ -8290,10 +8290,10 @@
         <v>31.14</v>
       </c>
       <c r="D106" s="5" t="n">
-        <v>39.32</v>
+        <v>39.86</v>
       </c>
       <c r="E106" s="5" t="n">
-        <v>45.03</v>
+        <v>45.65</v>
       </c>
     </row>
     <row r="107">
@@ -8309,10 +8309,10 @@
         <v>32.17</v>
       </c>
       <c r="D107" s="5" t="n">
-        <v>42.15</v>
+        <v>42.73</v>
       </c>
       <c r="E107" s="5" t="n">
-        <v>46.44</v>
+        <v>47.07</v>
       </c>
     </row>
     <row r="108">
@@ -8328,10 +8328,10 @@
         <v>27.95</v>
       </c>
       <c r="D108" s="5" t="n">
-        <v>36.95</v>
+        <v>37.45</v>
       </c>
       <c r="E108" s="5" t="n">
-        <v>40.27</v>
+        <v>40.83</v>
       </c>
     </row>
     <row r="109">
@@ -8347,10 +8347,10 @@
         <v>39.25</v>
       </c>
       <c r="D109" s="5" t="n">
-        <v>49.34</v>
+        <v>50.02</v>
       </c>
       <c r="E109" s="5" t="n">
-        <v>56.46</v>
+        <v>57.24</v>
       </c>
     </row>
     <row r="110">
@@ -8366,10 +8366,10 @@
         <v>71.37</v>
       </c>
       <c r="D110" s="5" t="n">
-        <v>91.02</v>
+        <v>92.27</v>
       </c>
       <c r="E110" s="5" t="n">
-        <v>102.2</v>
+        <v>103.61</v>
       </c>
     </row>
     <row r="111">
@@ -8385,10 +8385,10 @@
         <v>58.94</v>
       </c>
       <c r="D111" s="5" t="n">
-        <v>76.58</v>
+        <v>77.63</v>
       </c>
       <c r="E111" s="5" t="n">
-        <v>84.02</v>
+        <v>85.18000000000001</v>
       </c>
     </row>
     <row r="112">
@@ -8404,10 +8404,10 @@
         <v>56.11</v>
       </c>
       <c r="D112" s="5" t="n">
-        <v>74.72</v>
+        <v>75.75</v>
       </c>
       <c r="E112" s="5" t="n">
-        <v>79.63</v>
+        <v>80.72</v>
       </c>
     </row>
     <row r="113">
@@ -8423,10 +8423,10 @@
         <v>54.75</v>
       </c>
       <c r="D113" s="5" t="n">
-        <v>74.45999999999999</v>
+        <v>75.48</v>
       </c>
       <c r="E113" s="5" t="n">
-        <v>77.63</v>
+        <v>78.7</v>
       </c>
     </row>
     <row r="114">
@@ -8442,10 +8442,10 @@
         <v>60.67</v>
       </c>
       <c r="D114" s="5" t="n">
-        <v>76.79000000000001</v>
+        <v>77.84</v>
       </c>
       <c r="E114" s="5" t="n">
-        <v>85.95</v>
+        <v>87.14</v>
       </c>
     </row>
     <row r="115">
@@ -8461,10 +8461,10 @@
         <v>73.14</v>
       </c>
       <c r="D115" s="5" t="n">
-        <v>83.73</v>
+        <v>84.88</v>
       </c>
       <c r="E115" s="5" t="n">
-        <v>103.53</v>
+        <v>104.96</v>
       </c>
     </row>
     <row r="116">
@@ -8480,10 +8480,10 @@
         <v>178.66</v>
       </c>
       <c r="D116" s="5" t="n">
-        <v>220.44</v>
+        <v>223.47</v>
       </c>
       <c r="E116" s="5" t="n">
-        <v>252.62</v>
+        <v>256.09</v>
       </c>
     </row>
     <row r="117">
@@ -8499,10 +8499,10 @@
         <v>69.16</v>
       </c>
       <c r="D117" s="5" t="n">
-        <v>83.12</v>
+        <v>84.26000000000001</v>
       </c>
       <c r="E117" s="5" t="n">
-        <v>97.68000000000001</v>
+        <v>99.02</v>
       </c>
     </row>
     <row r="118">
@@ -8518,10 +8518,10 @@
         <v>80.01000000000001</v>
       </c>
       <c r="D118" s="5" t="n">
-        <v>104.11</v>
+        <v>105.55</v>
       </c>
       <c r="E118" s="5" t="n">
-        <v>112.88</v>
+        <v>114.43</v>
       </c>
     </row>
     <row r="119">
@@ -8537,10 +8537,10 @@
         <v>60.49</v>
       </c>
       <c r="D119" s="5" t="n">
-        <v>78.06</v>
+        <v>79.13</v>
       </c>
       <c r="E119" s="5" t="n">
-        <v>85.23</v>
+        <v>86.40000000000001</v>
       </c>
     </row>
     <row r="120">
@@ -8556,10 +8556,10 @@
         <v>65.18000000000001</v>
       </c>
       <c r="D120" s="5" t="n">
-        <v>81.45999999999999</v>
+        <v>82.58</v>
       </c>
       <c r="E120" s="5" t="n">
-        <v>91.72</v>
+        <v>92.98</v>
       </c>
     </row>
     <row r="121">
@@ -8575,10 +8575,10 @@
         <v>77.73999999999999</v>
       </c>
       <c r="D121" s="5" t="n">
-        <v>90.56999999999999</v>
+        <v>91.81</v>
       </c>
       <c r="E121" s="5" t="n">
-        <v>109.26</v>
+        <v>110.76</v>
       </c>
     </row>
     <row r="122">
@@ -8594,10 +8594,10 @@
         <v>64.43000000000001</v>
       </c>
       <c r="D122" s="5" t="n">
-        <v>85.3</v>
+        <v>86.47</v>
       </c>
       <c r="E122" s="5" t="n">
-        <v>90.19</v>
+        <v>91.43000000000001</v>
       </c>
     </row>
     <row r="123">
@@ -8613,10 +8613,10 @@
         <v>71.94</v>
       </c>
       <c r="D123" s="5" t="n">
-        <v>85.47</v>
+        <v>86.65000000000001</v>
       </c>
       <c r="E123" s="5" t="n">
-        <v>100.29</v>
+        <v>101.67</v>
       </c>
     </row>
     <row r="124">
@@ -8632,10 +8632,10 @@
         <v>62.27</v>
       </c>
       <c r="D124" s="5" t="n">
-        <v>77.87</v>
+        <v>78.94</v>
       </c>
       <c r="E124" s="5" t="n">
-        <v>86.45999999999999</v>
+        <v>87.65000000000001</v>
       </c>
     </row>
     <row r="125">
@@ -8651,10 +8651,10 @@
         <v>67.76000000000001</v>
       </c>
       <c r="D125" s="5" t="n">
-        <v>85</v>
+        <v>86.16</v>
       </c>
       <c r="E125" s="5" t="n">
-        <v>93.86</v>
+        <v>95.15000000000001</v>
       </c>
     </row>
     <row r="126">
@@ -8670,10 +8670,10 @@
         <v>59.33</v>
       </c>
       <c r="D126" s="5" t="n">
-        <v>75.22</v>
+        <v>76.25</v>
       </c>
       <c r="E126" s="5" t="n">
-        <v>81.98999999999999</v>
+        <v>83.11</v>
       </c>
     </row>
     <row r="127">
@@ -8689,10 +8689,10 @@
         <v>61.95</v>
       </c>
       <c r="D127" s="5" t="n">
-        <v>80.29000000000001</v>
+        <v>81.39</v>
       </c>
       <c r="E127" s="5" t="n">
-        <v>85.40000000000001</v>
+        <v>86.58</v>
       </c>
     </row>
     <row r="128">
@@ -8708,10 +8708,10 @@
         <v>84.06999999999999</v>
       </c>
       <c r="D128" s="5" t="n">
-        <v>97.83</v>
+        <v>99.17</v>
       </c>
       <c r="E128" s="5" t="n">
-        <v>115.67</v>
+        <v>117.26</v>
       </c>
     </row>
     <row r="129">
@@ -8727,10 +8727,10 @@
         <v>108.19</v>
       </c>
       <c r="D129" s="5" t="n">
-        <v>106.87</v>
+        <v>108.34</v>
       </c>
       <c r="E129" s="5" t="n">
-        <v>148.56</v>
+        <v>150.61</v>
       </c>
     </row>
     <row r="130">
@@ -8746,10 +8746,10 @@
         <v>55.81</v>
       </c>
       <c r="D130" s="5" t="n">
-        <v>68.09</v>
+        <v>69.02</v>
       </c>
       <c r="E130" s="5" t="n">
-        <v>76.48999999999999</v>
+        <v>77.54000000000001</v>
       </c>
     </row>
     <row r="131">
@@ -8765,10 +8765,10 @@
         <v>52.99</v>
       </c>
       <c r="D131" s="5" t="n">
-        <v>67.38</v>
+        <v>68.31</v>
       </c>
       <c r="E131" s="5" t="n">
-        <v>72.5</v>
+        <v>73.5</v>
       </c>
     </row>
     <row r="132">
@@ -8784,10 +8784,10 @@
         <v>56.78</v>
       </c>
       <c r="D132" s="5" t="n">
-        <v>69.73</v>
+        <v>70.69</v>
       </c>
       <c r="E132" s="5" t="n">
-        <v>77.56</v>
+        <v>78.62</v>
       </c>
     </row>
     <row r="133">
@@ -8803,10 +8803,10 @@
         <v>58.65</v>
       </c>
       <c r="D133" s="5" t="n">
-        <v>69.43000000000001</v>
+        <v>70.39</v>
       </c>
       <c r="E133" s="5" t="n">
-        <v>79.98</v>
+        <v>81.08</v>
       </c>
     </row>
     <row r="134">
@@ -8822,10 +8822,10 @@
         <v>37.69</v>
       </c>
       <c r="D134" s="5" t="n">
-        <v>44.66</v>
+        <v>45.28</v>
       </c>
       <c r="E134" s="5" t="n">
-        <v>51.32</v>
+        <v>52.03</v>
       </c>
     </row>
     <row r="135">
@@ -8841,10 +8841,10 @@
         <v>29.9</v>
       </c>
       <c r="D135" s="5" t="n">
-        <v>35.25</v>
+        <v>35.73</v>
       </c>
       <c r="E135" s="5" t="n">
-        <v>40.66</v>
+        <v>41.22</v>
       </c>
     </row>
     <row r="136">
@@ -8860,10 +8860,10 @@
         <v>42.79</v>
       </c>
       <c r="D136" s="5" t="n">
-        <v>45.86</v>
+        <v>46.49</v>
       </c>
       <c r="E136" s="5" t="n">
-        <v>58.1</v>
+        <v>58.9</v>
       </c>
     </row>
     <row r="137">
@@ -8879,10 +8879,10 @@
         <v>27.94</v>
       </c>
       <c r="D137" s="5" t="n">
-        <v>31.82</v>
+        <v>32.26</v>
       </c>
       <c r="E137" s="5" t="n">
-        <v>37.92</v>
+        <v>38.44</v>
       </c>
     </row>
     <row r="138">
@@ -8898,10 +8898,10 @@
         <v>57.77</v>
       </c>
       <c r="D138" s="5" t="n">
-        <v>53.5</v>
+        <v>54.24</v>
       </c>
       <c r="E138" s="5" t="n">
-        <v>78.34999999999999</v>
+        <v>79.42</v>
       </c>
     </row>
     <row r="139">
@@ -8917,10 +8917,10 @@
         <v>204.51</v>
       </c>
       <c r="D139" s="5" t="n">
-        <v>145.41</v>
+        <v>147.41</v>
       </c>
       <c r="E139" s="5" t="n">
-        <v>277.17</v>
+        <v>280.99</v>
       </c>
     </row>
     <row r="140">
@@ -8936,10 +8936,10 @@
         <v>185.37</v>
       </c>
       <c r="D140" s="5" t="n">
-        <v>158.93</v>
+        <v>161.12</v>
       </c>
       <c r="E140" s="5" t="n">
-        <v>251.08</v>
+        <v>254.53</v>
       </c>
     </row>
     <row r="141">
@@ -8955,10 +8955,10 @@
         <v>42.71</v>
       </c>
       <c r="D141" s="5" t="n">
-        <v>45.71</v>
+        <v>46.34</v>
       </c>
       <c r="E141" s="5" t="n">
-        <v>57.81</v>
+        <v>58.61</v>
       </c>
     </row>
     <row r="142">
@@ -8974,10 +8974,10 @@
         <v>218.4</v>
       </c>
       <c r="D142" s="5" t="n">
-        <v>159.11</v>
+        <v>161.3</v>
       </c>
       <c r="E142" s="5" t="n">
-        <v>295.44</v>
+        <v>299.5</v>
       </c>
     </row>
     <row r="143">
@@ -8993,10 +8993,10 @@
         <v>37.91</v>
       </c>
       <c r="D143" s="5" t="n">
-        <v>43.25</v>
+        <v>43.85</v>
       </c>
       <c r="E143" s="5" t="n">
-        <v>51.16</v>
+        <v>51.86</v>
       </c>
     </row>
     <row r="144">
@@ -9012,10 +9012,10 @@
         <v>34.67</v>
       </c>
       <c r="D144" s="5" t="n">
-        <v>41.92</v>
+        <v>42.5</v>
       </c>
       <c r="E144" s="5" t="n">
-        <v>46.68</v>
+        <v>47.32</v>
       </c>
     </row>
     <row r="145">
@@ -9031,10 +9031,10 @@
         <v>37.13</v>
       </c>
       <c r="D145" s="5" t="n">
-        <v>42.32</v>
+        <v>42.9</v>
       </c>
       <c r="E145" s="5" t="n">
-        <v>49.87</v>
+        <v>50.56</v>
       </c>
     </row>
     <row r="146">
@@ -9050,10 +9050,10 @@
         <v>58.91</v>
       </c>
       <c r="D146" s="5" t="n">
-        <v>62.59</v>
+        <v>63.45</v>
       </c>
       <c r="E146" s="5" t="n">
-        <v>79.02</v>
+        <v>80.11</v>
       </c>
     </row>
     <row r="147">
@@ -9069,10 +9069,10 @@
         <v>50.96</v>
       </c>
       <c r="D147" s="5" t="n">
-        <v>53.98</v>
+        <v>54.72</v>
       </c>
       <c r="E147" s="5" t="n">
-        <v>68.27</v>
+        <v>69.20999999999999</v>
       </c>
     </row>
     <row r="148">
@@ -9088,10 +9088,10 @@
         <v>48.15</v>
       </c>
       <c r="D148" s="5" t="n">
-        <v>59.93</v>
+        <v>60.75</v>
       </c>
       <c r="E148" s="5" t="n">
-        <v>64.42</v>
+        <v>65.31</v>
       </c>
     </row>
     <row r="149">
@@ -9107,10 +9107,10 @@
         <v>41.6</v>
       </c>
       <c r="D149" s="5" t="n">
-        <v>48.76</v>
+        <v>49.43</v>
       </c>
       <c r="E149" s="5" t="n">
-        <v>55.59</v>
+        <v>56.35</v>
       </c>
     </row>
     <row r="150">
@@ -9126,10 +9126,10 @@
         <v>61.27</v>
       </c>
       <c r="D150" s="5" t="n">
-        <v>60.45</v>
+        <v>61.29</v>
       </c>
       <c r="E150" s="5" t="n">
-        <v>81.77</v>
+        <v>82.89</v>
       </c>
     </row>
     <row r="151">
@@ -9145,10 +9145,10 @@
         <v>49.59</v>
       </c>
       <c r="D151" s="5" t="n">
-        <v>57.42</v>
+        <v>58.21</v>
       </c>
       <c r="E151" s="5" t="n">
-        <v>66.09</v>
+        <v>67</v>
       </c>
     </row>
     <row r="152">
@@ -9164,10 +9164,10 @@
         <v>71.04000000000001</v>
       </c>
       <c r="D152" s="5" t="n">
-        <v>68.75</v>
+        <v>69.7</v>
       </c>
       <c r="E152" s="5" t="n">
-        <v>94.75</v>
+        <v>96.05</v>
       </c>
     </row>
     <row r="153">
@@ -9183,10 +9183,10 @@
         <v>210.46</v>
       </c>
       <c r="D153" s="5" t="n">
-        <v>161.9</v>
+        <v>164.12</v>
       </c>
       <c r="E153" s="5" t="n">
-        <v>280.87</v>
+        <v>284.74</v>
       </c>
     </row>
     <row r="154">
@@ -9202,10 +9202,10 @@
         <v>90.26000000000001</v>
       </c>
       <c r="D154" s="5" t="n">
-        <v>94.86</v>
+        <v>96.16</v>
       </c>
       <c r="E154" s="5" t="n">
-        <v>120.54</v>
+        <v>122.2</v>
       </c>
     </row>
     <row r="155">
@@ -9221,10 +9221,10 @@
         <v>79.34999999999999</v>
       </c>
       <c r="D155" s="5" t="n">
-        <v>88.67</v>
+        <v>89.88</v>
       </c>
       <c r="E155" s="5" t="n">
-        <v>105.81</v>
+        <v>107.27</v>
       </c>
     </row>
     <row r="156">
@@ -9240,10 +9240,10 @@
         <v>86.59999999999999</v>
       </c>
       <c r="D156" s="5" t="n">
-        <v>92.41</v>
+        <v>93.68000000000001</v>
       </c>
       <c r="E156" s="5" t="n">
-        <v>115.31</v>
+        <v>116.9</v>
       </c>
     </row>
     <row r="157">
@@ -9259,10 +9259,10 @@
         <v>107.25</v>
       </c>
       <c r="D157" s="5" t="n">
-        <v>116.38</v>
+        <v>117.98</v>
       </c>
       <c r="E157" s="5" t="n">
-        <v>142.6</v>
+        <v>144.56</v>
       </c>
     </row>
     <row r="158">
@@ -9278,10 +9278,10 @@
         <v>80.31999999999999</v>
       </c>
       <c r="D158" s="5" t="n">
-        <v>80.81</v>
+        <v>81.92</v>
       </c>
       <c r="E158" s="5" t="n">
-        <v>106.55</v>
+        <v>108.01</v>
       </c>
     </row>
     <row r="159">
@@ -9297,10 +9297,10 @@
         <v>59.15</v>
       </c>
       <c r="D159" s="5" t="n">
-        <v>63.47</v>
+        <v>64.34</v>
       </c>
       <c r="E159" s="5" t="n">
-        <v>78.28</v>
+        <v>79.36</v>
       </c>
     </row>
     <row r="160">
@@ -9316,10 +9316,10 @@
         <v>52.96</v>
       </c>
       <c r="D160" s="5" t="n">
-        <v>60.82</v>
+        <v>61.65</v>
       </c>
       <c r="E160" s="5" t="n">
-        <v>69.93000000000001</v>
+        <v>70.89</v>
       </c>
     </row>
     <row r="161">
@@ -9335,10 +9335,10 @@
         <v>60.77</v>
       </c>
       <c r="D161" s="5" t="n">
-        <v>70.81999999999999</v>
+        <v>71.79000000000001</v>
       </c>
       <c r="E161" s="5" t="n">
-        <v>80.09999999999999</v>
+        <v>81.2</v>
       </c>
     </row>
     <row r="162">
@@ -9354,10 +9354,10 @@
         <v>87.69</v>
       </c>
       <c r="D162" s="5" t="n">
-        <v>91.36</v>
+        <v>92.62</v>
       </c>
       <c r="E162" s="5" t="n">
-        <v>115.38</v>
+        <v>116.96</v>
       </c>
     </row>
     <row r="163">
@@ -9373,10 +9373,10 @@
         <v>79.92</v>
       </c>
       <c r="D163" s="5" t="n">
-        <v>88.39</v>
+        <v>89.61</v>
       </c>
       <c r="E163" s="5" t="n">
-        <v>104.97</v>
+        <v>106.41</v>
       </c>
     </row>
     <row r="164">
@@ -9392,10 +9392,10 @@
         <v>232.26</v>
       </c>
       <c r="D164" s="5" t="n">
-        <v>259.2</v>
+        <v>262.77</v>
       </c>
       <c r="E164" s="5" t="n">
-        <v>304.59</v>
+        <v>308.78</v>
       </c>
     </row>
     <row r="165">
@@ -9411,10 +9411,10 @@
         <v>308.3</v>
       </c>
       <c r="D165" s="5" t="n">
-        <v>313.73</v>
+        <v>318.04</v>
       </c>
       <c r="E165" s="5" t="n">
-        <v>403.7</v>
+        <v>409.25</v>
       </c>
     </row>
     <row r="166">
@@ -9430,10 +9430,10 @@
         <v>105.94</v>
       </c>
       <c r="D166" s="5" t="n">
-        <v>116.04</v>
+        <v>117.63</v>
       </c>
       <c r="E166" s="5" t="n">
-        <v>138.51</v>
+        <v>140.42</v>
       </c>
     </row>
     <row r="167">
@@ -9449,10 +9449,10 @@
         <v>103.48</v>
       </c>
       <c r="D167" s="5" t="n">
-        <v>123.81</v>
+        <v>125.52</v>
       </c>
       <c r="E167" s="5" t="n">
-        <v>135.21</v>
+        <v>137.07</v>
       </c>
     </row>
     <row r="168">
@@ -9468,10 +9468,10 @@
         <v>93.61</v>
       </c>
       <c r="D168" s="5" t="n">
-        <v>112.63</v>
+        <v>114.18</v>
       </c>
       <c r="E168" s="5" t="n">
-        <v>122.23</v>
+        <v>123.91</v>
       </c>
     </row>
     <row r="169">
@@ -9487,10 +9487,10 @@
         <v>83.23</v>
       </c>
       <c r="D169" s="5" t="n">
-        <v>99.77</v>
+        <v>101.14</v>
       </c>
       <c r="E169" s="5" t="n">
-        <v>108.61</v>
+        <v>110.1</v>
       </c>
     </row>
     <row r="170">
@@ -9506,10 +9506,10 @@
         <v>87.06999999999999</v>
       </c>
       <c r="D170" s="5" t="n">
-        <v>101.05</v>
+        <v>102.44</v>
       </c>
       <c r="E170" s="5" t="n">
-        <v>113.39</v>
+        <v>114.95</v>
       </c>
     </row>
     <row r="171">
@@ -9525,10 +9525,10 @@
         <v>92.38</v>
       </c>
       <c r="D171" s="5" t="n">
-        <v>106.15</v>
+        <v>107.61</v>
       </c>
       <c r="E171" s="5" t="n">
-        <v>120.06</v>
+        <v>121.71</v>
       </c>
     </row>
     <row r="172">
@@ -9544,10 +9544,10 @@
         <v>87.77</v>
       </c>
       <c r="D172" s="5" t="n">
-        <v>104.46</v>
+        <v>105.89</v>
       </c>
       <c r="E172" s="5" t="n">
-        <v>113.83</v>
+        <v>115.4</v>
       </c>
     </row>
     <row r="173">
@@ -9563,10 +9563,10 @@
         <v>89.16</v>
       </c>
       <c r="D173" s="5" t="n">
-        <v>101.22</v>
+        <v>102.61</v>
       </c>
       <c r="E173" s="5" t="n">
-        <v>115.38</v>
+        <v>116.97</v>
       </c>
     </row>
     <row r="174">
@@ -9582,10 +9582,10 @@
         <v>72.36</v>
       </c>
       <c r="D174" s="5" t="n">
-        <v>84.40000000000001</v>
+        <v>85.56999999999999</v>
       </c>
       <c r="E174" s="5" t="n">
-        <v>93.43000000000001</v>
+        <v>94.70999999999999</v>
       </c>
     </row>
     <row r="175">
@@ -9601,10 +9601,10 @@
         <v>81.22</v>
       </c>
       <c r="D175" s="5" t="n">
-        <v>92.15000000000001</v>
+        <v>93.42</v>
       </c>
       <c r="E175" s="5" t="n">
-        <v>104.64</v>
+        <v>106.08</v>
       </c>
     </row>
     <row r="176">
@@ -9620,10 +9620,10 @@
         <v>82.28</v>
       </c>
       <c r="D176" s="5" t="n">
-        <v>97.48999999999999</v>
+        <v>98.83</v>
       </c>
       <c r="E176" s="5" t="n">
-        <v>105.85</v>
+        <v>107.3</v>
       </c>
     </row>
     <row r="177">
@@ -9639,10 +9639,10 @@
         <v>83.44</v>
       </c>
       <c r="D177" s="5" t="n">
-        <v>92.28</v>
+        <v>93.55</v>
       </c>
       <c r="E177" s="5" t="n">
-        <v>107.18</v>
+        <v>108.66</v>
       </c>
     </row>
     <row r="178">
@@ -9658,10 +9658,10 @@
         <v>66.75</v>
       </c>
       <c r="D178" s="5" t="n">
-        <v>80.20999999999999</v>
+        <v>81.31</v>
       </c>
       <c r="E178" s="5" t="n">
-        <v>85.62</v>
+        <v>86.8</v>
       </c>
     </row>
     <row r="179">
@@ -9677,10 +9677,10 @@
         <v>69.11</v>
       </c>
       <c r="D179" s="5" t="n">
-        <v>81.64</v>
+        <v>82.76000000000001</v>
       </c>
       <c r="E179" s="5" t="n">
-        <v>88.54000000000001</v>
+        <v>89.76000000000001</v>
       </c>
     </row>
     <row r="180">
@@ -9696,10 +9696,10 @@
         <v>72.86</v>
       </c>
       <c r="D180" s="5" t="n">
-        <v>83.28</v>
+        <v>84.42</v>
       </c>
       <c r="E180" s="5" t="n">
-        <v>93.23999999999999</v>
+        <v>94.52</v>
       </c>
     </row>
     <row r="181">
@@ -9715,10 +9715,10 @@
         <v>96.17</v>
       </c>
       <c r="D181" s="5" t="n">
-        <v>102.79</v>
+        <v>104.2</v>
       </c>
       <c r="E181" s="5" t="n">
-        <v>122.92</v>
+        <v>124.61</v>
       </c>
     </row>
     <row r="182">
@@ -9734,10 +9734,10 @@
         <v>77.84</v>
       </c>
       <c r="D182" s="5" t="n">
-        <v>88.22</v>
+        <v>89.43000000000001</v>
       </c>
       <c r="E182" s="5" t="n">
-        <v>99.34999999999999</v>
+        <v>100.71</v>
       </c>
     </row>
     <row r="183">
@@ -9753,10 +9753,10 @@
         <v>94.70999999999999</v>
       </c>
       <c r="D183" s="5" t="n">
-        <v>105.13</v>
+        <v>106.58</v>
       </c>
       <c r="E183" s="5" t="n">
-        <v>120.7</v>
+        <v>122.36</v>
       </c>
     </row>
     <row r="184">
@@ -9772,10 +9772,10 @@
         <v>92.73999999999999</v>
       </c>
       <c r="D184" s="5" t="n">
-        <v>102.57</v>
+        <v>103.98</v>
       </c>
       <c r="E184" s="5" t="n">
-        <v>118.02</v>
+        <v>119.65</v>
       </c>
     </row>
     <row r="185">
@@ -9791,10 +9791,10 @@
         <v>89.22</v>
       </c>
       <c r="D185" s="5" t="n">
-        <v>99.52</v>
+        <v>100.89</v>
       </c>
       <c r="E185" s="5" t="n">
-        <v>113.35</v>
+        <v>114.91</v>
       </c>
     </row>
     <row r="186">
@@ -9810,10 +9810,10 @@
         <v>105.34</v>
       </c>
       <c r="D186" s="5" t="n">
-        <v>112.69</v>
+        <v>114.24</v>
       </c>
       <c r="E186" s="5" t="n">
-        <v>133.59</v>
+        <v>135.43</v>
       </c>
     </row>
     <row r="187">
@@ -9829,10 +9829,10 @@
         <v>92.93000000000001</v>
       </c>
       <c r="D187" s="5" t="n">
-        <v>100.24</v>
+        <v>101.62</v>
       </c>
       <c r="E187" s="5" t="n">
-        <v>117.65</v>
+        <v>119.27</v>
       </c>
     </row>
     <row r="188">
@@ -9848,10 +9848,10 @@
         <v>113.36</v>
       </c>
       <c r="D188" s="5" t="n">
-        <v>118.9</v>
+        <v>120.53</v>
       </c>
       <c r="E188" s="5" t="n">
-        <v>143.52</v>
+        <v>145.5</v>
       </c>
     </row>
     <row r="189">
@@ -9867,10 +9867,10 @@
         <v>95.13</v>
       </c>
       <c r="D189" s="5" t="n">
-        <v>106.48</v>
+        <v>107.95</v>
       </c>
       <c r="E189" s="5" t="n">
-        <v>120.45</v>
+        <v>122.1</v>
       </c>
     </row>
     <row r="190">
@@ -9886,10 +9886,10 @@
         <v>91.70999999999999</v>
       </c>
       <c r="D190" s="5" t="n">
-        <v>102.42</v>
+        <v>103.83</v>
       </c>
       <c r="E190" s="5" t="n">
-        <v>116.12</v>
+        <v>117.72</v>
       </c>
     </row>
     <row r="191">
@@ -9905,10 +9905,10 @@
         <v>76.88</v>
       </c>
       <c r="D191" s="5" t="n">
-        <v>86.73999999999999</v>
+        <v>87.93000000000001</v>
       </c>
       <c r="E191" s="5" t="n">
-        <v>97.15000000000001</v>
+        <v>98.48999999999999</v>
       </c>
     </row>
     <row r="192">
@@ -9924,10 +9924,10 @@
         <v>82.59999999999999</v>
       </c>
       <c r="D192" s="5" t="n">
-        <v>91.83</v>
+        <v>93.09</v>
       </c>
       <c r="E192" s="5" t="n">
-        <v>104.18</v>
+        <v>105.61</v>
       </c>
     </row>
     <row r="193">
@@ -9943,10 +9943,10 @@
         <v>99.83</v>
       </c>
       <c r="D193" s="5" t="n">
-        <v>106.99</v>
+        <v>108.46</v>
       </c>
       <c r="E193" s="5" t="n">
-        <v>125.66</v>
+        <v>127.39</v>
       </c>
     </row>
     <row r="194">
@@ -9962,10 +9962,10 @@
         <v>73.22</v>
       </c>
       <c r="D194" s="5" t="n">
-        <v>83.13</v>
+        <v>84.28</v>
       </c>
       <c r="E194" s="5" t="n">
-        <v>91.98999999999999</v>
+        <v>93.26000000000001</v>
       </c>
     </row>
     <row r="195">
@@ -9981,10 +9981,10 @@
         <v>66.72</v>
       </c>
       <c r="D195" s="5" t="n">
-        <v>77.41</v>
+        <v>78.47</v>
       </c>
       <c r="E195" s="5" t="n">
-        <v>83.67</v>
+        <v>84.81999999999999</v>
       </c>
     </row>
     <row r="196">
@@ -10000,10 +10000,10 @@
         <v>64.55</v>
       </c>
       <c r="D196" s="5" t="n">
-        <v>73.25</v>
+        <v>74.25</v>
       </c>
       <c r="E196" s="5" t="n">
-        <v>80.79000000000001</v>
+        <v>81.91</v>
       </c>
     </row>
     <row r="197">
@@ -10019,10 +10019,10 @@
         <v>77.53</v>
       </c>
       <c r="D197" s="5" t="n">
-        <v>92.61</v>
+        <v>93.88</v>
       </c>
       <c r="E197" s="5" t="n">
-        <v>96.81999999999999</v>
+        <v>98.15000000000001</v>
       </c>
     </row>
     <row r="198">
@@ -10038,10 +10038,10 @@
         <v>65.44</v>
       </c>
       <c r="D198" s="5" t="n">
-        <v>76.09999999999999</v>
+        <v>77.15000000000001</v>
       </c>
       <c r="E198" s="5" t="n">
-        <v>81.54000000000001</v>
+        <v>82.66</v>
       </c>
     </row>
     <row r="199">
@@ -10057,10 +10057,10 @@
         <v>58.51</v>
       </c>
       <c r="D199" s="5" t="n">
-        <v>68.16</v>
+        <v>69.09999999999999</v>
       </c>
       <c r="E199" s="5" t="n">
-        <v>72.73999999999999</v>
+        <v>73.73999999999999</v>
       </c>
     </row>
     <row r="200">
@@ -10076,10 +10076,10 @@
         <v>83.67</v>
       </c>
       <c r="D200" s="5" t="n">
-        <v>82.93000000000001</v>
+        <v>84.06999999999999</v>
       </c>
       <c r="E200" s="5" t="n">
-        <v>103.88</v>
+        <v>105.31</v>
       </c>
     </row>
     <row r="201">
@@ -10095,10 +10095,10 @@
         <v>58.28</v>
       </c>
       <c r="D201" s="5" t="n">
-        <v>66.73</v>
+        <v>67.64</v>
       </c>
       <c r="E201" s="5" t="n">
-        <v>72.27</v>
+        <v>73.26000000000001</v>
       </c>
     </row>
     <row r="202">
@@ -10114,10 +10114,10 @@
         <v>46.18</v>
       </c>
       <c r="D202" s="5" t="n">
-        <v>51.11</v>
+        <v>51.82</v>
       </c>
       <c r="E202" s="5" t="n">
-        <v>57.19</v>
+        <v>57.98</v>
       </c>
     </row>
     <row r="203">
@@ -10133,10 +10133,10 @@
         <v>40.2</v>
       </c>
       <c r="D203" s="5" t="n">
-        <v>46.11</v>
+        <v>46.74</v>
       </c>
       <c r="E203" s="5" t="n">
-        <v>50.11</v>
+        <v>50.8</v>
       </c>
     </row>
     <row r="204">
@@ -10152,10 +10152,10 @@
         <v>35.09</v>
       </c>
       <c r="D204" s="5" t="n">
-        <v>39.12</v>
+        <v>39.66</v>
       </c>
       <c r="E204" s="5" t="n">
-        <v>44.02</v>
+        <v>44.63</v>
       </c>
     </row>
     <row r="205">
@@ -10171,10 +10171,10 @@
         <v>35.86</v>
       </c>
       <c r="D205" s="5" t="n">
-        <v>42.57</v>
+        <v>43.16</v>
       </c>
       <c r="E205" s="5" t="n">
-        <v>45.29</v>
+        <v>45.91</v>
       </c>
     </row>
     <row r="206">
@@ -10190,10 +10190,10 @@
         <v>42.74</v>
       </c>
       <c r="D206" s="5" t="n">
-        <v>48.03</v>
+        <v>48.69</v>
       </c>
       <c r="E206" s="5" t="n">
-        <v>53.7</v>
+        <v>54.44</v>
       </c>
     </row>
     <row r="207">
@@ -10209,10 +10209,10 @@
         <v>30.26</v>
       </c>
       <c r="D207" s="5" t="n">
-        <v>38.06</v>
+        <v>38.58</v>
       </c>
       <c r="E207" s="5" t="n">
-        <v>37.82</v>
+        <v>38.34</v>
       </c>
     </row>
     <row r="208">
@@ -10228,10 +10228,10 @@
         <v>26.55</v>
       </c>
       <c r="D208" s="5" t="n">
-        <v>34.02</v>
+        <v>34.49</v>
       </c>
       <c r="E208" s="5" t="n">
-        <v>33.02</v>
+        <v>33.47</v>
       </c>
     </row>
     <row r="209">
@@ -10247,10 +10247,10 @@
         <v>37.4</v>
       </c>
       <c r="D209" s="5" t="n">
-        <v>43.67</v>
+        <v>44.27</v>
       </c>
       <c r="E209" s="5" t="n">
-        <v>46.37</v>
+        <v>47.01</v>
       </c>
     </row>
     <row r="210">
@@ -10266,10 +10266,10 @@
         <v>52.86</v>
       </c>
       <c r="D210" s="5" t="n">
-        <v>56.06</v>
+        <v>56.83</v>
       </c>
       <c r="E210" s="5" t="n">
-        <v>65.34</v>
+        <v>66.23999999999999</v>
       </c>
     </row>
     <row r="211">
@@ -10285,10 +10285,10 @@
         <v>65.43000000000001</v>
       </c>
       <c r="D211" s="5" t="n">
-        <v>67.12</v>
+        <v>68.04000000000001</v>
       </c>
       <c r="E211" s="5" t="n">
-        <v>80.64</v>
+        <v>81.75</v>
       </c>
     </row>
     <row r="212">
@@ -10304,10 +10304,10 @@
         <v>43.8</v>
       </c>
       <c r="D212" s="5" t="n">
-        <v>49.63</v>
+        <v>50.32</v>
       </c>
       <c r="E212" s="5" t="n">
-        <v>53.88</v>
+        <v>54.62</v>
       </c>
     </row>
     <row r="213">
@@ -10323,10 +10323,10 @@
         <v>47.73</v>
       </c>
       <c r="D213" s="5" t="n">
-        <v>51.18</v>
+        <v>51.89</v>
       </c>
       <c r="E213" s="5" t="n">
-        <v>58.6</v>
+        <v>59.4</v>
       </c>
     </row>
     <row r="214">
@@ -10342,10 +10342,10 @@
         <v>54.37</v>
       </c>
       <c r="D214" s="5" t="n">
-        <v>56.13</v>
+        <v>56.91</v>
       </c>
       <c r="E214" s="5" t="n">
-        <v>66.62</v>
+        <v>67.54000000000001</v>
       </c>
     </row>
     <row r="215">
@@ -10361,10 +10361,10 @@
         <v>61.17</v>
       </c>
       <c r="D215" s="5" t="n">
-        <v>65.34999999999999</v>
+        <v>66.25</v>
       </c>
       <c r="E215" s="5" t="n">
-        <v>74.77</v>
+        <v>75.8</v>
       </c>
     </row>
     <row r="216">
@@ -10380,10 +10380,10 @@
         <v>223.28</v>
       </c>
       <c r="D216" s="5" t="n">
-        <v>157.61</v>
+        <v>159.78</v>
       </c>
       <c r="E216" s="5" t="n">
-        <v>272.27</v>
+        <v>276.01</v>
       </c>
     </row>
     <row r="217">
@@ -10399,10 +10399,10 @@
         <v>334.25</v>
       </c>
       <c r="D217" s="5" t="n">
-        <v>244.16</v>
+        <v>247.52</v>
       </c>
       <c r="E217" s="5" t="n">
-        <v>406.6</v>
+        <v>412.19</v>
       </c>
     </row>
     <row r="218">
@@ -10418,10 +10418,10 @@
         <v>185.43</v>
       </c>
       <c r="D218" s="5" t="n">
-        <v>163.85</v>
+        <v>166.11</v>
       </c>
       <c r="E218" s="5" t="n">
-        <v>224.93</v>
+        <v>228.02</v>
       </c>
     </row>
     <row r="219">
@@ -10437,10 +10437,10 @@
         <v>55.55</v>
       </c>
       <c r="D219" s="5" t="n">
-        <v>64.77</v>
+        <v>65.66</v>
       </c>
       <c r="E219" s="5" t="n">
-        <v>67.19</v>
+        <v>68.12</v>
       </c>
     </row>
     <row r="220">
@@ -10456,10 +10456,10 @@
         <v>52.32</v>
       </c>
       <c r="D220" s="5" t="n">
-        <v>61.78</v>
+        <v>62.63</v>
       </c>
       <c r="E220" s="5" t="n">
-        <v>63.11</v>
+        <v>63.98</v>
       </c>
     </row>
     <row r="221">
@@ -10475,10 +10475,10 @@
         <v>80.47</v>
       </c>
       <c r="D221" s="5" t="n">
-        <v>79.84999999999999</v>
+        <v>80.95</v>
       </c>
       <c r="E221" s="5" t="n">
-        <v>96.65000000000001</v>
+        <v>97.98</v>
       </c>
     </row>
     <row r="222">
@@ -10494,10 +10494,10 @@
         <v>132.44</v>
       </c>
       <c r="D222" s="5" t="n">
-        <v>115.48</v>
+        <v>117.07</v>
       </c>
       <c r="E222" s="5" t="n">
-        <v>158.4</v>
+        <v>160.58</v>
       </c>
     </row>
     <row r="223">
@@ -10513,10 +10513,10 @@
         <v>182.96</v>
       </c>
       <c r="D223" s="5" t="n">
-        <v>153.18</v>
+        <v>155.28</v>
       </c>
       <c r="E223" s="5" t="n">
-        <v>217.91</v>
+        <v>220.91</v>
       </c>
     </row>
     <row r="224">
@@ -10532,10 +10532,10 @@
         <v>189.96</v>
       </c>
       <c r="D224" s="5" t="n">
-        <v>165.43</v>
+        <v>167.71</v>
       </c>
       <c r="E224" s="5" t="n">
-        <v>224.63</v>
+        <v>227.72</v>
       </c>
     </row>
     <row r="225">
@@ -10551,10 +10551,10 @@
         <v>257.03</v>
       </c>
       <c r="D225" s="5" t="n">
-        <v>191.05</v>
+        <v>193.68</v>
       </c>
       <c r="E225" s="5" t="n">
-        <v>301.78</v>
+        <v>305.93</v>
       </c>
     </row>
     <row r="226">
@@ -10570,10 +10570,10 @@
         <v>196.7</v>
       </c>
       <c r="D226" s="5" t="n">
-        <v>171.61</v>
+        <v>173.97</v>
       </c>
       <c r="E226" s="5" t="n">
-        <v>229.32</v>
+        <v>232.47</v>
       </c>
     </row>
     <row r="227">
@@ -10589,10 +10589,10 @@
         <v>265.86</v>
       </c>
       <c r="D227" s="5" t="n">
-        <v>254.68</v>
+        <v>258.19</v>
       </c>
       <c r="E227" s="5" t="n">
-        <v>308.11</v>
+        <v>312.35</v>
       </c>
     </row>
     <row r="228">
@@ -10608,10 +10608,10 @@
         <v>415.45</v>
       </c>
       <c r="D228" s="5" t="n">
-        <v>400.1</v>
+        <v>405.6</v>
       </c>
       <c r="E228" s="5" t="n">
-        <v>478.64</v>
+        <v>485.22</v>
       </c>
     </row>
     <row r="229">
@@ -10627,10 +10627,10 @@
         <v>439.14</v>
       </c>
       <c r="D229" s="5" t="n">
-        <v>458.4</v>
+        <v>464.7</v>
       </c>
       <c r="E229" s="5" t="n">
-        <v>502.96</v>
+        <v>509.88</v>
       </c>
     </row>
     <row r="230">
@@ -10646,10 +10646,10 @@
         <v>507.37</v>
       </c>
       <c r="D230" s="5" t="n">
-        <v>445.77</v>
+        <v>451.9</v>
       </c>
       <c r="E230" s="5" t="n">
-        <v>577.5700000000001</v>
+        <v>585.52</v>
       </c>
     </row>
     <row r="231">
@@ -10665,10 +10665,10 @@
         <v>129.62</v>
       </c>
       <c r="D231" s="5" t="n">
-        <v>151.06</v>
+        <v>153.14</v>
       </c>
       <c r="E231" s="5" t="n">
-        <v>146.66</v>
+        <v>148.68</v>
       </c>
     </row>
     <row r="232">
@@ -10684,10 +10684,10 @@
         <v>152.44</v>
       </c>
       <c r="D232" s="5" t="n">
-        <v>176.46</v>
+        <v>178.89</v>
       </c>
       <c r="E232" s="5" t="n">
-        <v>171.44</v>
+        <v>173.8</v>
       </c>
     </row>
     <row r="233">
@@ -10703,10 +10703,10 @@
         <v>161.28</v>
       </c>
       <c r="D233" s="5" t="n">
-        <v>172.19</v>
+        <v>174.56</v>
       </c>
       <c r="E233" s="5" t="n">
-        <v>180.27</v>
+        <v>182.75</v>
       </c>
     </row>
     <row r="234">
@@ -10722,10 +10722,10 @@
         <v>118.14</v>
       </c>
       <c r="D234" s="5" t="n">
-        <v>134.98</v>
+        <v>136.84</v>
       </c>
       <c r="E234" s="5" t="n">
-        <v>131.25</v>
+        <v>133.05</v>
       </c>
     </row>
     <row r="235">
@@ -10741,10 +10741,10 @@
         <v>76.42</v>
       </c>
       <c r="D235" s="5" t="n">
-        <v>94.37</v>
+        <v>95.67</v>
       </c>
       <c r="E235" s="5" t="n">
-        <v>84.39</v>
+        <v>85.55</v>
       </c>
     </row>
     <row r="236">
@@ -10760,10 +10760,10 @@
         <v>113.54</v>
       </c>
       <c r="D236" s="5" t="n">
-        <v>108.78</v>
+        <v>110.28</v>
       </c>
       <c r="E236" s="5" t="n">
-        <v>124.81</v>
+        <v>126.53</v>
       </c>
     </row>
     <row r="237">
@@ -10779,10 +10779,10 @@
         <v>95.48</v>
       </c>
       <c r="D237" s="5" t="n">
-        <v>97.17</v>
+        <v>98.5</v>
       </c>
       <c r="E237" s="5" t="n">
-        <v>104.49</v>
+        <v>105.93</v>
       </c>
     </row>
     <row r="238">
@@ -10798,10 +10798,10 @@
         <v>157.17</v>
       </c>
       <c r="D238" s="5" t="n">
-        <v>134.09</v>
+        <v>135.94</v>
       </c>
       <c r="E238" s="5" t="n">
-        <v>171.23</v>
+        <v>173.59</v>
       </c>
     </row>
     <row r="239">
@@ -10817,10 +10817,10 @@
         <v>111.33</v>
       </c>
       <c r="D239" s="5" t="n">
-        <v>119.44</v>
+        <v>121.08</v>
       </c>
       <c r="E239" s="5" t="n">
-        <v>120.95</v>
+        <v>122.61</v>
       </c>
     </row>
     <row r="240">
@@ -10836,10 +10836,10 @@
         <v>187</v>
       </c>
       <c r="D240" s="5" t="n">
-        <v>178.63</v>
+        <v>181.09</v>
       </c>
       <c r="E240" s="5" t="n">
-        <v>202.58</v>
+        <v>205.36</v>
       </c>
     </row>
     <row r="241">
@@ -10855,10 +10855,10 @@
         <v>117.86</v>
       </c>
       <c r="D241" s="5" t="n">
-        <v>110.85</v>
+        <v>112.38</v>
       </c>
       <c r="E241" s="5" t="n">
-        <v>127.31</v>
+        <v>129.07</v>
       </c>
     </row>
     <row r="242">
@@ -10874,10 +10874,10 @@
         <v>83.20999999999999</v>
       </c>
       <c r="D242" s="5" t="n">
-        <v>83.15000000000001</v>
+        <v>84.29000000000001</v>
       </c>
       <c r="E242" s="5" t="n">
-        <v>89.54000000000001</v>
+        <v>90.77</v>
       </c>
     </row>
     <row r="243">
@@ -10893,10 +10893,10 @@
         <v>64.40000000000001</v>
       </c>
       <c r="D243" s="5" t="n">
-        <v>72.5</v>
+        <v>73.5</v>
       </c>
       <c r="E243" s="5" t="n">
-        <v>69.04000000000001</v>
+        <v>69.98999999999999</v>
       </c>
     </row>
     <row r="244">
@@ -10912,10 +10912,10 @@
         <v>48.95</v>
       </c>
       <c r="D244" s="5" t="n">
-        <v>54.22</v>
+        <v>54.96</v>
       </c>
       <c r="E244" s="5" t="n">
-        <v>52.27</v>
+        <v>52.99</v>
       </c>
     </row>
     <row r="245">
@@ -10931,10 +10931,10 @@
         <v>31.89</v>
       </c>
       <c r="D245" s="5" t="n">
-        <v>39.48</v>
+        <v>40.03</v>
       </c>
       <c r="E245" s="5" t="n">
-        <v>33.98</v>
+        <v>34.45</v>
       </c>
     </row>
     <row r="246">
@@ -10950,10 +10950,10 @@
         <v>73.34999999999999</v>
       </c>
       <c r="D246" s="5" t="n">
-        <v>77.59999999999999</v>
+        <v>78.67</v>
       </c>
       <c r="E246" s="5" t="n">
-        <v>78.01000000000001</v>
+        <v>79.08</v>
       </c>
     </row>
     <row r="247">
@@ -10969,10 +10969,10 @@
         <v>117.11</v>
       </c>
       <c r="D247" s="5" t="n">
-        <v>98.7</v>
+        <v>100.05</v>
       </c>
       <c r="E247" s="5" t="n">
-        <v>124.28</v>
+        <v>125.99</v>
       </c>
     </row>
     <row r="248">
@@ -10988,10 +10988,10 @@
         <v>172.77</v>
       </c>
       <c r="D248" s="5" t="n">
-        <v>169.73</v>
+        <v>172.06</v>
       </c>
       <c r="E248" s="5" t="n">
-        <v>182.79</v>
+        <v>185.3</v>
       </c>
     </row>
     <row r="249">
@@ -11007,10 +11007,10 @@
         <v>164.47</v>
       </c>
       <c r="D249" s="5" t="n">
-        <v>126.28</v>
+        <v>128.02</v>
       </c>
       <c r="E249" s="5" t="n">
-        <v>173.47</v>
+        <v>175.85</v>
       </c>
     </row>
     <row r="250">
@@ -11026,10 +11026,10 @@
         <v>74.56</v>
       </c>
       <c r="D250" s="5" t="n">
-        <v>77.90000000000001</v>
+        <v>78.97</v>
       </c>
       <c r="E250" s="5" t="n">
-        <v>78.40000000000001</v>
+        <v>79.48</v>
       </c>
     </row>
     <row r="251">
@@ -11045,10 +11045,10 @@
         <v>77.23</v>
       </c>
       <c r="D251" s="5" t="n">
-        <v>88.86</v>
+        <v>90.09</v>
       </c>
       <c r="E251" s="5" t="n">
-        <v>80.92</v>
+        <v>82.03</v>
       </c>
     </row>
     <row r="252">
@@ -11064,10 +11064,10 @@
         <v>87.48999999999999</v>
       </c>
       <c r="D252" s="5" t="n">
-        <v>96.78</v>
+        <v>98.12</v>
       </c>
       <c r="E252" s="5" t="n">
-        <v>91.34999999999999</v>
+        <v>92.61</v>
       </c>
     </row>
     <row r="253">
@@ -11083,10 +11083,10 @@
         <v>127.4</v>
       </c>
       <c r="D253" s="5" t="n">
-        <v>129.73</v>
+        <v>131.51</v>
       </c>
       <c r="E253" s="5" t="n">
-        <v>132.57</v>
+        <v>134.39</v>
       </c>
     </row>
     <row r="254">
@@ -11102,10 +11102,10 @@
         <v>135.85</v>
       </c>
       <c r="D254" s="5" t="n">
-        <v>123.8</v>
+        <v>125.5</v>
       </c>
       <c r="E254" s="5" t="n">
-        <v>141.26</v>
+        <v>143.2</v>
       </c>
     </row>
     <row r="255">
@@ -11121,10 +11121,10 @@
         <v>162.05</v>
       </c>
       <c r="D255" s="5" t="n">
-        <v>135.18</v>
+        <v>137.04</v>
       </c>
       <c r="E255" s="5" t="n">
-        <v>168.38</v>
+        <v>170.69</v>
       </c>
     </row>
     <row r="256">
@@ -11140,10 +11140,10 @@
         <v>31.67</v>
       </c>
       <c r="D256" s="5" t="n">
-        <v>51.56</v>
+        <v>52.27</v>
       </c>
       <c r="E256" s="5" t="n">
-        <v>32.88</v>
+        <v>33.34</v>
       </c>
     </row>
     <row r="257">
@@ -11159,10 +11159,10 @@
         <v>61.54</v>
       </c>
       <c r="D257" s="5" t="n">
-        <v>73.51000000000001</v>
+        <v>74.53</v>
       </c>
       <c r="E257" s="5" t="n">
-        <v>63.85</v>
+        <v>64.73</v>
       </c>
     </row>
     <row r="258">
@@ -11178,10 +11178,10 @@
         <v>259.36</v>
       </c>
       <c r="D258" s="5" t="n">
-        <v>184.04</v>
+        <v>186.57</v>
       </c>
       <c r="E258" s="5" t="n">
-        <v>268.94</v>
+        <v>272.64</v>
       </c>
     </row>
     <row r="259">
@@ -11197,10 +11197,10 @@
         <v>150.79</v>
       </c>
       <c r="D259" s="5" t="n">
-        <v>139.31</v>
+        <v>141.23</v>
       </c>
       <c r="E259" s="5" t="n">
-        <v>156.26</v>
+        <v>158.41</v>
       </c>
     </row>
     <row r="260">
@@ -11216,10 +11216,10 @@
         <v>147.57</v>
       </c>
       <c r="D260" s="5" t="n">
-        <v>117.78</v>
+        <v>119.4</v>
       </c>
       <c r="E260" s="5" t="n">
-        <v>152.45</v>
+        <v>154.55</v>
       </c>
     </row>
     <row r="261">
@@ -11235,10 +11235,10 @@
         <v>72.06999999999999</v>
       </c>
       <c r="D261" s="5" t="n">
-        <v>77.15000000000001</v>
+        <v>78.20999999999999</v>
       </c>
       <c r="E261" s="5" t="n">
-        <v>74.23</v>
+        <v>75.25</v>
       </c>
     </row>
     <row r="262">
@@ -11254,10 +11254,10 @@
         <v>80.88</v>
       </c>
       <c r="D262" s="5" t="n">
-        <v>81.13</v>
+        <v>82.23999999999999</v>
       </c>
       <c r="E262" s="5" t="n">
-        <v>83.05</v>
+        <v>84.19</v>
       </c>
     </row>
     <row r="263">
@@ -11273,10 +11273,10 @@
         <v>99.73999999999999</v>
       </c>
       <c r="D263" s="5" t="n">
-        <v>100.89</v>
+        <v>102.28</v>
       </c>
       <c r="E263" s="5" t="n">
-        <v>102.16</v>
+        <v>103.57</v>
       </c>
     </row>
     <row r="264">
@@ -11292,10 +11292,10 @@
         <v>108.25</v>
       </c>
       <c r="D264" s="5" t="n">
-        <v>97.70999999999999</v>
+        <v>99.05</v>
       </c>
       <c r="E264" s="5" t="n">
-        <v>110.6</v>
+        <v>112.12</v>
       </c>
     </row>
     <row r="265">
@@ -11311,10 +11311,10 @@
         <v>252.36</v>
       </c>
       <c r="D265" s="5" t="n">
-        <v>172.59</v>
+        <v>174.97</v>
       </c>
       <c r="E265" s="5" t="n">
-        <v>257.21</v>
+        <v>260.74</v>
       </c>
     </row>
     <row r="266">
@@ -11330,10 +11330,10 @@
         <v>82.66</v>
       </c>
       <c r="D266" s="5" t="n">
-        <v>83.34</v>
+        <v>84.48999999999999</v>
       </c>
       <c r="E266" s="5" t="n">
-        <v>83.88</v>
+        <v>85.03</v>
       </c>
     </row>
     <row r="267">
@@ -11349,10 +11349,10 @@
         <v>73.3</v>
       </c>
       <c r="D267" s="5" t="n">
-        <v>79.01000000000001</v>
+        <v>80.09</v>
       </c>
       <c r="E267" s="5" t="n">
-        <v>74.06</v>
+        <v>75.06999999999999</v>
       </c>
     </row>
     <row r="268">
@@ -11368,10 +11368,10 @@
         <v>40.87</v>
       </c>
       <c r="D268" s="5" t="n">
-        <v>54.67</v>
+        <v>55.42</v>
       </c>
       <c r="E268" s="5" t="n">
-        <v>41.11</v>
+        <v>41.68</v>
       </c>
     </row>
     <row r="269">
@@ -11387,10 +11387,10 @@
         <v>45.11</v>
       </c>
       <c r="D269" s="5" t="n">
-        <v>55.88</v>
+        <v>56.65</v>
       </c>
       <c r="E269" s="5" t="n">
-        <v>45.29</v>
+        <v>45.91</v>
       </c>
     </row>
     <row r="270">
@@ -11406,10 +11406,10 @@
         <v>48.44</v>
       </c>
       <c r="D270" s="5" t="n">
-        <v>63.17</v>
+        <v>64.04000000000001</v>
       </c>
       <c r="E270" s="5" t="n">
-        <v>48.54</v>
+        <v>49.2</v>
       </c>
     </row>
     <row r="271">
@@ -11425,10 +11425,10 @@
         <v>46.52</v>
       </c>
       <c r="D271" s="5" t="n">
-        <v>54.38</v>
+        <v>55.13</v>
       </c>
       <c r="E271" s="5" t="n">
-        <v>46.52</v>
+        <v>47.16</v>
       </c>
     </row>
     <row r="272">
@@ -11444,10 +11444,10 @@
         <v>64.54000000000001</v>
       </c>
       <c r="D272" s="5" t="n">
-        <v>64.03</v>
+        <v>64.61</v>
       </c>
       <c r="E272" s="5" t="n">
-        <v>64.54000000000001</v>
+        <v>65.13</v>
       </c>
     </row>
     <row r="273">
@@ -11463,10 +11463,10 @@
         <v>72.40000000000001</v>
       </c>
       <c r="D273" s="5" t="n">
-        <v>69.87</v>
+        <v>70.19</v>
       </c>
       <c r="E273" s="5" t="n">
-        <v>72.40000000000001</v>
+        <v>72.73</v>
       </c>
     </row>
     <row r="274">
@@ -11495,16 +11495,16 @@
         </is>
       </c>
       <c r="B275" s="5" t="n">
-        <v>57.69</v>
+        <v>53.31</v>
       </c>
       <c r="C275" s="5" t="n">
-        <v>51.98</v>
+        <v>45.62</v>
       </c>
       <c r="D275" s="5" t="n">
-        <v>57.69</v>
+        <v>53.31</v>
       </c>
       <c r="E275" s="5" t="n">
-        <v>51.98</v>
+        <v>45.62</v>
       </c>
     </row>
   </sheetData>
